--- a/IAC IP25 - Machine Learning - Development Log - Pranay Sunil Jagtap.xlsx
+++ b/IAC IP25 - Machine Learning - Development Log - Pranay Sunil Jagtap.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29303"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,15 +10,18 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="345" documentId="8_{A89BEE9E-4518-4BCB-B274-F05E8F8D25DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F161BB36-EA32-4A73-9501-B3F289306DBA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Challenges &amp; Goals" sheetId="2" r:id="rId2"/>
     <sheet name="Tracker" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -248,6 +251,9 @@
     <t>Get Industry Training completion certificate</t>
   </si>
   <si>
+    <t>6/8/12 weeks starting 7th March 2025</t>
+  </si>
+  <si>
     <t>Develop specialised talent and abilities you need to advance your career</t>
   </si>
   <si>
@@ -274,6 +280,9 @@
     <t>Start date (MM-DD-YYYY)</t>
   </si>
   <si>
+    <t>01-23-2025</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -292,6 +301,9 @@
     <t>Internship Preparation &amp; Goal Setting</t>
   </si>
   <si>
+    <t>Orientation</t>
+  </si>
+  <si>
     <t>Internship Preparation</t>
   </si>
   <si>
@@ -316,25 +328,16 @@
     <t>Live Project</t>
   </si>
   <si>
+    <t>GPI Live Project Onboarding</t>
+  </si>
+  <si>
+    <t>Working on Problem Statement</t>
+  </si>
+  <si>
     <t>Submit weekly update report</t>
   </si>
   <si>
     <t>Submit project deliverables</t>
-  </si>
-  <si>
-    <t>Orientation</t>
-  </si>
-  <si>
-    <t>01-23-2025</t>
-  </si>
-  <si>
-    <t>Working on Problem Statement</t>
-  </si>
-  <si>
-    <t>GPI Live Project Onboarding</t>
-  </si>
-  <si>
-    <t>6/8/12 weeks starting 7th March 2025</t>
   </si>
 </sst>
 </file>
@@ -343,9 +346,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-4009]dd\-mm\-yyyy;@"/>
-    <numFmt numFmtId="166" formatCode="[hh]:mm;@"/>
+    <numFmt numFmtId="165" formatCode="[hh]:mm;@"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -664,9 +667,6 @@
   </cellStyleXfs>
   <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -776,15 +776,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="20" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -819,8 +810,20 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -911,10 +914,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1107,134 +1106,134 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+    <row r="1" spans="1:10" ht="21">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.6">
+      <c r="A2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.6">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.6">
+      <c r="A4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.6">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="15.6">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="15.6">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:10" ht="15.6">
+      <c r="A9" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="15.6">
       <c r="A10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="15.6">
+      <c r="A11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.6">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="15.6">
       <c r="A14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:2" ht="15.6">
+      <c r="A17" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
+    <row r="18" spans="1:2" ht="15.6">
+      <c r="A18" s="8"/>
       <c r="B18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
+    <row r="19" spans="1:2" ht="15.6">
+      <c r="A19" s="9"/>
       <c r="B19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="15.6">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="15.6">
       <c r="A23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12" t="s">
+    <row r="24" spans="1:2" ht="15.6">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="12" t="s">
+    <row r="25" spans="1:2" ht="15.6">
+      <c r="A25" s="12"/>
+      <c r="B25" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="12" t="s">
+    <row r="26" spans="1:2" ht="15.6">
+      <c r="A26" s="13"/>
+      <c r="B26" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="15"/>
-      <c r="B27" s="12" t="s">
+    <row r="27" spans="1:2" ht="15.6">
+      <c r="A27" s="14"/>
+      <c r="B27" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="16"/>
-      <c r="B28" s="17" t="s">
+    <row r="28" spans="1:2" ht="15.6">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="18"/>
-      <c r="B29" s="12" t="s">
+    <row r="29" spans="1:2" ht="15.6">
+      <c r="A29" s="17"/>
+      <c r="B29" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1247,296 +1246,296 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.3984375" style="19" customWidth="1"/>
-    <col min="2" max="2" width="44" style="20" customWidth="1"/>
-    <col min="3" max="3" width="33.5" style="20" customWidth="1"/>
-    <col min="4" max="4" width="37.8984375" style="20" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="20"/>
+    <col min="1" max="1" width="7.375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="44" style="19" customWidth="1"/>
+    <col min="3" max="3" width="33.5" style="19" customWidth="1"/>
+    <col min="4" max="4" width="37.875" style="19" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="15.6">
+      <c r="A1" s="51" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-    </row>
-    <row r="3" spans="1:2" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+    </row>
+    <row r="3" spans="1:2" ht="78.75" customHeight="1">
+      <c r="A3" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="53"/>
-    </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="B3" s="70"/>
+    </row>
+    <row r="5" spans="1:2" ht="15.6">
+      <c r="A5" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="22"/>
-    </row>
-    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="22">
+      <c r="B5" s="21"/>
+    </row>
+    <row r="6" spans="1:2" ht="15.6">
+      <c r="A6" s="21">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="22">
+    <row r="7" spans="1:2" ht="15.6">
+      <c r="A7" s="21">
         <v>2</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="22">
+    <row r="8" spans="1:2" ht="15.6">
+      <c r="A8" s="21">
         <v>3</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="22" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="22">
+    <row r="9" spans="1:2" ht="15.6">
+      <c r="A9" s="21">
         <v>4</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="22">
+    <row r="10" spans="1:2" ht="15.6">
+      <c r="A10" s="21">
         <v>5</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="22">
+    <row r="11" spans="1:2" ht="15.6">
+      <c r="A11" s="21">
         <v>6</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:2" ht="15.6">
+      <c r="A13" s="23" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="22">
+    <row r="14" spans="1:2" ht="31.15">
+      <c r="A14" s="21">
         <v>1</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="22">
+    <row r="15" spans="1:2" ht="31.15">
+      <c r="A15" s="21">
         <v>2</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="24" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="22">
+    <row r="16" spans="1:2" ht="15.6">
+      <c r="A16" s="21">
         <v>3</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="22">
+    <row r="17" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A17" s="21">
         <v>4</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="22">
+    <row r="18" spans="1:4" ht="15.6">
+      <c r="A18" s="21">
         <v>5</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="24" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="22">
+    <row r="19" spans="1:4" ht="31.15">
+      <c r="A19" s="21">
         <v>6</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="22">
+    <row r="20" spans="1:4" ht="31.15">
+      <c r="A20" s="21">
         <v>7</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="24" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:4" ht="15.6">
+      <c r="A21" s="51" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:4" ht="15.6">
+      <c r="A23" s="51" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="26" t="s">
+    <row r="24" spans="1:4" ht="15.6">
+      <c r="A24" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-    </row>
-    <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="28" t="s">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.6">
+      <c r="A25" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="29" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="31" t="s">
+    <row r="26" spans="1:4" ht="79.900000000000006">
+      <c r="A26" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="33" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="78" x14ac:dyDescent="0.3">
-      <c r="A27" s="31" t="s">
+    <row r="27" spans="1:4" ht="78">
+      <c r="A27" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D27" s="33" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" s="35" t="s">
+    <row r="28" spans="1:4" ht="93.6">
+      <c r="A28" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="B28" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="36" t="s">
+      <c r="C28" s="34" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
-      <c r="B29" s="37"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-    </row>
-    <row r="30" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-    </row>
-    <row r="31" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-    </row>
-    <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-    </row>
-    <row r="33" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-    </row>
-    <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-    </row>
-    <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-    </row>
-    <row r="36" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-    </row>
-    <row r="37" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-    </row>
-    <row r="38" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="37"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-    </row>
-    <row r="39" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-    </row>
-    <row r="40" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-    </row>
-    <row r="41" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
+      <c r="D28" s="35" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.6">
+      <c r="A29" s="36"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.6">
+      <c r="A30" s="36"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.6">
+      <c r="A31" s="36"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.6">
+      <c r="A32" s="36"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+    </row>
+    <row r="33" spans="1:4" ht="15.6">
+      <c r="A33" s="36"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+    </row>
+    <row r="34" spans="1:4" ht="15.6">
+      <c r="A34" s="36"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+    </row>
+    <row r="35" spans="1:4" ht="15.6">
+      <c r="A35" s="36"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+    </row>
+    <row r="36" spans="1:4" ht="15.6">
+      <c r="A36" s="36"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+    </row>
+    <row r="37" spans="1:4" ht="15.6">
+      <c r="A37" s="36"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+    </row>
+    <row r="38" spans="1:4" ht="15.6">
+      <c r="A38" s="36"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+    </row>
+    <row r="39" spans="1:4" ht="15.6">
+      <c r="A39" s="36"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+    </row>
+    <row r="40" spans="1:4" ht="15.6">
+      <c r="A40" s="36"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+    </row>
+    <row r="41" spans="1:4" ht="15.6">
+      <c r="A41" s="36"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1559,5517 +1558,5517 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:EZ23"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.09765625" customWidth="1"/>
-    <col min="2" max="2" width="20.796875" customWidth="1"/>
-    <col min="3" max="93" width="5.59765625" customWidth="1"/>
-    <col min="94" max="117" width="5.796875" customWidth="1"/>
-    <col min="118" max="119" width="5.3984375" customWidth="1"/>
+    <col min="1" max="1" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="3" max="93" width="5.625" customWidth="1"/>
+    <col min="94" max="117" width="5.75" customWidth="1"/>
+    <col min="118" max="119" width="5.375" customWidth="1"/>
     <col min="120" max="154" width="5.5" customWidth="1"/>
     <col min="155" max="155" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="39"/>
-    </row>
-    <row r="2" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="39"/>
-    </row>
-    <row r="3" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="1" spans="1:156" ht="15.6">
+      <c r="A1" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="39"/>
-    </row>
-    <row r="4" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="B1" s="38"/>
+    </row>
+    <row r="2" spans="1:156" ht="15.6">
+      <c r="A2" s="3"/>
+      <c r="B2" s="38"/>
+    </row>
+    <row r="3" spans="1:156" ht="15.6">
+      <c r="A3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="39"/>
-    </row>
-    <row r="5" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="B3" s="38"/>
+    </row>
+    <row r="4" spans="1:156" ht="15.6">
+      <c r="A4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="39"/>
-    </row>
-    <row r="6" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="39"/>
-    </row>
-    <row r="7" spans="1:156" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="B4" s="38"/>
+    </row>
+    <row r="5" spans="1:156" ht="15.6">
+      <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="41"/>
-    </row>
-    <row r="8" spans="1:156" s="43" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="42"/>
-      <c r="B8" s="48" t="s">
+      <c r="B5" s="38"/>
+    </row>
+    <row r="6" spans="1:156" ht="15.6">
+      <c r="A6" s="3"/>
+      <c r="B6" s="38"/>
+    </row>
+    <row r="7" spans="1:156" ht="31.15">
+      <c r="A7" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="50">
+      <c r="B7" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="40"/>
+    </row>
+    <row r="8" spans="1:156" s="42" customFormat="1" ht="66" customHeight="1">
+      <c r="A8" s="41"/>
+      <c r="B8" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="49">
         <f>DATE(2025,1,23)</f>
         <v>45680</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="50">
         <f t="shared" ref="D8:AI8" si="0">C8+1</f>
         <v>45681</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="50">
         <f t="shared" si="0"/>
         <v>45682</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="50">
         <f t="shared" si="0"/>
         <v>45683</v>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="50">
         <f t="shared" si="0"/>
         <v>45684</v>
       </c>
-      <c r="H8" s="51">
+      <c r="H8" s="50">
         <f t="shared" si="0"/>
         <v>45685</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="50">
         <f t="shared" si="0"/>
         <v>45686</v>
       </c>
-      <c r="J8" s="51">
+      <c r="J8" s="50">
         <f t="shared" si="0"/>
         <v>45687</v>
       </c>
-      <c r="K8" s="51">
+      <c r="K8" s="50">
         <f t="shared" si="0"/>
         <v>45688</v>
       </c>
-      <c r="L8" s="51">
+      <c r="L8" s="50">
         <f t="shared" si="0"/>
         <v>45689</v>
       </c>
-      <c r="M8" s="51">
+      <c r="M8" s="50">
         <f t="shared" si="0"/>
         <v>45690</v>
       </c>
-      <c r="N8" s="51">
+      <c r="N8" s="50">
         <f t="shared" si="0"/>
         <v>45691</v>
       </c>
-      <c r="O8" s="51">
+      <c r="O8" s="50">
         <f t="shared" si="0"/>
         <v>45692</v>
       </c>
-      <c r="P8" s="51">
+      <c r="P8" s="50">
         <f t="shared" si="0"/>
         <v>45693</v>
       </c>
-      <c r="Q8" s="51">
+      <c r="Q8" s="50">
         <f t="shared" si="0"/>
         <v>45694</v>
       </c>
-      <c r="R8" s="51">
+      <c r="R8" s="50">
         <f t="shared" si="0"/>
         <v>45695</v>
       </c>
-      <c r="S8" s="51">
+      <c r="S8" s="50">
         <f t="shared" si="0"/>
         <v>45696</v>
       </c>
-      <c r="T8" s="51">
+      <c r="T8" s="50">
         <f t="shared" si="0"/>
         <v>45697</v>
       </c>
-      <c r="U8" s="51">
+      <c r="U8" s="50">
         <f t="shared" si="0"/>
         <v>45698</v>
       </c>
-      <c r="V8" s="51">
+      <c r="V8" s="50">
         <f t="shared" si="0"/>
         <v>45699</v>
       </c>
-      <c r="W8" s="51">
+      <c r="W8" s="50">
         <f t="shared" si="0"/>
         <v>45700</v>
       </c>
-      <c r="X8" s="51">
+      <c r="X8" s="50">
         <f t="shared" si="0"/>
         <v>45701</v>
       </c>
-      <c r="Y8" s="51">
+      <c r="Y8" s="50">
         <f t="shared" si="0"/>
         <v>45702</v>
       </c>
-      <c r="Z8" s="51">
+      <c r="Z8" s="50">
         <f t="shared" si="0"/>
         <v>45703</v>
       </c>
-      <c r="AA8" s="51">
+      <c r="AA8" s="50">
         <f t="shared" si="0"/>
         <v>45704</v>
       </c>
-      <c r="AB8" s="51">
+      <c r="AB8" s="50">
         <f t="shared" si="0"/>
         <v>45705</v>
       </c>
-      <c r="AC8" s="51">
+      <c r="AC8" s="50">
         <f t="shared" si="0"/>
         <v>45706</v>
       </c>
-      <c r="AD8" s="51">
+      <c r="AD8" s="50">
         <f t="shared" si="0"/>
         <v>45707</v>
       </c>
-      <c r="AE8" s="51">
+      <c r="AE8" s="50">
         <f t="shared" si="0"/>
         <v>45708</v>
       </c>
-      <c r="AF8" s="51">
+      <c r="AF8" s="50">
         <f t="shared" si="0"/>
         <v>45709</v>
       </c>
-      <c r="AG8" s="51">
+      <c r="AG8" s="50">
         <f t="shared" si="0"/>
         <v>45710</v>
       </c>
-      <c r="AH8" s="51">
+      <c r="AH8" s="50">
         <f t="shared" si="0"/>
         <v>45711</v>
       </c>
-      <c r="AI8" s="51">
+      <c r="AI8" s="50">
         <f t="shared" si="0"/>
         <v>45712</v>
       </c>
-      <c r="AJ8" s="51">
+      <c r="AJ8" s="50">
         <f t="shared" ref="AJ8:BO8" si="1">AI8+1</f>
         <v>45713</v>
       </c>
-      <c r="AK8" s="51">
+      <c r="AK8" s="50">
         <f t="shared" si="1"/>
         <v>45714</v>
       </c>
-      <c r="AL8" s="51">
+      <c r="AL8" s="50">
         <f t="shared" si="1"/>
         <v>45715</v>
       </c>
-      <c r="AM8" s="51">
+      <c r="AM8" s="50">
         <f t="shared" si="1"/>
         <v>45716</v>
       </c>
-      <c r="AN8" s="51">
+      <c r="AN8" s="50">
         <f t="shared" si="1"/>
         <v>45717</v>
       </c>
-      <c r="AO8" s="51">
+      <c r="AO8" s="50">
         <f t="shared" si="1"/>
         <v>45718</v>
       </c>
-      <c r="AP8" s="51">
+      <c r="AP8" s="50">
         <f t="shared" si="1"/>
         <v>45719</v>
       </c>
-      <c r="AQ8" s="51">
+      <c r="AQ8" s="50">
         <f t="shared" si="1"/>
         <v>45720</v>
       </c>
-      <c r="AR8" s="51">
+      <c r="AR8" s="50">
         <f t="shared" si="1"/>
         <v>45721</v>
       </c>
-      <c r="AS8" s="51">
+      <c r="AS8" s="50">
         <f t="shared" si="1"/>
         <v>45722</v>
       </c>
-      <c r="AT8" s="51">
+      <c r="AT8" s="50">
         <f t="shared" si="1"/>
         <v>45723</v>
       </c>
-      <c r="AU8" s="51">
+      <c r="AU8" s="50">
         <f t="shared" si="1"/>
         <v>45724</v>
       </c>
-      <c r="AV8" s="51">
+      <c r="AV8" s="50">
         <f t="shared" si="1"/>
         <v>45725</v>
       </c>
-      <c r="AW8" s="51">
+      <c r="AW8" s="50">
         <f t="shared" si="1"/>
         <v>45726</v>
       </c>
-      <c r="AX8" s="51">
+      <c r="AX8" s="50">
         <f t="shared" si="1"/>
         <v>45727</v>
       </c>
-      <c r="AY8" s="51">
+      <c r="AY8" s="50">
         <f t="shared" si="1"/>
         <v>45728</v>
       </c>
-      <c r="AZ8" s="51">
+      <c r="AZ8" s="50">
         <f t="shared" si="1"/>
         <v>45729</v>
       </c>
-      <c r="BA8" s="51">
+      <c r="BA8" s="50">
         <f t="shared" si="1"/>
         <v>45730</v>
       </c>
-      <c r="BB8" s="51">
+      <c r="BB8" s="50">
         <f t="shared" si="1"/>
         <v>45731</v>
       </c>
-      <c r="BC8" s="51">
+      <c r="BC8" s="50">
         <f t="shared" si="1"/>
         <v>45732</v>
       </c>
-      <c r="BD8" s="51">
+      <c r="BD8" s="50">
         <f t="shared" si="1"/>
         <v>45733</v>
       </c>
-      <c r="BE8" s="51">
+      <c r="BE8" s="50">
         <f t="shared" si="1"/>
         <v>45734</v>
       </c>
-      <c r="BF8" s="51">
+      <c r="BF8" s="50">
         <f t="shared" si="1"/>
         <v>45735</v>
       </c>
-      <c r="BG8" s="51">
+      <c r="BG8" s="50">
         <f t="shared" si="1"/>
         <v>45736</v>
       </c>
-      <c r="BH8" s="51">
+      <c r="BH8" s="50">
         <f t="shared" si="1"/>
         <v>45737</v>
       </c>
-      <c r="BI8" s="51">
+      <c r="BI8" s="50">
         <f t="shared" si="1"/>
         <v>45738</v>
       </c>
-      <c r="BJ8" s="51">
+      <c r="BJ8" s="50">
         <f t="shared" si="1"/>
         <v>45739</v>
       </c>
-      <c r="BK8" s="51">
+      <c r="BK8" s="50">
         <f t="shared" si="1"/>
         <v>45740</v>
       </c>
-      <c r="BL8" s="51">
+      <c r="BL8" s="50">
         <f t="shared" si="1"/>
         <v>45741</v>
       </c>
-      <c r="BM8" s="51">
+      <c r="BM8" s="50">
         <f t="shared" si="1"/>
         <v>45742</v>
       </c>
-      <c r="BN8" s="51">
+      <c r="BN8" s="50">
         <f t="shared" si="1"/>
         <v>45743</v>
       </c>
-      <c r="BO8" s="51">
+      <c r="BO8" s="50">
         <f t="shared" si="1"/>
         <v>45744</v>
       </c>
-      <c r="BP8" s="51">
+      <c r="BP8" s="50">
         <f t="shared" ref="BP8:CM8" si="2">BO8+1</f>
         <v>45745</v>
       </c>
-      <c r="BQ8" s="51">
+      <c r="BQ8" s="50">
         <f t="shared" si="2"/>
         <v>45746</v>
       </c>
-      <c r="BR8" s="51">
+      <c r="BR8" s="50">
         <f t="shared" si="2"/>
         <v>45747</v>
       </c>
-      <c r="BS8" s="51">
+      <c r="BS8" s="50">
         <f t="shared" si="2"/>
         <v>45748</v>
       </c>
-      <c r="BT8" s="51">
+      <c r="BT8" s="50">
         <f t="shared" si="2"/>
         <v>45749</v>
       </c>
-      <c r="BU8" s="51">
+      <c r="BU8" s="50">
         <f t="shared" si="2"/>
         <v>45750</v>
       </c>
-      <c r="BV8" s="51">
+      <c r="BV8" s="50">
         <f t="shared" si="2"/>
         <v>45751</v>
       </c>
-      <c r="BW8" s="51">
+      <c r="BW8" s="50">
         <f t="shared" si="2"/>
         <v>45752</v>
       </c>
-      <c r="BX8" s="51">
+      <c r="BX8" s="50">
         <f t="shared" si="2"/>
         <v>45753</v>
       </c>
-      <c r="BY8" s="51">
+      <c r="BY8" s="50">
         <f t="shared" si="2"/>
         <v>45754</v>
       </c>
-      <c r="BZ8" s="51">
+      <c r="BZ8" s="50">
         <f t="shared" si="2"/>
         <v>45755</v>
       </c>
-      <c r="CA8" s="51">
+      <c r="CA8" s="50">
         <f t="shared" si="2"/>
         <v>45756</v>
       </c>
-      <c r="CB8" s="51">
+      <c r="CB8" s="50">
         <f t="shared" si="2"/>
         <v>45757</v>
       </c>
-      <c r="CC8" s="51">
+      <c r="CC8" s="50">
         <f t="shared" si="2"/>
         <v>45758</v>
       </c>
-      <c r="CD8" s="51">
+      <c r="CD8" s="50">
         <f t="shared" si="2"/>
         <v>45759</v>
       </c>
-      <c r="CE8" s="51">
+      <c r="CE8" s="50">
         <f t="shared" si="2"/>
         <v>45760</v>
       </c>
-      <c r="CF8" s="51">
+      <c r="CF8" s="50">
         <f t="shared" si="2"/>
         <v>45761</v>
       </c>
-      <c r="CG8" s="51">
+      <c r="CG8" s="50">
         <f t="shared" si="2"/>
         <v>45762</v>
       </c>
-      <c r="CH8" s="51">
+      <c r="CH8" s="50">
         <f t="shared" si="2"/>
         <v>45763</v>
       </c>
-      <c r="CI8" s="51">
+      <c r="CI8" s="50">
         <f t="shared" si="2"/>
         <v>45764</v>
       </c>
-      <c r="CJ8" s="51">
+      <c r="CJ8" s="50">
         <f t="shared" si="2"/>
         <v>45765</v>
       </c>
-      <c r="CK8" s="51">
+      <c r="CK8" s="50">
         <f t="shared" si="2"/>
         <v>45766</v>
       </c>
-      <c r="CL8" s="51">
+      <c r="CL8" s="50">
         <f t="shared" si="2"/>
         <v>45767</v>
       </c>
-      <c r="CM8" s="51">
+      <c r="CM8" s="50">
         <f t="shared" si="2"/>
         <v>45768</v>
       </c>
-      <c r="CN8" s="51">
+      <c r="CN8" s="50">
         <f>CM8+1</f>
         <v>45769</v>
       </c>
-      <c r="CO8" s="51">
+      <c r="CO8" s="50">
         <f t="shared" ref="CO8:DP8" si="3">CN8+1</f>
         <v>45770</v>
       </c>
-      <c r="CP8" s="51">
+      <c r="CP8" s="50">
         <f t="shared" si="3"/>
         <v>45771</v>
       </c>
-      <c r="CQ8" s="51">
+      <c r="CQ8" s="50">
         <f t="shared" si="3"/>
         <v>45772</v>
       </c>
-      <c r="CR8" s="51">
+      <c r="CR8" s="50">
         <f t="shared" si="3"/>
         <v>45773</v>
       </c>
-      <c r="CS8" s="51">
+      <c r="CS8" s="50">
         <f t="shared" si="3"/>
         <v>45774</v>
       </c>
-      <c r="CT8" s="51">
+      <c r="CT8" s="50">
         <f t="shared" si="3"/>
         <v>45775</v>
       </c>
-      <c r="CU8" s="51">
+      <c r="CU8" s="50">
         <f t="shared" si="3"/>
         <v>45776</v>
       </c>
-      <c r="CV8" s="51">
+      <c r="CV8" s="50">
         <f t="shared" si="3"/>
         <v>45777</v>
       </c>
-      <c r="CW8" s="51">
+      <c r="CW8" s="50">
         <f t="shared" si="3"/>
         <v>45778</v>
       </c>
-      <c r="CX8" s="51">
+      <c r="CX8" s="50">
         <f t="shared" si="3"/>
         <v>45779</v>
       </c>
-      <c r="CY8" s="51">
+      <c r="CY8" s="50">
         <f t="shared" si="3"/>
         <v>45780</v>
       </c>
-      <c r="CZ8" s="51">
+      <c r="CZ8" s="50">
         <f t="shared" si="3"/>
         <v>45781</v>
       </c>
-      <c r="DA8" s="51">
+      <c r="DA8" s="50">
         <f t="shared" si="3"/>
         <v>45782</v>
       </c>
-      <c r="DB8" s="51">
+      <c r="DB8" s="50">
         <f t="shared" si="3"/>
         <v>45783</v>
       </c>
-      <c r="DC8" s="51">
+      <c r="DC8" s="50">
         <f t="shared" si="3"/>
         <v>45784</v>
       </c>
-      <c r="DD8" s="51">
+      <c r="DD8" s="50">
         <f t="shared" si="3"/>
         <v>45785</v>
       </c>
-      <c r="DE8" s="51">
+      <c r="DE8" s="50">
         <f t="shared" si="3"/>
         <v>45786</v>
       </c>
-      <c r="DF8" s="51">
+      <c r="DF8" s="50">
         <f t="shared" si="3"/>
         <v>45787</v>
       </c>
-      <c r="DG8" s="51">
+      <c r="DG8" s="50">
         <f t="shared" si="3"/>
         <v>45788</v>
       </c>
-      <c r="DH8" s="51">
+      <c r="DH8" s="50">
         <f t="shared" si="3"/>
         <v>45789</v>
       </c>
-      <c r="DI8" s="51">
+      <c r="DI8" s="50">
         <f t="shared" si="3"/>
         <v>45790</v>
       </c>
-      <c r="DJ8" s="51">
+      <c r="DJ8" s="50">
         <f t="shared" si="3"/>
         <v>45791</v>
       </c>
-      <c r="DK8" s="51">
+      <c r="DK8" s="50">
         <f t="shared" si="3"/>
         <v>45792</v>
       </c>
-      <c r="DL8" s="51">
+      <c r="DL8" s="50">
         <f t="shared" si="3"/>
         <v>45793</v>
       </c>
-      <c r="DM8" s="51">
+      <c r="DM8" s="50">
         <f t="shared" si="3"/>
         <v>45794</v>
       </c>
-      <c r="DN8" s="51">
+      <c r="DN8" s="50">
         <f t="shared" si="3"/>
         <v>45795</v>
       </c>
-      <c r="DO8" s="51">
+      <c r="DO8" s="50">
         <f t="shared" si="3"/>
         <v>45796</v>
       </c>
-      <c r="DP8" s="51">
+      <c r="DP8" s="50">
         <f t="shared" si="3"/>
         <v>45797</v>
       </c>
-      <c r="DQ8" s="51">
+      <c r="DQ8" s="50">
         <f t="shared" ref="DQ8:EI8" si="4">DP8+1</f>
         <v>45798</v>
       </c>
-      <c r="DR8" s="51">
+      <c r="DR8" s="50">
         <f t="shared" si="4"/>
         <v>45799</v>
       </c>
-      <c r="DS8" s="51">
+      <c r="DS8" s="50">
         <f t="shared" si="4"/>
         <v>45800</v>
       </c>
-      <c r="DT8" s="51">
+      <c r="DT8" s="50">
         <f t="shared" si="4"/>
         <v>45801</v>
       </c>
-      <c r="DU8" s="51">
+      <c r="DU8" s="50">
         <f t="shared" si="4"/>
         <v>45802</v>
       </c>
-      <c r="DV8" s="51">
+      <c r="DV8" s="50">
         <f t="shared" si="4"/>
         <v>45803</v>
       </c>
-      <c r="DW8" s="51">
+      <c r="DW8" s="50">
         <f t="shared" si="4"/>
         <v>45804</v>
       </c>
-      <c r="DX8" s="51">
+      <c r="DX8" s="50">
         <f t="shared" si="4"/>
         <v>45805</v>
       </c>
-      <c r="DY8" s="51">
+      <c r="DY8" s="50">
         <f t="shared" si="4"/>
         <v>45806</v>
       </c>
-      <c r="DZ8" s="51">
+      <c r="DZ8" s="50">
         <f t="shared" si="4"/>
         <v>45807</v>
       </c>
-      <c r="EA8" s="51">
+      <c r="EA8" s="50">
         <f t="shared" si="4"/>
         <v>45808</v>
       </c>
-      <c r="EB8" s="51">
+      <c r="EB8" s="50">
         <f t="shared" si="4"/>
         <v>45809</v>
       </c>
-      <c r="EC8" s="51">
+      <c r="EC8" s="50">
         <f t="shared" si="4"/>
         <v>45810</v>
       </c>
-      <c r="ED8" s="51">
+      <c r="ED8" s="50">
         <f t="shared" si="4"/>
         <v>45811</v>
       </c>
-      <c r="EE8" s="51">
+      <c r="EE8" s="50">
         <f t="shared" si="4"/>
         <v>45812</v>
       </c>
-      <c r="EF8" s="51">
+      <c r="EF8" s="50">
         <f t="shared" si="4"/>
         <v>45813</v>
       </c>
-      <c r="EG8" s="51">
+      <c r="EG8" s="50">
         <f t="shared" si="4"/>
         <v>45814</v>
       </c>
-      <c r="EH8" s="51">
+      <c r="EH8" s="50">
         <f t="shared" si="4"/>
         <v>45815</v>
       </c>
-      <c r="EI8" s="51">
+      <c r="EI8" s="50">
         <f t="shared" si="4"/>
         <v>45816</v>
       </c>
-      <c r="EJ8" s="51">
+      <c r="EJ8" s="50">
         <f t="shared" ref="EJ8:EX8" si="5">EI8+1</f>
         <v>45817</v>
       </c>
-      <c r="EK8" s="51">
+      <c r="EK8" s="50">
         <f t="shared" si="5"/>
         <v>45818</v>
       </c>
-      <c r="EL8" s="51">
+      <c r="EL8" s="50">
         <f t="shared" si="5"/>
         <v>45819</v>
       </c>
-      <c r="EM8" s="51">
+      <c r="EM8" s="50">
         <f t="shared" si="5"/>
         <v>45820</v>
       </c>
-      <c r="EN8" s="51">
+      <c r="EN8" s="50">
         <f t="shared" si="5"/>
         <v>45821</v>
       </c>
-      <c r="EO8" s="51">
+      <c r="EO8" s="50">
         <f t="shared" si="5"/>
         <v>45822</v>
       </c>
-      <c r="EP8" s="51">
+      <c r="EP8" s="50">
         <f t="shared" si="5"/>
         <v>45823</v>
       </c>
-      <c r="EQ8" s="51">
+      <c r="EQ8" s="50">
         <f t="shared" si="5"/>
         <v>45824</v>
       </c>
-      <c r="ER8" s="51">
+      <c r="ER8" s="50">
         <f t="shared" si="5"/>
         <v>45825</v>
       </c>
-      <c r="ES8" s="51">
+      <c r="ES8" s="50">
         <f t="shared" si="5"/>
         <v>45826</v>
       </c>
-      <c r="ET8" s="51">
+      <c r="ET8" s="50">
         <f t="shared" si="5"/>
         <v>45827</v>
       </c>
-      <c r="EU8" s="51">
+      <c r="EU8" s="50">
         <f t="shared" si="5"/>
         <v>45828</v>
       </c>
-      <c r="EV8" s="51">
+      <c r="EV8" s="50">
         <f t="shared" si="5"/>
         <v>45829</v>
       </c>
-      <c r="EW8" s="51">
+      <c r="EW8" s="50">
         <f t="shared" si="5"/>
         <v>45830</v>
       </c>
-      <c r="EX8" s="51">
+      <c r="EX8" s="50">
         <f t="shared" si="5"/>
         <v>45831</v>
       </c>
-      <c r="EY8" s="65" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:156" s="46" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="44" t="s">
+      <c r="EY8" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="45" t="s">
+    </row>
+    <row r="9" spans="1:156" s="45" customFormat="1" ht="41.45">
+      <c r="A9" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="J9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="K9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="L9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="M9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="N9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="R9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="S9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="T9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="U9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="V9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="W9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="X9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AQ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AS9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AT9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AV9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AY9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AZ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BA9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BB9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BC9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BD9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BE9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BF9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BG9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BH9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BI9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BJ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BK9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BL9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BM9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BN9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BO9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BP9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BQ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BR9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BS9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BT9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BU9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BV9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BW9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BX9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BY9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="BZ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CA9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CB9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CC9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CD9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CE9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CF9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CG9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CH9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CI9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CJ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CK9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CL9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CM9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CN9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CO9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CP9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CQ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CR9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CS9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CT9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CU9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CV9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CW9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CX9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CY9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CZ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DA9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DB9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DC9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DD9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DE9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DF9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DG9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DH9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DI9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DJ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DK9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DL9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DM9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DN9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DO9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DP9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DQ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DR9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DS9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DT9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DU9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DV9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DW9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DX9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DY9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="DZ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EA9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EB9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EC9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="ED9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EE9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EF9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EG9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EH9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EI9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EJ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EK9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EL9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EM9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EN9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EO9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EP9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EQ9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="ER9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="ES9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="ET9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EU9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EV9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EW9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EX9" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="EY9" s="71" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54" t="s">
+      <c r="B9" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="56">
+      <c r="C9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="O9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="T9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="U9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="V9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="W9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AQ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AS9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AU9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AV9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AY9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BA9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BB9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BC9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BF9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BG9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BI9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BK9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BL9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BM9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BN9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BO9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BQ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BR9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BS9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BT9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BU9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BV9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BW9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BX9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BY9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="BZ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CA9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CB9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CC9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CD9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CE9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CF9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CG9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CH9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CI9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CJ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CK9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CL9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CM9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CN9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CO9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CP9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CQ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CR9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CS9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CT9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CU9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CV9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CW9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CX9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CY9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="CZ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DA9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DB9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DC9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DD9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DE9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DF9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DG9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DH9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DI9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DJ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DK9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DL9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DM9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DN9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DO9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DP9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DQ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DR9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DS9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DT9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DU9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DV9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DW9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DX9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DY9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="DZ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EA9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EB9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EC9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="ED9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EE9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EF9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EG9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EH9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EI9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EJ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EK9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EL9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EM9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EN9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EO9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EP9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EQ9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="ER9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="ES9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="ET9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EU9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EV9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EW9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EX9" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="EY9" s="67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:156" ht="15.75" customHeight="1">
+      <c r="A10" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E10" s="60"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="60"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="12"/>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="12"/>
-      <c r="AE10" s="12"/>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="12"/>
-      <c r="AJ10" s="12"/>
-      <c r="AK10" s="12"/>
-      <c r="AL10" s="12"/>
-      <c r="AM10" s="12"/>
-      <c r="AN10" s="12"/>
-      <c r="AO10" s="12"/>
-      <c r="AP10" s="12"/>
-      <c r="AQ10" s="12"/>
-      <c r="AR10" s="12"/>
-      <c r="AS10" s="12"/>
-      <c r="AT10" s="12"/>
-      <c r="AU10" s="12"/>
-      <c r="AV10" s="12"/>
-      <c r="AW10" s="12"/>
-      <c r="AX10" s="12"/>
-      <c r="AY10" s="12"/>
-      <c r="AZ10" s="12"/>
-      <c r="BA10" s="12"/>
-      <c r="BB10" s="12"/>
-      <c r="BC10" s="12"/>
-      <c r="BD10" s="12"/>
-      <c r="BE10" s="12"/>
-      <c r="BF10" s="12"/>
-      <c r="BG10" s="12"/>
-      <c r="BH10" s="12"/>
-      <c r="BI10" s="12"/>
-      <c r="BJ10" s="12"/>
-      <c r="BK10" s="12"/>
-      <c r="BL10" s="12"/>
-      <c r="BM10" s="12"/>
-      <c r="BN10" s="12"/>
-      <c r="BO10" s="12"/>
-      <c r="BP10" s="12"/>
-      <c r="BQ10" s="12"/>
-      <c r="BR10" s="12"/>
-      <c r="BS10" s="12"/>
-      <c r="BT10" s="12"/>
-      <c r="BU10" s="12"/>
-      <c r="BV10" s="12"/>
-      <c r="BW10" s="12"/>
-      <c r="BX10" s="12"/>
-      <c r="BY10" s="12"/>
-      <c r="BZ10" s="12"/>
-      <c r="CA10" s="12"/>
-      <c r="CB10" s="12"/>
-      <c r="CC10" s="12"/>
-      <c r="CD10" s="12"/>
-      <c r="CE10" s="12"/>
-      <c r="CF10" s="12"/>
-      <c r="CG10" s="12"/>
-      <c r="CH10" s="12"/>
-      <c r="CI10" s="12"/>
-      <c r="CJ10" s="12"/>
-      <c r="CK10" s="12"/>
-      <c r="CL10" s="12"/>
-      <c r="CM10" s="12"/>
-      <c r="CN10" s="12"/>
-      <c r="CO10" s="12"/>
-      <c r="CP10" s="12"/>
-      <c r="CQ10" s="12"/>
-      <c r="CR10" s="12"/>
-      <c r="CS10" s="12"/>
-      <c r="CT10" s="12"/>
-      <c r="CU10" s="12"/>
-      <c r="CV10" s="12"/>
-      <c r="CW10" s="12"/>
-      <c r="CX10" s="12"/>
-      <c r="CY10" s="12"/>
-      <c r="CZ10" s="12"/>
-      <c r="DA10" s="12"/>
-      <c r="DB10" s="12"/>
-      <c r="DC10" s="12"/>
-      <c r="DD10" s="12"/>
-      <c r="DE10" s="12"/>
-      <c r="DF10" s="12"/>
-      <c r="DG10" s="12"/>
-      <c r="DH10" s="12"/>
-      <c r="DI10" s="12"/>
-      <c r="DJ10" s="12"/>
-      <c r="DK10" s="12"/>
-      <c r="DL10" s="12"/>
-      <c r="DM10" s="12"/>
-      <c r="DN10" s="12"/>
-      <c r="DO10" s="12"/>
-      <c r="DP10" s="12"/>
-      <c r="DQ10" s="12"/>
-      <c r="DR10" s="12"/>
-      <c r="DS10" s="12"/>
-      <c r="DT10" s="12"/>
-      <c r="DU10" s="12"/>
-      <c r="DV10" s="12"/>
-      <c r="DW10" s="12"/>
-      <c r="DX10" s="12"/>
-      <c r="DY10" s="12"/>
-      <c r="DZ10" s="12"/>
-      <c r="EA10" s="12"/>
-      <c r="EB10" s="12"/>
-      <c r="EC10" s="12"/>
-      <c r="ED10" s="12"/>
-      <c r="EE10" s="12"/>
-      <c r="EF10" s="12"/>
-      <c r="EG10" s="12"/>
-      <c r="EH10" s="12"/>
-      <c r="EI10" s="12"/>
-      <c r="EJ10" s="12"/>
-      <c r="EK10" s="12"/>
-      <c r="EL10" s="12"/>
-      <c r="EM10" s="12"/>
-      <c r="EN10" s="12"/>
-      <c r="EO10" s="12"/>
-      <c r="EP10" s="12"/>
-      <c r="EQ10" s="12"/>
-      <c r="ER10" s="12"/>
-      <c r="ES10" s="12"/>
-      <c r="ET10" s="12"/>
-      <c r="EU10" s="12"/>
-      <c r="EV10" s="12"/>
-      <c r="EW10" s="12"/>
-      <c r="EX10" s="12"/>
-      <c r="EY10" s="72">
+      <c r="E10" s="56"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="11"/>
+      <c r="AB10" s="11"/>
+      <c r="AC10" s="11"/>
+      <c r="AD10" s="11"/>
+      <c r="AE10" s="11"/>
+      <c r="AF10" s="11"/>
+      <c r="AG10" s="11"/>
+      <c r="AH10" s="11"/>
+      <c r="AI10" s="11"/>
+      <c r="AJ10" s="11"/>
+      <c r="AK10" s="11"/>
+      <c r="AL10" s="11"/>
+      <c r="AM10" s="11"/>
+      <c r="AN10" s="11"/>
+      <c r="AO10" s="11"/>
+      <c r="AP10" s="11"/>
+      <c r="AQ10" s="11"/>
+      <c r="AR10" s="11"/>
+      <c r="AS10" s="11"/>
+      <c r="AT10" s="11"/>
+      <c r="AU10" s="11"/>
+      <c r="AV10" s="11"/>
+      <c r="AW10" s="11"/>
+      <c r="AX10" s="11"/>
+      <c r="AY10" s="11"/>
+      <c r="AZ10" s="11"/>
+      <c r="BA10" s="11"/>
+      <c r="BB10" s="11"/>
+      <c r="BC10" s="11"/>
+      <c r="BD10" s="11"/>
+      <c r="BE10" s="11"/>
+      <c r="BF10" s="11"/>
+      <c r="BG10" s="11"/>
+      <c r="BH10" s="11"/>
+      <c r="BI10" s="11"/>
+      <c r="BJ10" s="11"/>
+      <c r="BK10" s="11"/>
+      <c r="BL10" s="11"/>
+      <c r="BM10" s="11"/>
+      <c r="BN10" s="11"/>
+      <c r="BO10" s="11"/>
+      <c r="BP10" s="11"/>
+      <c r="BQ10" s="11"/>
+      <c r="BR10" s="11"/>
+      <c r="BS10" s="11"/>
+      <c r="BT10" s="11"/>
+      <c r="BU10" s="11"/>
+      <c r="BV10" s="11"/>
+      <c r="BW10" s="11"/>
+      <c r="BX10" s="11"/>
+      <c r="BY10" s="11"/>
+      <c r="BZ10" s="11"/>
+      <c r="CA10" s="11"/>
+      <c r="CB10" s="11"/>
+      <c r="CC10" s="11"/>
+      <c r="CD10" s="11"/>
+      <c r="CE10" s="11"/>
+      <c r="CF10" s="11"/>
+      <c r="CG10" s="11"/>
+      <c r="CH10" s="11"/>
+      <c r="CI10" s="11"/>
+      <c r="CJ10" s="11"/>
+      <c r="CK10" s="11"/>
+      <c r="CL10" s="11"/>
+      <c r="CM10" s="11"/>
+      <c r="CN10" s="11"/>
+      <c r="CO10" s="11"/>
+      <c r="CP10" s="11"/>
+      <c r="CQ10" s="11"/>
+      <c r="CR10" s="11"/>
+      <c r="CS10" s="11"/>
+      <c r="CT10" s="11"/>
+      <c r="CU10" s="11"/>
+      <c r="CV10" s="11"/>
+      <c r="CW10" s="11"/>
+      <c r="CX10" s="11"/>
+      <c r="CY10" s="11"/>
+      <c r="CZ10" s="11"/>
+      <c r="DA10" s="11"/>
+      <c r="DB10" s="11"/>
+      <c r="DC10" s="11"/>
+      <c r="DD10" s="11"/>
+      <c r="DE10" s="11"/>
+      <c r="DF10" s="11"/>
+      <c r="DG10" s="11"/>
+      <c r="DH10" s="11"/>
+      <c r="DI10" s="11"/>
+      <c r="DJ10" s="11"/>
+      <c r="DK10" s="11"/>
+      <c r="DL10" s="11"/>
+      <c r="DM10" s="11"/>
+      <c r="DN10" s="11"/>
+      <c r="DO10" s="11"/>
+      <c r="DP10" s="11"/>
+      <c r="DQ10" s="11"/>
+      <c r="DR10" s="11"/>
+      <c r="DS10" s="11"/>
+      <c r="DT10" s="11"/>
+      <c r="DU10" s="11"/>
+      <c r="DV10" s="11"/>
+      <c r="DW10" s="11"/>
+      <c r="DX10" s="11"/>
+      <c r="DY10" s="11"/>
+      <c r="DZ10" s="11"/>
+      <c r="EA10" s="11"/>
+      <c r="EB10" s="11"/>
+      <c r="EC10" s="11"/>
+      <c r="ED10" s="11"/>
+      <c r="EE10" s="11"/>
+      <c r="EF10" s="11"/>
+      <c r="EG10" s="11"/>
+      <c r="EH10" s="11"/>
+      <c r="EI10" s="11"/>
+      <c r="EJ10" s="11"/>
+      <c r="EK10" s="11"/>
+      <c r="EL10" s="11"/>
+      <c r="EM10" s="11"/>
+      <c r="EN10" s="11"/>
+      <c r="EO10" s="11"/>
+      <c r="EP10" s="11"/>
+      <c r="EQ10" s="11"/>
+      <c r="ER10" s="11"/>
+      <c r="ES10" s="11"/>
+      <c r="ET10" s="11"/>
+      <c r="EU10" s="11"/>
+      <c r="EV10" s="11"/>
+      <c r="EW10" s="11"/>
+      <c r="EX10" s="11"/>
+      <c r="EY10" s="68">
         <f>SUM(C10:EX10)</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="11" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
-      <c r="B11" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="56">
-        <v>0.125</v>
-      </c>
-      <c r="H11" s="56">
-        <v>0.125</v>
-      </c>
-      <c r="I11" s="56">
-        <v>0.125</v>
-      </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="60"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="12"/>
-      <c r="AB11" s="12"/>
-      <c r="AC11" s="12"/>
-      <c r="AD11" s="12"/>
-      <c r="AE11" s="12"/>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AH11" s="12"/>
-      <c r="AI11" s="12"/>
-      <c r="AJ11" s="12"/>
-      <c r="AK11" s="12"/>
-      <c r="AL11" s="12"/>
-      <c r="AM11" s="12"/>
-      <c r="AN11" s="12"/>
-      <c r="AO11" s="12"/>
-      <c r="AP11" s="12"/>
-      <c r="AQ11" s="12"/>
-      <c r="AR11" s="12"/>
-      <c r="AS11" s="12"/>
-      <c r="AT11" s="12"/>
-      <c r="AU11" s="12"/>
-      <c r="AV11" s="12"/>
-      <c r="AW11" s="12"/>
-      <c r="AX11" s="12"/>
-      <c r="AY11" s="12"/>
-      <c r="AZ11" s="12"/>
-      <c r="BA11" s="12"/>
-      <c r="BB11" s="12"/>
-      <c r="BC11" s="12"/>
-      <c r="BD11" s="12"/>
-      <c r="BE11" s="12"/>
-      <c r="BF11" s="12"/>
-      <c r="BG11" s="12"/>
-      <c r="BH11" s="12"/>
-      <c r="BI11" s="12"/>
-      <c r="BJ11" s="12"/>
-      <c r="BK11" s="12"/>
-      <c r="BL11" s="12"/>
-      <c r="BM11" s="12"/>
-      <c r="BN11" s="12"/>
-      <c r="BO11" s="12"/>
-      <c r="BP11" s="12"/>
-      <c r="BQ11" s="12"/>
-      <c r="BR11" s="12"/>
-      <c r="BS11" s="12"/>
-      <c r="BT11" s="12"/>
-      <c r="BU11" s="12"/>
-      <c r="BV11" s="12"/>
-      <c r="BW11" s="12"/>
-      <c r="BX11" s="12"/>
-      <c r="BY11" s="12"/>
-      <c r="BZ11" s="12"/>
-      <c r="CA11" s="12"/>
-      <c r="CB11" s="12"/>
-      <c r="CC11" s="12"/>
-      <c r="CD11" s="12"/>
-      <c r="CE11" s="12"/>
-      <c r="CF11" s="12"/>
-      <c r="CG11" s="12"/>
-      <c r="CH11" s="12"/>
-      <c r="CI11" s="12"/>
-      <c r="CJ11" s="12"/>
-      <c r="CK11" s="12"/>
-      <c r="CL11" s="12"/>
-      <c r="CM11" s="12"/>
-      <c r="CN11" s="12"/>
-      <c r="CO11" s="12"/>
-      <c r="CP11" s="12"/>
-      <c r="CQ11" s="12"/>
-      <c r="CR11" s="12"/>
-      <c r="CS11" s="12"/>
-      <c r="CT11" s="12"/>
-      <c r="CU11" s="12"/>
-      <c r="CV11" s="12"/>
-      <c r="CW11" s="12"/>
-      <c r="CX11" s="12"/>
-      <c r="CY11" s="12"/>
-      <c r="CZ11" s="12"/>
-      <c r="DA11" s="12"/>
-      <c r="DB11" s="12"/>
-      <c r="DC11" s="12"/>
-      <c r="DD11" s="12"/>
-      <c r="DE11" s="12"/>
-      <c r="DF11" s="12"/>
-      <c r="DG11" s="12"/>
-      <c r="DH11" s="12"/>
-      <c r="DI11" s="12"/>
-      <c r="DJ11" s="12"/>
-      <c r="DK11" s="12"/>
-      <c r="DL11" s="12"/>
-      <c r="DM11" s="12"/>
-      <c r="DN11" s="12"/>
-      <c r="DO11" s="12"/>
-      <c r="DP11" s="12"/>
-      <c r="DQ11" s="12"/>
-      <c r="DR11" s="12"/>
-      <c r="DS11" s="12"/>
-      <c r="DT11" s="12"/>
-      <c r="DU11" s="12"/>
-      <c r="DV11" s="12"/>
-      <c r="DW11" s="12"/>
-      <c r="DX11" s="12"/>
-      <c r="DY11" s="12"/>
-      <c r="DZ11" s="12"/>
-      <c r="EA11" s="12"/>
-      <c r="EB11" s="12"/>
-      <c r="EC11" s="12"/>
-      <c r="ED11" s="12"/>
-      <c r="EE11" s="12"/>
-      <c r="EF11" s="12"/>
-      <c r="EG11" s="12"/>
-      <c r="EH11" s="12"/>
-      <c r="EI11" s="12"/>
-      <c r="EJ11" s="12"/>
-      <c r="EK11" s="12"/>
-      <c r="EL11" s="12"/>
-      <c r="EM11" s="12"/>
-      <c r="EN11" s="12"/>
-      <c r="EO11" s="12"/>
-      <c r="EP11" s="12"/>
-      <c r="EQ11" s="12"/>
-      <c r="ER11" s="12"/>
-      <c r="ES11" s="12"/>
-      <c r="ET11" s="12"/>
-      <c r="EU11" s="12"/>
-      <c r="EV11" s="12"/>
-      <c r="EW11" s="12"/>
-      <c r="EX11" s="12"/>
-      <c r="EY11" s="72">
+    <row r="11" spans="1:156" ht="15.6">
+      <c r="A11" s="71"/>
+      <c r="B11" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="56"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="52">
+        <v>0.125</v>
+      </c>
+      <c r="H11" s="52">
+        <v>0.125</v>
+      </c>
+      <c r="I11" s="52">
+        <v>0.125</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="11"/>
+      <c r="AF11" s="11"/>
+      <c r="AG11" s="11"/>
+      <c r="AH11" s="11"/>
+      <c r="AI11" s="11"/>
+      <c r="AJ11" s="11"/>
+      <c r="AK11" s="11"/>
+      <c r="AL11" s="11"/>
+      <c r="AM11" s="11"/>
+      <c r="AN11" s="11"/>
+      <c r="AO11" s="11"/>
+      <c r="AP11" s="11"/>
+      <c r="AQ11" s="11"/>
+      <c r="AR11" s="11"/>
+      <c r="AS11" s="11"/>
+      <c r="AT11" s="11"/>
+      <c r="AU11" s="11"/>
+      <c r="AV11" s="11"/>
+      <c r="AW11" s="11"/>
+      <c r="AX11" s="11"/>
+      <c r="AY11" s="11"/>
+      <c r="AZ11" s="11"/>
+      <c r="BA11" s="11"/>
+      <c r="BB11" s="11"/>
+      <c r="BC11" s="11"/>
+      <c r="BD11" s="11"/>
+      <c r="BE11" s="11"/>
+      <c r="BF11" s="11"/>
+      <c r="BG11" s="11"/>
+      <c r="BH11" s="11"/>
+      <c r="BI11" s="11"/>
+      <c r="BJ11" s="11"/>
+      <c r="BK11" s="11"/>
+      <c r="BL11" s="11"/>
+      <c r="BM11" s="11"/>
+      <c r="BN11" s="11"/>
+      <c r="BO11" s="11"/>
+      <c r="BP11" s="11"/>
+      <c r="BQ11" s="11"/>
+      <c r="BR11" s="11"/>
+      <c r="BS11" s="11"/>
+      <c r="BT11" s="11"/>
+      <c r="BU11" s="11"/>
+      <c r="BV11" s="11"/>
+      <c r="BW11" s="11"/>
+      <c r="BX11" s="11"/>
+      <c r="BY11" s="11"/>
+      <c r="BZ11" s="11"/>
+      <c r="CA11" s="11"/>
+      <c r="CB11" s="11"/>
+      <c r="CC11" s="11"/>
+      <c r="CD11" s="11"/>
+      <c r="CE11" s="11"/>
+      <c r="CF11" s="11"/>
+      <c r="CG11" s="11"/>
+      <c r="CH11" s="11"/>
+      <c r="CI11" s="11"/>
+      <c r="CJ11" s="11"/>
+      <c r="CK11" s="11"/>
+      <c r="CL11" s="11"/>
+      <c r="CM11" s="11"/>
+      <c r="CN11" s="11"/>
+      <c r="CO11" s="11"/>
+      <c r="CP11" s="11"/>
+      <c r="CQ11" s="11"/>
+      <c r="CR11" s="11"/>
+      <c r="CS11" s="11"/>
+      <c r="CT11" s="11"/>
+      <c r="CU11" s="11"/>
+      <c r="CV11" s="11"/>
+      <c r="CW11" s="11"/>
+      <c r="CX11" s="11"/>
+      <c r="CY11" s="11"/>
+      <c r="CZ11" s="11"/>
+      <c r="DA11" s="11"/>
+      <c r="DB11" s="11"/>
+      <c r="DC11" s="11"/>
+      <c r="DD11" s="11"/>
+      <c r="DE11" s="11"/>
+      <c r="DF11" s="11"/>
+      <c r="DG11" s="11"/>
+      <c r="DH11" s="11"/>
+      <c r="DI11" s="11"/>
+      <c r="DJ11" s="11"/>
+      <c r="DK11" s="11"/>
+      <c r="DL11" s="11"/>
+      <c r="DM11" s="11"/>
+      <c r="DN11" s="11"/>
+      <c r="DO11" s="11"/>
+      <c r="DP11" s="11"/>
+      <c r="DQ11" s="11"/>
+      <c r="DR11" s="11"/>
+      <c r="DS11" s="11"/>
+      <c r="DT11" s="11"/>
+      <c r="DU11" s="11"/>
+      <c r="DV11" s="11"/>
+      <c r="DW11" s="11"/>
+      <c r="DX11" s="11"/>
+      <c r="DY11" s="11"/>
+      <c r="DZ11" s="11"/>
+      <c r="EA11" s="11"/>
+      <c r="EB11" s="11"/>
+      <c r="EC11" s="11"/>
+      <c r="ED11" s="11"/>
+      <c r="EE11" s="11"/>
+      <c r="EF11" s="11"/>
+      <c r="EG11" s="11"/>
+      <c r="EH11" s="11"/>
+      <c r="EI11" s="11"/>
+      <c r="EJ11" s="11"/>
+      <c r="EK11" s="11"/>
+      <c r="EL11" s="11"/>
+      <c r="EM11" s="11"/>
+      <c r="EN11" s="11"/>
+      <c r="EO11" s="11"/>
+      <c r="EP11" s="11"/>
+      <c r="EQ11" s="11"/>
+      <c r="ER11" s="11"/>
+      <c r="ES11" s="11"/>
+      <c r="ET11" s="11"/>
+      <c r="EU11" s="11"/>
+      <c r="EV11" s="11"/>
+      <c r="EW11" s="11"/>
+      <c r="EX11" s="11"/>
+      <c r="EY11" s="68">
         <f t="shared" ref="EY11:EY13" si="6">SUM(C11:EX11)</f>
         <v>0.375</v>
       </c>
     </row>
-    <row r="12" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="56">
+    <row r="12" spans="1:156" ht="15.6">
+      <c r="A12" s="71"/>
+      <c r="B12" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="K12" s="56">
+      <c r="K12" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="L12" s="62"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="60"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
-      <c r="AB12" s="12"/>
-      <c r="AC12" s="12"/>
-      <c r="AD12" s="12"/>
-      <c r="AE12" s="12"/>
-      <c r="AF12" s="12"/>
-      <c r="AG12" s="12"/>
-      <c r="AH12" s="12"/>
-      <c r="AI12" s="12"/>
-      <c r="AJ12" s="12"/>
-      <c r="AK12" s="12"/>
-      <c r="AL12" s="12"/>
-      <c r="AM12" s="12"/>
-      <c r="AN12" s="12"/>
-      <c r="AO12" s="12"/>
-      <c r="AP12" s="12"/>
-      <c r="AQ12" s="12"/>
-      <c r="AR12" s="12"/>
-      <c r="AS12" s="12"/>
-      <c r="AT12" s="12"/>
-      <c r="AU12" s="12"/>
-      <c r="AV12" s="12"/>
-      <c r="AW12" s="12"/>
-      <c r="AX12" s="12"/>
-      <c r="AY12" s="12"/>
-      <c r="AZ12" s="12"/>
-      <c r="BA12" s="12"/>
-      <c r="BB12" s="12"/>
-      <c r="BC12" s="12"/>
-      <c r="BD12" s="12"/>
-      <c r="BE12" s="12"/>
-      <c r="BF12" s="12"/>
-      <c r="BG12" s="12"/>
-      <c r="BH12" s="12"/>
-      <c r="BI12" s="12"/>
-      <c r="BJ12" s="12"/>
-      <c r="BK12" s="12"/>
-      <c r="BL12" s="12"/>
-      <c r="BM12" s="12"/>
-      <c r="BN12" s="12"/>
-      <c r="BO12" s="12"/>
-      <c r="BP12" s="12"/>
-      <c r="BQ12" s="12"/>
-      <c r="BR12" s="12"/>
-      <c r="BS12" s="12"/>
-      <c r="BT12" s="12"/>
-      <c r="BU12" s="12"/>
-      <c r="BV12" s="12"/>
-      <c r="BW12" s="12"/>
-      <c r="BX12" s="12"/>
-      <c r="BY12" s="12"/>
-      <c r="BZ12" s="12"/>
-      <c r="CA12" s="12"/>
-      <c r="CB12" s="12"/>
-      <c r="CC12" s="12"/>
-      <c r="CD12" s="12"/>
-      <c r="CE12" s="12"/>
-      <c r="CF12" s="12"/>
-      <c r="CG12" s="12"/>
-      <c r="CH12" s="12"/>
-      <c r="CI12" s="12"/>
-      <c r="CJ12" s="12"/>
-      <c r="CK12" s="12"/>
-      <c r="CL12" s="12"/>
-      <c r="CM12" s="12"/>
-      <c r="CN12" s="12"/>
-      <c r="CO12" s="12"/>
-      <c r="CP12" s="12"/>
-      <c r="CQ12" s="12"/>
-      <c r="CR12" s="12"/>
-      <c r="CS12" s="12"/>
-      <c r="CT12" s="12"/>
-      <c r="CU12" s="12"/>
-      <c r="CV12" s="12"/>
-      <c r="CW12" s="12"/>
-      <c r="CX12" s="12"/>
-      <c r="CY12" s="12"/>
-      <c r="CZ12" s="12"/>
-      <c r="DA12" s="12"/>
-      <c r="DB12" s="12"/>
-      <c r="DC12" s="12"/>
-      <c r="DD12" s="12"/>
-      <c r="DE12" s="12"/>
-      <c r="DF12" s="12"/>
-      <c r="DG12" s="12"/>
-      <c r="DH12" s="12"/>
-      <c r="DI12" s="12"/>
-      <c r="DJ12" s="12"/>
-      <c r="DK12" s="12"/>
-      <c r="DL12" s="12"/>
-      <c r="DM12" s="12"/>
-      <c r="DN12" s="12"/>
-      <c r="DO12" s="12"/>
-      <c r="DP12" s="12"/>
-      <c r="DQ12" s="12"/>
-      <c r="DR12" s="12"/>
-      <c r="DS12" s="12"/>
-      <c r="DT12" s="12"/>
-      <c r="DU12" s="12"/>
-      <c r="DV12" s="12"/>
-      <c r="DW12" s="12"/>
-      <c r="DX12" s="12"/>
-      <c r="DY12" s="12"/>
-      <c r="DZ12" s="12"/>
-      <c r="EA12" s="12"/>
-      <c r="EB12" s="12"/>
-      <c r="EC12" s="12"/>
-      <c r="ED12" s="12"/>
-      <c r="EE12" s="12"/>
-      <c r="EF12" s="12"/>
-      <c r="EG12" s="12"/>
-      <c r="EH12" s="12"/>
-      <c r="EI12" s="12"/>
-      <c r="EJ12" s="12"/>
-      <c r="EK12" s="12"/>
-      <c r="EL12" s="12"/>
-      <c r="EM12" s="12"/>
-      <c r="EN12" s="12"/>
-      <c r="EO12" s="12"/>
-      <c r="EP12" s="12"/>
-      <c r="EQ12" s="12"/>
-      <c r="ER12" s="12"/>
-      <c r="ES12" s="12"/>
-      <c r="ET12" s="12"/>
-      <c r="EU12" s="12"/>
-      <c r="EV12" s="12"/>
-      <c r="EW12" s="12"/>
-      <c r="EX12" s="12"/>
-      <c r="EY12" s="72">
+      <c r="L12" s="58"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="11"/>
+      <c r="AB12" s="11"/>
+      <c r="AC12" s="11"/>
+      <c r="AD12" s="11"/>
+      <c r="AE12" s="11"/>
+      <c r="AF12" s="11"/>
+      <c r="AG12" s="11"/>
+      <c r="AH12" s="11"/>
+      <c r="AI12" s="11"/>
+      <c r="AJ12" s="11"/>
+      <c r="AK12" s="11"/>
+      <c r="AL12" s="11"/>
+      <c r="AM12" s="11"/>
+      <c r="AN12" s="11"/>
+      <c r="AO12" s="11"/>
+      <c r="AP12" s="11"/>
+      <c r="AQ12" s="11"/>
+      <c r="AR12" s="11"/>
+      <c r="AS12" s="11"/>
+      <c r="AT12" s="11"/>
+      <c r="AU12" s="11"/>
+      <c r="AV12" s="11"/>
+      <c r="AW12" s="11"/>
+      <c r="AX12" s="11"/>
+      <c r="AY12" s="11"/>
+      <c r="AZ12" s="11"/>
+      <c r="BA12" s="11"/>
+      <c r="BB12" s="11"/>
+      <c r="BC12" s="11"/>
+      <c r="BD12" s="11"/>
+      <c r="BE12" s="11"/>
+      <c r="BF12" s="11"/>
+      <c r="BG12" s="11"/>
+      <c r="BH12" s="11"/>
+      <c r="BI12" s="11"/>
+      <c r="BJ12" s="11"/>
+      <c r="BK12" s="11"/>
+      <c r="BL12" s="11"/>
+      <c r="BM12" s="11"/>
+      <c r="BN12" s="11"/>
+      <c r="BO12" s="11"/>
+      <c r="BP12" s="11"/>
+      <c r="BQ12" s="11"/>
+      <c r="BR12" s="11"/>
+      <c r="BS12" s="11"/>
+      <c r="BT12" s="11"/>
+      <c r="BU12" s="11"/>
+      <c r="BV12" s="11"/>
+      <c r="BW12" s="11"/>
+      <c r="BX12" s="11"/>
+      <c r="BY12" s="11"/>
+      <c r="BZ12" s="11"/>
+      <c r="CA12" s="11"/>
+      <c r="CB12" s="11"/>
+      <c r="CC12" s="11"/>
+      <c r="CD12" s="11"/>
+      <c r="CE12" s="11"/>
+      <c r="CF12" s="11"/>
+      <c r="CG12" s="11"/>
+      <c r="CH12" s="11"/>
+      <c r="CI12" s="11"/>
+      <c r="CJ12" s="11"/>
+      <c r="CK12" s="11"/>
+      <c r="CL12" s="11"/>
+      <c r="CM12" s="11"/>
+      <c r="CN12" s="11"/>
+      <c r="CO12" s="11"/>
+      <c r="CP12" s="11"/>
+      <c r="CQ12" s="11"/>
+      <c r="CR12" s="11"/>
+      <c r="CS12" s="11"/>
+      <c r="CT12" s="11"/>
+      <c r="CU12" s="11"/>
+      <c r="CV12" s="11"/>
+      <c r="CW12" s="11"/>
+      <c r="CX12" s="11"/>
+      <c r="CY12" s="11"/>
+      <c r="CZ12" s="11"/>
+      <c r="DA12" s="11"/>
+      <c r="DB12" s="11"/>
+      <c r="DC12" s="11"/>
+      <c r="DD12" s="11"/>
+      <c r="DE12" s="11"/>
+      <c r="DF12" s="11"/>
+      <c r="DG12" s="11"/>
+      <c r="DH12" s="11"/>
+      <c r="DI12" s="11"/>
+      <c r="DJ12" s="11"/>
+      <c r="DK12" s="11"/>
+      <c r="DL12" s="11"/>
+      <c r="DM12" s="11"/>
+      <c r="DN12" s="11"/>
+      <c r="DO12" s="11"/>
+      <c r="DP12" s="11"/>
+      <c r="DQ12" s="11"/>
+      <c r="DR12" s="11"/>
+      <c r="DS12" s="11"/>
+      <c r="DT12" s="11"/>
+      <c r="DU12" s="11"/>
+      <c r="DV12" s="11"/>
+      <c r="DW12" s="11"/>
+      <c r="DX12" s="11"/>
+      <c r="DY12" s="11"/>
+      <c r="DZ12" s="11"/>
+      <c r="EA12" s="11"/>
+      <c r="EB12" s="11"/>
+      <c r="EC12" s="11"/>
+      <c r="ED12" s="11"/>
+      <c r="EE12" s="11"/>
+      <c r="EF12" s="11"/>
+      <c r="EG12" s="11"/>
+      <c r="EH12" s="11"/>
+      <c r="EI12" s="11"/>
+      <c r="EJ12" s="11"/>
+      <c r="EK12" s="11"/>
+      <c r="EL12" s="11"/>
+      <c r="EM12" s="11"/>
+      <c r="EN12" s="11"/>
+      <c r="EO12" s="11"/>
+      <c r="EP12" s="11"/>
+      <c r="EQ12" s="11"/>
+      <c r="ER12" s="11"/>
+      <c r="ES12" s="11"/>
+      <c r="ET12" s="11"/>
+      <c r="EU12" s="11"/>
+      <c r="EV12" s="11"/>
+      <c r="EW12" s="11"/>
+      <c r="EX12" s="11"/>
+      <c r="EY12" s="68">
         <f t="shared" si="6"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="13" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="54"/>
-      <c r="B13" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="56">
-        <v>0.125</v>
-      </c>
-      <c r="O13" s="56">
-        <v>0.125</v>
-      </c>
-      <c r="P13" s="56">
-        <v>0.125</v>
-      </c>
-      <c r="Q13" s="56">
-        <v>0.125</v>
-      </c>
-      <c r="R13" s="56">
-        <v>0.125</v>
-      </c>
-      <c r="S13" s="63"/>
-      <c r="T13" s="62"/>
-      <c r="U13" s="56">
-        <v>0.125</v>
-      </c>
-      <c r="V13" s="56">
-        <v>0.125</v>
-      </c>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="12"/>
-      <c r="Z13" s="12"/>
-      <c r="AA13" s="12"/>
-      <c r="AB13" s="12"/>
-      <c r="AC13" s="12"/>
-      <c r="AD13" s="12"/>
-      <c r="AE13" s="12"/>
-      <c r="AF13" s="12"/>
-      <c r="AG13" s="12"/>
-      <c r="AH13" s="12"/>
-      <c r="AI13" s="12"/>
-      <c r="AJ13" s="12"/>
-      <c r="AK13" s="12"/>
-      <c r="AL13" s="12"/>
-      <c r="AM13" s="12"/>
-      <c r="AN13" s="12"/>
-      <c r="AO13" s="12"/>
-      <c r="AP13" s="12"/>
-      <c r="AQ13" s="12"/>
-      <c r="AR13" s="12"/>
-      <c r="AS13" s="12"/>
-      <c r="AT13" s="12"/>
-      <c r="AU13" s="12"/>
-      <c r="AV13" s="12"/>
-      <c r="AW13" s="12"/>
-      <c r="AX13" s="12"/>
-      <c r="AY13" s="12"/>
-      <c r="AZ13" s="12"/>
-      <c r="BA13" s="12"/>
-      <c r="BB13" s="12"/>
-      <c r="BC13" s="12"/>
-      <c r="BD13" s="12"/>
-      <c r="BE13" s="12"/>
-      <c r="BF13" s="12"/>
-      <c r="BG13" s="12"/>
-      <c r="BH13" s="12"/>
-      <c r="BI13" s="12"/>
-      <c r="BJ13" s="12"/>
-      <c r="BK13" s="12"/>
-      <c r="BL13" s="12"/>
-      <c r="BM13" s="12"/>
-      <c r="BN13" s="12"/>
-      <c r="BO13" s="12"/>
-      <c r="BP13" s="12"/>
-      <c r="BQ13" s="12"/>
-      <c r="BR13" s="12"/>
-      <c r="BS13" s="12"/>
-      <c r="BT13" s="12"/>
-      <c r="BU13" s="12"/>
-      <c r="BV13" s="12"/>
-      <c r="BW13" s="12"/>
-      <c r="BX13" s="12"/>
-      <c r="BY13" s="12"/>
-      <c r="BZ13" s="12"/>
-      <c r="CA13" s="12"/>
-      <c r="CB13" s="12"/>
-      <c r="CC13" s="12"/>
-      <c r="CD13" s="12"/>
-      <c r="CE13" s="12"/>
-      <c r="CF13" s="12"/>
-      <c r="CG13" s="12"/>
-      <c r="CH13" s="12"/>
-      <c r="CI13" s="12"/>
-      <c r="CJ13" s="12"/>
-      <c r="CK13" s="12"/>
-      <c r="CL13" s="12"/>
-      <c r="CM13" s="12"/>
-      <c r="CN13" s="12"/>
-      <c r="CO13" s="12"/>
-      <c r="CP13" s="12"/>
-      <c r="CQ13" s="12"/>
-      <c r="CR13" s="12"/>
-      <c r="CS13" s="12"/>
-      <c r="CT13" s="12"/>
-      <c r="CU13" s="12"/>
-      <c r="CV13" s="12"/>
-      <c r="CW13" s="12"/>
-      <c r="CX13" s="12"/>
-      <c r="CY13" s="12"/>
-      <c r="CZ13" s="12"/>
-      <c r="DA13" s="12"/>
-      <c r="DB13" s="12"/>
-      <c r="DC13" s="12"/>
-      <c r="DD13" s="12"/>
-      <c r="DE13" s="12"/>
-      <c r="DF13" s="12"/>
-      <c r="DG13" s="12"/>
-      <c r="DH13" s="12"/>
-      <c r="DI13" s="12"/>
-      <c r="DJ13" s="12"/>
-      <c r="DK13" s="12"/>
-      <c r="DL13" s="12"/>
-      <c r="DM13" s="12"/>
-      <c r="DN13" s="12"/>
-      <c r="DO13" s="12"/>
-      <c r="DP13" s="12"/>
-      <c r="DQ13" s="12"/>
-      <c r="DR13" s="12"/>
-      <c r="DS13" s="12"/>
-      <c r="DT13" s="12"/>
-      <c r="DU13" s="12"/>
-      <c r="DV13" s="12"/>
-      <c r="DW13" s="12"/>
-      <c r="DX13" s="12"/>
-      <c r="DY13" s="12"/>
-      <c r="DZ13" s="12"/>
-      <c r="EA13" s="12"/>
-      <c r="EB13" s="12"/>
-      <c r="EC13" s="12"/>
-      <c r="ED13" s="12"/>
-      <c r="EE13" s="12"/>
-      <c r="EF13" s="12"/>
-      <c r="EG13" s="12"/>
-      <c r="EH13" s="12"/>
-      <c r="EI13" s="12"/>
-      <c r="EJ13" s="12"/>
-      <c r="EK13" s="12"/>
-      <c r="EL13" s="12"/>
-      <c r="EM13" s="12"/>
-      <c r="EN13" s="12"/>
-      <c r="EO13" s="12"/>
-      <c r="EP13" s="12"/>
-      <c r="EQ13" s="12"/>
-      <c r="ER13" s="12"/>
-      <c r="ES13" s="12"/>
-      <c r="ET13" s="12"/>
-      <c r="EU13" s="12"/>
-      <c r="EV13" s="12"/>
-      <c r="EW13" s="12"/>
-      <c r="EX13" s="12"/>
-      <c r="EY13" s="72">
+    <row r="13" spans="1:156" ht="15.6">
+      <c r="A13" s="71"/>
+      <c r="B13" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="52">
+        <v>0.125</v>
+      </c>
+      <c r="O13" s="52">
+        <v>0.125</v>
+      </c>
+      <c r="P13" s="52">
+        <v>0.125</v>
+      </c>
+      <c r="Q13" s="52">
+        <v>0.125</v>
+      </c>
+      <c r="R13" s="52">
+        <v>0.125</v>
+      </c>
+      <c r="S13" s="59"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="52">
+        <v>0.125</v>
+      </c>
+      <c r="V13" s="52">
+        <v>0.125</v>
+      </c>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
+      <c r="AC13" s="11"/>
+      <c r="AD13" s="11"/>
+      <c r="AE13" s="11"/>
+      <c r="AF13" s="11"/>
+      <c r="AG13" s="11"/>
+      <c r="AH13" s="11"/>
+      <c r="AI13" s="11"/>
+      <c r="AJ13" s="11"/>
+      <c r="AK13" s="11"/>
+      <c r="AL13" s="11"/>
+      <c r="AM13" s="11"/>
+      <c r="AN13" s="11"/>
+      <c r="AO13" s="11"/>
+      <c r="AP13" s="11"/>
+      <c r="AQ13" s="11"/>
+      <c r="AR13" s="11"/>
+      <c r="AS13" s="11"/>
+      <c r="AT13" s="11"/>
+      <c r="AU13" s="11"/>
+      <c r="AV13" s="11"/>
+      <c r="AW13" s="11"/>
+      <c r="AX13" s="11"/>
+      <c r="AY13" s="11"/>
+      <c r="AZ13" s="11"/>
+      <c r="BA13" s="11"/>
+      <c r="BB13" s="11"/>
+      <c r="BC13" s="11"/>
+      <c r="BD13" s="11"/>
+      <c r="BE13" s="11"/>
+      <c r="BF13" s="11"/>
+      <c r="BG13" s="11"/>
+      <c r="BH13" s="11"/>
+      <c r="BI13" s="11"/>
+      <c r="BJ13" s="11"/>
+      <c r="BK13" s="11"/>
+      <c r="BL13" s="11"/>
+      <c r="BM13" s="11"/>
+      <c r="BN13" s="11"/>
+      <c r="BO13" s="11"/>
+      <c r="BP13" s="11"/>
+      <c r="BQ13" s="11"/>
+      <c r="BR13" s="11"/>
+      <c r="BS13" s="11"/>
+      <c r="BT13" s="11"/>
+      <c r="BU13" s="11"/>
+      <c r="BV13" s="11"/>
+      <c r="BW13" s="11"/>
+      <c r="BX13" s="11"/>
+      <c r="BY13" s="11"/>
+      <c r="BZ13" s="11"/>
+      <c r="CA13" s="11"/>
+      <c r="CB13" s="11"/>
+      <c r="CC13" s="11"/>
+      <c r="CD13" s="11"/>
+      <c r="CE13" s="11"/>
+      <c r="CF13" s="11"/>
+      <c r="CG13" s="11"/>
+      <c r="CH13" s="11"/>
+      <c r="CI13" s="11"/>
+      <c r="CJ13" s="11"/>
+      <c r="CK13" s="11"/>
+      <c r="CL13" s="11"/>
+      <c r="CM13" s="11"/>
+      <c r="CN13" s="11"/>
+      <c r="CO13" s="11"/>
+      <c r="CP13" s="11"/>
+      <c r="CQ13" s="11"/>
+      <c r="CR13" s="11"/>
+      <c r="CS13" s="11"/>
+      <c r="CT13" s="11"/>
+      <c r="CU13" s="11"/>
+      <c r="CV13" s="11"/>
+      <c r="CW13" s="11"/>
+      <c r="CX13" s="11"/>
+      <c r="CY13" s="11"/>
+      <c r="CZ13" s="11"/>
+      <c r="DA13" s="11"/>
+      <c r="DB13" s="11"/>
+      <c r="DC13" s="11"/>
+      <c r="DD13" s="11"/>
+      <c r="DE13" s="11"/>
+      <c r="DF13" s="11"/>
+      <c r="DG13" s="11"/>
+      <c r="DH13" s="11"/>
+      <c r="DI13" s="11"/>
+      <c r="DJ13" s="11"/>
+      <c r="DK13" s="11"/>
+      <c r="DL13" s="11"/>
+      <c r="DM13" s="11"/>
+      <c r="DN13" s="11"/>
+      <c r="DO13" s="11"/>
+      <c r="DP13" s="11"/>
+      <c r="DQ13" s="11"/>
+      <c r="DR13" s="11"/>
+      <c r="DS13" s="11"/>
+      <c r="DT13" s="11"/>
+      <c r="DU13" s="11"/>
+      <c r="DV13" s="11"/>
+      <c r="DW13" s="11"/>
+      <c r="DX13" s="11"/>
+      <c r="DY13" s="11"/>
+      <c r="DZ13" s="11"/>
+      <c r="EA13" s="11"/>
+      <c r="EB13" s="11"/>
+      <c r="EC13" s="11"/>
+      <c r="ED13" s="11"/>
+      <c r="EE13" s="11"/>
+      <c r="EF13" s="11"/>
+      <c r="EG13" s="11"/>
+      <c r="EH13" s="11"/>
+      <c r="EI13" s="11"/>
+      <c r="EJ13" s="11"/>
+      <c r="EK13" s="11"/>
+      <c r="EL13" s="11"/>
+      <c r="EM13" s="11"/>
+      <c r="EN13" s="11"/>
+      <c r="EO13" s="11"/>
+      <c r="EP13" s="11"/>
+      <c r="EQ13" s="11"/>
+      <c r="ER13" s="11"/>
+      <c r="ES13" s="11"/>
+      <c r="ET13" s="11"/>
+      <c r="EU13" s="11"/>
+      <c r="EV13" s="11"/>
+      <c r="EW13" s="11"/>
+      <c r="EX13" s="11"/>
+      <c r="EY13" s="68">
         <f t="shared" si="6"/>
         <v>0.875</v>
       </c>
     </row>
-    <row r="14" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="54"/>
-      <c r="B14" s="58" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="47">
+    <row r="14" spans="1:156" ht="15.6">
+      <c r="A14" s="71"/>
+      <c r="B14" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="46">
         <f>SUM(C10:C13)</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="46">
         <f>SUM(D10:D13)</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="46">
         <f t="shared" ref="E14:AH14" si="7">SUM(E10:E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="46">
         <f>SUM(F10:F13)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="46">
         <f>SUM(G10:G13)</f>
         <v>0.125</v>
       </c>
-      <c r="H14" s="47">
+      <c r="H14" s="46">
         <f>SUM(H10:H13)</f>
         <v>0.125</v>
       </c>
-      <c r="I14" s="47">
+      <c r="I14" s="46">
         <f>SUM(I10:I13)</f>
         <v>0.125</v>
       </c>
-      <c r="J14" s="47">
+      <c r="J14" s="46">
         <f>SUM(J10:J13)</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="46">
         <f>SUM(K10:K13)</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="L14" s="47">
+      <c r="L14" s="46">
         <f>SUM(L10:L13)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="47">
+      <c r="M14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N14" s="47">
+      <c r="N14" s="46">
         <f>SUM(N10:N13)</f>
         <v>0.125</v>
       </c>
-      <c r="O14" s="47">
+      <c r="O14" s="46">
         <f>SUM(O10:O13)</f>
         <v>0.125</v>
       </c>
-      <c r="P14" s="47">
+      <c r="P14" s="46">
         <f>SUM(P10:P13)</f>
         <v>0.125</v>
       </c>
-      <c r="Q14" s="47">
+      <c r="Q14" s="46">
         <f>SUM(Q10:Q13)</f>
         <v>0.125</v>
       </c>
-      <c r="R14" s="47">
+      <c r="R14" s="46">
         <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
-      <c r="S14" s="47">
+      <c r="S14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T14" s="47">
+      <c r="T14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U14" s="47">
+      <c r="U14" s="46">
         <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
-      <c r="V14" s="47">
+      <c r="V14" s="46">
         <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
-      <c r="W14" s="47">
+      <c r="W14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="X14" s="47">
+      <c r="X14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Y14" s="47">
+      <c r="Y14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Z14" s="47">
+      <c r="Z14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AA14" s="47">
+      <c r="AA14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="47">
+      <c r="AB14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AC14" s="47">
+      <c r="AC14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD14" s="47">
+      <c r="AD14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AE14" s="47">
+      <c r="AE14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF14" s="47">
+      <c r="AF14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="47">
+      <c r="AG14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="47">
+      <c r="AH14" s="46">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI14" s="47">
+      <c r="AI14" s="46">
         <f t="shared" ref="AI14:BN14" si="8">SUM(AI10:AI13)</f>
         <v>0</v>
       </c>
-      <c r="AJ14" s="47">
+      <c r="AJ14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK14" s="47">
+      <c r="AK14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="47">
+      <c r="AL14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="47">
+      <c r="AM14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="47">
+      <c r="AN14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AO14" s="47">
+      <c r="AO14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AP14" s="47">
+      <c r="AP14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AQ14" s="47">
+      <c r="AQ14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AR14" s="47">
+      <c r="AR14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AS14" s="47">
+      <c r="AS14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AT14" s="47">
+      <c r="AT14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AU14" s="47">
+      <c r="AU14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AV14" s="47">
+      <c r="AV14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AW14" s="47">
+      <c r="AW14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AX14" s="47">
+      <c r="AX14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AY14" s="47">
+      <c r="AY14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AZ14" s="47">
+      <c r="AZ14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BA14" s="47">
+      <c r="BA14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BB14" s="47">
+      <c r="BB14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BC14" s="47">
+      <c r="BC14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BD14" s="47">
+      <c r="BD14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BE14" s="47">
+      <c r="BE14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BF14" s="47">
+      <c r="BF14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BG14" s="47">
+      <c r="BG14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BH14" s="47">
+      <c r="BH14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BI14" s="47">
+      <c r="BI14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BJ14" s="47">
+      <c r="BJ14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BK14" s="47">
+      <c r="BK14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BL14" s="47">
+      <c r="BL14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BM14" s="47">
+      <c r="BM14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BN14" s="47">
+      <c r="BN14" s="46">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="BO14" s="47">
+      <c r="BO14" s="46">
         <f t="shared" ref="BO14:CN14" si="9">SUM(BO10:BO13)</f>
         <v>0</v>
       </c>
-      <c r="BP14" s="47">
+      <c r="BP14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BQ14" s="47">
+      <c r="BQ14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BR14" s="47">
+      <c r="BR14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BS14" s="47">
+      <c r="BS14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BT14" s="47">
+      <c r="BT14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BU14" s="47">
+      <c r="BU14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BV14" s="47">
+      <c r="BV14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BW14" s="47">
+      <c r="BW14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BX14" s="47">
+      <c r="BX14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BY14" s="47">
+      <c r="BY14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BZ14" s="47">
+      <c r="BZ14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CA14" s="47">
+      <c r="CA14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CB14" s="47">
+      <c r="CB14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CC14" s="47">
+      <c r="CC14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CD14" s="47">
+      <c r="CD14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CE14" s="47">
+      <c r="CE14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CF14" s="47">
+      <c r="CF14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CG14" s="47">
+      <c r="CG14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CH14" s="47">
+      <c r="CH14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CI14" s="47">
+      <c r="CI14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CJ14" s="47">
+      <c r="CJ14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CK14" s="47">
+      <c r="CK14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CL14" s="47">
+      <c r="CL14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CM14" s="47">
+      <c r="CM14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CN14" s="47">
+      <c r="CN14" s="46">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="CO14" s="47">
+      <c r="CO14" s="46">
         <f t="shared" ref="CO14" si="10">SUM(CO10:CO13)</f>
         <v>0</v>
       </c>
-      <c r="CP14" s="47">
+      <c r="CP14" s="46">
         <f t="shared" ref="CP14" si="11">SUM(CP10:CP13)</f>
         <v>0</v>
       </c>
-      <c r="CQ14" s="47">
+      <c r="CQ14" s="46">
         <f t="shared" ref="CQ14" si="12">SUM(CQ10:CQ13)</f>
         <v>0</v>
       </c>
-      <c r="CR14" s="47">
+      <c r="CR14" s="46">
         <f t="shared" ref="CR14" si="13">SUM(CR10:CR13)</f>
         <v>0</v>
       </c>
-      <c r="CS14" s="47">
+      <c r="CS14" s="46">
         <f t="shared" ref="CS14" si="14">SUM(CS10:CS13)</f>
         <v>0</v>
       </c>
-      <c r="CT14" s="47">
+      <c r="CT14" s="46">
         <f t="shared" ref="CT14" si="15">SUM(CT10:CT13)</f>
         <v>0</v>
       </c>
-      <c r="CU14" s="47">
+      <c r="CU14" s="46">
         <f t="shared" ref="CU14" si="16">SUM(CU10:CU13)</f>
         <v>0</v>
       </c>
-      <c r="CV14" s="47">
+      <c r="CV14" s="46">
         <f t="shared" ref="CV14" si="17">SUM(CV10:CV13)</f>
         <v>0</v>
       </c>
-      <c r="CW14" s="47">
+      <c r="CW14" s="46">
         <f t="shared" ref="CW14" si="18">SUM(CW10:CW13)</f>
         <v>0</v>
       </c>
-      <c r="CX14" s="47">
+      <c r="CX14" s="46">
         <f t="shared" ref="CX14" si="19">SUM(CX10:CX13)</f>
         <v>0</v>
       </c>
-      <c r="CY14" s="47">
+      <c r="CY14" s="46">
         <f t="shared" ref="CY14" si="20">SUM(CY10:CY13)</f>
         <v>0</v>
       </c>
-      <c r="CZ14" s="47">
+      <c r="CZ14" s="46">
         <f t="shared" ref="CZ14" si="21">SUM(CZ10:CZ13)</f>
         <v>0</v>
       </c>
-      <c r="DA14" s="47">
+      <c r="DA14" s="46">
         <f t="shared" ref="DA14" si="22">SUM(DA10:DA13)</f>
         <v>0</v>
       </c>
-      <c r="DB14" s="47">
+      <c r="DB14" s="46">
         <f t="shared" ref="DB14" si="23">SUM(DB10:DB13)</f>
         <v>0</v>
       </c>
-      <c r="DC14" s="47">
+      <c r="DC14" s="46">
         <f t="shared" ref="DC14" si="24">SUM(DC10:DC13)</f>
         <v>0</v>
       </c>
-      <c r="DD14" s="47">
+      <c r="DD14" s="46">
         <f t="shared" ref="DD14" si="25">SUM(DD10:DD13)</f>
         <v>0</v>
       </c>
-      <c r="DE14" s="47">
+      <c r="DE14" s="46">
         <f t="shared" ref="DE14" si="26">SUM(DE10:DE13)</f>
         <v>0</v>
       </c>
-      <c r="DF14" s="47">
+      <c r="DF14" s="46">
         <f t="shared" ref="DF14" si="27">SUM(DF10:DF13)</f>
         <v>0</v>
       </c>
-      <c r="DG14" s="47">
+      <c r="DG14" s="46">
         <f t="shared" ref="DG14" si="28">SUM(DG10:DG13)</f>
         <v>0</v>
       </c>
-      <c r="DH14" s="47">
+      <c r="DH14" s="46">
         <f t="shared" ref="DH14" si="29">SUM(DH10:DH13)</f>
         <v>0</v>
       </c>
-      <c r="DI14" s="47">
+      <c r="DI14" s="46">
         <f t="shared" ref="DI14" si="30">SUM(DI10:DI13)</f>
         <v>0</v>
       </c>
-      <c r="DJ14" s="47">
+      <c r="DJ14" s="46">
         <f t="shared" ref="DJ14" si="31">SUM(DJ10:DJ13)</f>
         <v>0</v>
       </c>
-      <c r="DK14" s="47">
+      <c r="DK14" s="46">
         <f t="shared" ref="DK14" si="32">SUM(DK10:DK13)</f>
         <v>0</v>
       </c>
-      <c r="DL14" s="47">
+      <c r="DL14" s="46">
         <f t="shared" ref="DL14" si="33">SUM(DL10:DL13)</f>
         <v>0</v>
       </c>
-      <c r="DM14" s="47">
+      <c r="DM14" s="46">
         <f t="shared" ref="DM14" si="34">SUM(DM10:DM13)</f>
         <v>0</v>
       </c>
-      <c r="DN14" s="47">
+      <c r="DN14" s="46">
         <f t="shared" ref="DN14" si="35">SUM(DN10:DN13)</f>
         <v>0</v>
       </c>
-      <c r="DO14" s="47">
+      <c r="DO14" s="46">
         <f t="shared" ref="DO14" si="36">SUM(DO10:DO13)</f>
         <v>0</v>
       </c>
-      <c r="DP14" s="47">
+      <c r="DP14" s="46">
         <f t="shared" ref="DP14" si="37">SUM(DP10:DP13)</f>
         <v>0</v>
       </c>
-      <c r="DQ14" s="47">
+      <c r="DQ14" s="46">
         <f t="shared" ref="DQ14" si="38">SUM(DQ10:DQ13)</f>
         <v>0</v>
       </c>
-      <c r="DR14" s="47">
+      <c r="DR14" s="46">
         <f t="shared" ref="DR14" si="39">SUM(DR10:DR13)</f>
         <v>0</v>
       </c>
-      <c r="DS14" s="47">
+      <c r="DS14" s="46">
         <f t="shared" ref="DS14" si="40">SUM(DS10:DS13)</f>
         <v>0</v>
       </c>
-      <c r="DT14" s="47">
+      <c r="DT14" s="46">
         <f t="shared" ref="DT14" si="41">SUM(DT10:DT13)</f>
         <v>0</v>
       </c>
-      <c r="DU14" s="47">
+      <c r="DU14" s="46">
         <f t="shared" ref="DU14" si="42">SUM(DU10:DU13)</f>
         <v>0</v>
       </c>
-      <c r="DV14" s="47">
+      <c r="DV14" s="46">
         <f t="shared" ref="DV14" si="43">SUM(DV10:DV13)</f>
         <v>0</v>
       </c>
-      <c r="DW14" s="47">
+      <c r="DW14" s="46">
         <f t="shared" ref="DW14" si="44">SUM(DW10:DW13)</f>
         <v>0</v>
       </c>
-      <c r="DX14" s="47">
+      <c r="DX14" s="46">
         <f t="shared" ref="DX14" si="45">SUM(DX10:DX13)</f>
         <v>0</v>
       </c>
-      <c r="DY14" s="47">
+      <c r="DY14" s="46">
         <f t="shared" ref="DY14" si="46">SUM(DY10:DY13)</f>
         <v>0</v>
       </c>
-      <c r="DZ14" s="47">
+      <c r="DZ14" s="46">
         <f t="shared" ref="DZ14" si="47">SUM(DZ10:DZ13)</f>
         <v>0</v>
       </c>
-      <c r="EA14" s="47">
+      <c r="EA14" s="46">
         <f t="shared" ref="EA14" si="48">SUM(EA10:EA13)</f>
         <v>0</v>
       </c>
-      <c r="EB14" s="47">
+      <c r="EB14" s="46">
         <f t="shared" ref="EB14" si="49">SUM(EB10:EB13)</f>
         <v>0</v>
       </c>
-      <c r="EC14" s="47">
+      <c r="EC14" s="46">
         <f t="shared" ref="EC14" si="50">SUM(EC10:EC13)</f>
         <v>0</v>
       </c>
-      <c r="ED14" s="47">
+      <c r="ED14" s="46">
         <f t="shared" ref="ED14" si="51">SUM(ED10:ED13)</f>
         <v>0</v>
       </c>
-      <c r="EE14" s="47">
+      <c r="EE14" s="46">
         <f t="shared" ref="EE14" si="52">SUM(EE10:EE13)</f>
         <v>0</v>
       </c>
-      <c r="EF14" s="47">
+      <c r="EF14" s="46">
         <f t="shared" ref="EF14" si="53">SUM(EF10:EF13)</f>
         <v>0</v>
       </c>
-      <c r="EG14" s="47">
+      <c r="EG14" s="46">
         <f t="shared" ref="EG14" si="54">SUM(EG10:EG13)</f>
         <v>0</v>
       </c>
-      <c r="EH14" s="47">
+      <c r="EH14" s="46">
         <f t="shared" ref="EH14" si="55">SUM(EH10:EH13)</f>
         <v>0</v>
       </c>
-      <c r="EI14" s="47">
+      <c r="EI14" s="46">
         <f t="shared" ref="EI14" si="56">SUM(EI10:EI13)</f>
         <v>0</v>
       </c>
-      <c r="EJ14" s="47">
+      <c r="EJ14" s="46">
         <f t="shared" ref="EJ14" si="57">SUM(EJ10:EJ13)</f>
         <v>0</v>
       </c>
-      <c r="EK14" s="47">
+      <c r="EK14" s="46">
         <f t="shared" ref="EK14" si="58">SUM(EK10:EK13)</f>
         <v>0</v>
       </c>
-      <c r="EL14" s="47">
+      <c r="EL14" s="46">
         <f t="shared" ref="EL14" si="59">SUM(EL10:EL13)</f>
         <v>0</v>
       </c>
-      <c r="EM14" s="47">
+      <c r="EM14" s="46">
         <f t="shared" ref="EM14" si="60">SUM(EM10:EM13)</f>
         <v>0</v>
       </c>
-      <c r="EN14" s="47">
+      <c r="EN14" s="46">
         <f t="shared" ref="EN14" si="61">SUM(EN10:EN13)</f>
         <v>0</v>
       </c>
-      <c r="EO14" s="47">
+      <c r="EO14" s="46">
         <f t="shared" ref="EO14" si="62">SUM(EO10:EO13)</f>
         <v>0</v>
       </c>
-      <c r="EP14" s="47">
+      <c r="EP14" s="46">
         <f t="shared" ref="EP14" si="63">SUM(EP10:EP13)</f>
         <v>0</v>
       </c>
-      <c r="EQ14" s="47">
+      <c r="EQ14" s="46">
         <f t="shared" ref="EQ14" si="64">SUM(EQ10:EQ13)</f>
         <v>0</v>
       </c>
-      <c r="ER14" s="47">
+      <c r="ER14" s="46">
         <f t="shared" ref="ER14" si="65">SUM(ER10:ER13)</f>
         <v>0</v>
       </c>
-      <c r="ES14" s="47">
+      <c r="ES14" s="46">
         <f t="shared" ref="ES14" si="66">SUM(ES10:ES13)</f>
         <v>0</v>
       </c>
-      <c r="ET14" s="47">
+      <c r="ET14" s="46">
         <f t="shared" ref="ET14" si="67">SUM(ET10:ET13)</f>
         <v>0</v>
       </c>
-      <c r="EU14" s="47">
+      <c r="EU14" s="46">
         <f t="shared" ref="EU14" si="68">SUM(EU10:EU13)</f>
         <v>0</v>
       </c>
-      <c r="EV14" s="47">
+      <c r="EV14" s="46">
         <f t="shared" ref="EV14" si="69">SUM(EV10:EV13)</f>
         <v>0</v>
       </c>
-      <c r="EW14" s="47">
+      <c r="EW14" s="46">
         <f t="shared" ref="EW14" si="70">SUM(EW10:EW13)</f>
         <v>0</v>
       </c>
-      <c r="EX14" s="47">
+      <c r="EX14" s="46">
         <f t="shared" ref="EX14" si="71">SUM(EX10:EX13)</f>
         <v>0</v>
       </c>
-      <c r="EY14" s="72">
+      <c r="EY14" s="68">
         <f>SUM(C14:EX14)</f>
         <v>1.5833333333333335</v>
       </c>
-      <c r="EZ14" s="64"/>
-    </row>
-    <row r="15" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="60"/>
-      <c r="V15" s="60"/>
-      <c r="W15" s="56">
+      <c r="EZ14" s="60"/>
+    </row>
+    <row r="15" spans="1:156" ht="15.6">
+      <c r="A15" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="56"/>
+      <c r="V15" s="56"/>
+      <c r="W15" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="X15" s="56">
+      <c r="X15" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="Y15" s="56">
+      <c r="Y15" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="Z15" s="63"/>
-      <c r="AA15" s="62"/>
-      <c r="AB15" s="67">
+      <c r="Z15" s="59"/>
+      <c r="AA15" s="58"/>
+      <c r="AB15" s="63">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AC15" s="56">
+      <c r="AC15" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AD15" s="56">
+      <c r="AD15" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AE15" s="56">
+      <c r="AE15" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AF15" s="67">
+      <c r="AF15" s="63">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AG15" s="63"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="56">
+      <c r="AG15" s="59"/>
+      <c r="AH15" s="58"/>
+      <c r="AI15" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AJ15" s="56">
+      <c r="AJ15" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AK15" s="67">
+      <c r="AK15" s="63">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AL15" s="56">
+      <c r="AL15" s="52">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AM15" s="12"/>
-      <c r="AN15" s="12"/>
-      <c r="AO15" s="12"/>
-      <c r="AP15" s="12"/>
-      <c r="AQ15" s="12"/>
-      <c r="AR15" s="12"/>
-      <c r="AS15" s="12"/>
-      <c r="AT15" s="12"/>
-      <c r="AU15" s="12"/>
-      <c r="AV15" s="12"/>
-      <c r="AW15" s="12"/>
-      <c r="AX15" s="12"/>
-      <c r="AY15" s="12"/>
-      <c r="AZ15" s="12"/>
-      <c r="BA15" s="12"/>
-      <c r="BB15" s="12"/>
-      <c r="BC15" s="12"/>
-      <c r="BD15" s="12"/>
-      <c r="BE15" s="12"/>
-      <c r="BF15" s="12"/>
-      <c r="BG15" s="12"/>
-      <c r="BH15" s="12"/>
-      <c r="BI15" s="12"/>
-      <c r="BJ15" s="12"/>
-      <c r="BK15" s="12"/>
-      <c r="BL15" s="12"/>
-      <c r="BM15" s="12"/>
-      <c r="BN15" s="12"/>
-      <c r="BO15" s="12"/>
-      <c r="BP15" s="12"/>
-      <c r="BQ15" s="12"/>
-      <c r="BR15" s="12"/>
-      <c r="BS15" s="12"/>
-      <c r="BT15" s="12"/>
-      <c r="BU15" s="12"/>
-      <c r="BV15" s="12"/>
-      <c r="BW15" s="12"/>
-      <c r="BX15" s="12"/>
-      <c r="BY15" s="12"/>
-      <c r="BZ15" s="12"/>
-      <c r="CA15" s="12"/>
-      <c r="CB15" s="12"/>
-      <c r="CC15" s="12"/>
-      <c r="CD15" s="12"/>
-      <c r="CE15" s="12"/>
-      <c r="CF15" s="12"/>
-      <c r="CG15" s="12"/>
-      <c r="CH15" s="12"/>
-      <c r="CI15" s="12"/>
-      <c r="CJ15" s="12"/>
-      <c r="CK15" s="12"/>
-      <c r="CL15" s="12"/>
-      <c r="CM15" s="12"/>
-      <c r="CN15" s="12"/>
-      <c r="CO15" s="12"/>
-      <c r="CP15" s="12"/>
-      <c r="CQ15" s="12"/>
-      <c r="CR15" s="12"/>
-      <c r="CS15" s="12"/>
-      <c r="CT15" s="12"/>
-      <c r="CU15" s="12"/>
-      <c r="CV15" s="12"/>
-      <c r="CW15" s="12"/>
-      <c r="CX15" s="12"/>
-      <c r="CY15" s="12"/>
-      <c r="CZ15" s="12"/>
-      <c r="DA15" s="12"/>
-      <c r="DB15" s="12"/>
-      <c r="DC15" s="12"/>
-      <c r="DD15" s="12"/>
-      <c r="DE15" s="12"/>
-      <c r="DF15" s="12"/>
-      <c r="DG15" s="12"/>
-      <c r="DH15" s="12"/>
-      <c r="DI15" s="12"/>
-      <c r="DJ15" s="12"/>
-      <c r="DK15" s="12"/>
-      <c r="DL15" s="12"/>
-      <c r="DM15" s="12"/>
-      <c r="DN15" s="12"/>
-      <c r="DO15" s="12"/>
-      <c r="DP15" s="12"/>
-      <c r="DQ15" s="12"/>
-      <c r="DR15" s="12"/>
-      <c r="DS15" s="12"/>
-      <c r="DT15" s="12"/>
-      <c r="DU15" s="12"/>
-      <c r="DV15" s="12"/>
-      <c r="DW15" s="12"/>
-      <c r="DX15" s="12"/>
-      <c r="DY15" s="12"/>
-      <c r="DZ15" s="12"/>
-      <c r="EA15" s="12"/>
-      <c r="EB15" s="12"/>
-      <c r="EC15" s="12"/>
-      <c r="ED15" s="12"/>
-      <c r="EE15" s="12"/>
-      <c r="EF15" s="12"/>
-      <c r="EG15" s="12"/>
-      <c r="EH15" s="12"/>
-      <c r="EI15" s="12"/>
-      <c r="EJ15" s="12"/>
-      <c r="EK15" s="12"/>
-      <c r="EL15" s="12"/>
-      <c r="EM15" s="12"/>
-      <c r="EN15" s="12"/>
-      <c r="EO15" s="12"/>
-      <c r="EP15" s="12"/>
-      <c r="EQ15" s="12"/>
-      <c r="ER15" s="12"/>
-      <c r="ES15" s="12"/>
-      <c r="ET15" s="12"/>
-      <c r="EU15" s="12"/>
-      <c r="EV15" s="12"/>
-      <c r="EW15" s="12"/>
-      <c r="EX15" s="12"/>
-      <c r="EY15" s="72">
+      <c r="AM15" s="11"/>
+      <c r="AN15" s="11"/>
+      <c r="AO15" s="11"/>
+      <c r="AP15" s="11"/>
+      <c r="AQ15" s="11"/>
+      <c r="AR15" s="11"/>
+      <c r="AS15" s="11"/>
+      <c r="AT15" s="11"/>
+      <c r="AU15" s="11"/>
+      <c r="AV15" s="11"/>
+      <c r="AW15" s="11"/>
+      <c r="AX15" s="11"/>
+      <c r="AY15" s="11"/>
+      <c r="AZ15" s="11"/>
+      <c r="BA15" s="11"/>
+      <c r="BB15" s="11"/>
+      <c r="BC15" s="11"/>
+      <c r="BD15" s="11"/>
+      <c r="BE15" s="11"/>
+      <c r="BF15" s="11"/>
+      <c r="BG15" s="11"/>
+      <c r="BH15" s="11"/>
+      <c r="BI15" s="11"/>
+      <c r="BJ15" s="11"/>
+      <c r="BK15" s="11"/>
+      <c r="BL15" s="11"/>
+      <c r="BM15" s="11"/>
+      <c r="BN15" s="11"/>
+      <c r="BO15" s="11"/>
+      <c r="BP15" s="11"/>
+      <c r="BQ15" s="11"/>
+      <c r="BR15" s="11"/>
+      <c r="BS15" s="11"/>
+      <c r="BT15" s="11"/>
+      <c r="BU15" s="11"/>
+      <c r="BV15" s="11"/>
+      <c r="BW15" s="11"/>
+      <c r="BX15" s="11"/>
+      <c r="BY15" s="11"/>
+      <c r="BZ15" s="11"/>
+      <c r="CA15" s="11"/>
+      <c r="CB15" s="11"/>
+      <c r="CC15" s="11"/>
+      <c r="CD15" s="11"/>
+      <c r="CE15" s="11"/>
+      <c r="CF15" s="11"/>
+      <c r="CG15" s="11"/>
+      <c r="CH15" s="11"/>
+      <c r="CI15" s="11"/>
+      <c r="CJ15" s="11"/>
+      <c r="CK15" s="11"/>
+      <c r="CL15" s="11"/>
+      <c r="CM15" s="11"/>
+      <c r="CN15" s="11"/>
+      <c r="CO15" s="11"/>
+      <c r="CP15" s="11"/>
+      <c r="CQ15" s="11"/>
+      <c r="CR15" s="11"/>
+      <c r="CS15" s="11"/>
+      <c r="CT15" s="11"/>
+      <c r="CU15" s="11"/>
+      <c r="CV15" s="11"/>
+      <c r="CW15" s="11"/>
+      <c r="CX15" s="11"/>
+      <c r="CY15" s="11"/>
+      <c r="CZ15" s="11"/>
+      <c r="DA15" s="11"/>
+      <c r="DB15" s="11"/>
+      <c r="DC15" s="11"/>
+      <c r="DD15" s="11"/>
+      <c r="DE15" s="11"/>
+      <c r="DF15" s="11"/>
+      <c r="DG15" s="11"/>
+      <c r="DH15" s="11"/>
+      <c r="DI15" s="11"/>
+      <c r="DJ15" s="11"/>
+      <c r="DK15" s="11"/>
+      <c r="DL15" s="11"/>
+      <c r="DM15" s="11"/>
+      <c r="DN15" s="11"/>
+      <c r="DO15" s="11"/>
+      <c r="DP15" s="11"/>
+      <c r="DQ15" s="11"/>
+      <c r="DR15" s="11"/>
+      <c r="DS15" s="11"/>
+      <c r="DT15" s="11"/>
+      <c r="DU15" s="11"/>
+      <c r="DV15" s="11"/>
+      <c r="DW15" s="11"/>
+      <c r="DX15" s="11"/>
+      <c r="DY15" s="11"/>
+      <c r="DZ15" s="11"/>
+      <c r="EA15" s="11"/>
+      <c r="EB15" s="11"/>
+      <c r="EC15" s="11"/>
+      <c r="ED15" s="11"/>
+      <c r="EE15" s="11"/>
+      <c r="EF15" s="11"/>
+      <c r="EG15" s="11"/>
+      <c r="EH15" s="11"/>
+      <c r="EI15" s="11"/>
+      <c r="EJ15" s="11"/>
+      <c r="EK15" s="11"/>
+      <c r="EL15" s="11"/>
+      <c r="EM15" s="11"/>
+      <c r="EN15" s="11"/>
+      <c r="EO15" s="11"/>
+      <c r="EP15" s="11"/>
+      <c r="EQ15" s="11"/>
+      <c r="ER15" s="11"/>
+      <c r="ES15" s="11"/>
+      <c r="ET15" s="11"/>
+      <c r="EU15" s="11"/>
+      <c r="EV15" s="11"/>
+      <c r="EW15" s="11"/>
+      <c r="EX15" s="11"/>
+      <c r="EY15" s="68">
         <f t="shared" ref="EY15:EY23" si="72">SUM(C15:EX15)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:156" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="55"/>
-      <c r="B16" s="57" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="60"/>
-      <c r="V16" s="60"/>
-      <c r="W16" s="56">
+    <row r="16" spans="1:156" ht="15.6">
+      <c r="A16" s="72"/>
+      <c r="B16" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="56"/>
+      <c r="V16" s="56"/>
+      <c r="W16" s="52">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="X16" s="67">
+      <c r="X16" s="63">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="Y16" s="56">
+      <c r="Y16" s="52">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="Z16" s="63"/>
-      <c r="AA16" s="62"/>
-      <c r="AB16" s="56">
+      <c r="Z16" s="59"/>
+      <c r="AA16" s="58"/>
+      <c r="AB16" s="52">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="AC16" s="56">
+      <c r="AC16" s="52">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="AD16" s="67">
+      <c r="AD16" s="63">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="AE16" s="56">
+      <c r="AE16" s="52">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="AF16" s="56">
+      <c r="AF16" s="52">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="AG16" s="63"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="56">
+      <c r="AG16" s="59"/>
+      <c r="AH16" s="58"/>
+      <c r="AI16" s="52">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="AJ16" s="56">
+      <c r="AJ16" s="52">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="AK16" s="56">
+      <c r="AK16" s="52">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="AL16" s="56">
+      <c r="AL16" s="52">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="AM16" s="12"/>
-      <c r="AN16" s="12"/>
-      <c r="AO16" s="12"/>
-      <c r="AP16" s="12"/>
-      <c r="AQ16" s="12"/>
-      <c r="AR16" s="12"/>
-      <c r="AS16" s="12"/>
-      <c r="AT16" s="12"/>
-      <c r="AU16" s="12"/>
-      <c r="AV16" s="12"/>
-      <c r="AW16" s="12"/>
-      <c r="AX16" s="12"/>
-      <c r="AY16" s="12"/>
-      <c r="AZ16" s="12"/>
-      <c r="BA16" s="12"/>
-      <c r="BB16" s="12"/>
-      <c r="BC16" s="12"/>
-      <c r="BD16" s="12"/>
-      <c r="BE16" s="12"/>
-      <c r="BF16" s="12"/>
-      <c r="BG16" s="12"/>
-      <c r="BH16" s="12"/>
-      <c r="BI16" s="12"/>
-      <c r="BJ16" s="12"/>
-      <c r="BK16" s="12"/>
-      <c r="BL16" s="12"/>
-      <c r="BM16" s="12"/>
-      <c r="BN16" s="12"/>
-      <c r="BO16" s="12"/>
-      <c r="BP16" s="12"/>
-      <c r="BQ16" s="12"/>
-      <c r="BR16" s="12"/>
-      <c r="BS16" s="12"/>
-      <c r="BT16" s="12"/>
-      <c r="BU16" s="12"/>
-      <c r="BV16" s="12"/>
-      <c r="BW16" s="12"/>
-      <c r="BX16" s="12"/>
-      <c r="BY16" s="12"/>
-      <c r="BZ16" s="12"/>
-      <c r="CA16" s="12"/>
-      <c r="CB16" s="12"/>
-      <c r="CC16" s="12"/>
-      <c r="CD16" s="12"/>
-      <c r="CE16" s="12"/>
-      <c r="CF16" s="12"/>
-      <c r="CG16" s="12"/>
-      <c r="CH16" s="12"/>
-      <c r="CI16" s="12"/>
-      <c r="CJ16" s="12"/>
-      <c r="CK16" s="12"/>
-      <c r="CL16" s="12"/>
-      <c r="CM16" s="12"/>
-      <c r="CN16" s="12"/>
-      <c r="CO16" s="12"/>
-      <c r="CP16" s="12"/>
-      <c r="CQ16" s="12"/>
-      <c r="CR16" s="12"/>
-      <c r="CS16" s="12"/>
-      <c r="CT16" s="12"/>
-      <c r="CU16" s="12"/>
-      <c r="CV16" s="12"/>
-      <c r="CW16" s="12"/>
-      <c r="CX16" s="12"/>
-      <c r="CY16" s="12"/>
-      <c r="CZ16" s="12"/>
-      <c r="DA16" s="12"/>
-      <c r="DB16" s="12"/>
-      <c r="DC16" s="12"/>
-      <c r="DD16" s="12"/>
-      <c r="DE16" s="12"/>
-      <c r="DF16" s="12"/>
-      <c r="DG16" s="12"/>
-      <c r="DH16" s="12"/>
-      <c r="DI16" s="12"/>
-      <c r="DJ16" s="12"/>
-      <c r="DK16" s="12"/>
-      <c r="DL16" s="12"/>
-      <c r="DM16" s="12"/>
-      <c r="DN16" s="12"/>
-      <c r="DO16" s="12"/>
-      <c r="DP16" s="12"/>
-      <c r="DQ16" s="12"/>
-      <c r="DR16" s="12"/>
-      <c r="DS16" s="12"/>
-      <c r="DT16" s="12"/>
-      <c r="DU16" s="12"/>
-      <c r="DV16" s="12"/>
-      <c r="DW16" s="12"/>
-      <c r="DX16" s="12"/>
-      <c r="DY16" s="12"/>
-      <c r="DZ16" s="12"/>
-      <c r="EA16" s="12"/>
-      <c r="EB16" s="12"/>
-      <c r="EC16" s="12"/>
-      <c r="ED16" s="12"/>
-      <c r="EE16" s="12"/>
-      <c r="EF16" s="12"/>
-      <c r="EG16" s="12"/>
-      <c r="EH16" s="12"/>
-      <c r="EI16" s="12"/>
-      <c r="EJ16" s="12"/>
-      <c r="EK16" s="12"/>
-      <c r="EL16" s="12"/>
-      <c r="EM16" s="12"/>
-      <c r="EN16" s="12"/>
-      <c r="EO16" s="12"/>
-      <c r="EP16" s="12"/>
-      <c r="EQ16" s="12"/>
-      <c r="ER16" s="12"/>
-      <c r="ES16" s="12"/>
-      <c r="ET16" s="12"/>
-      <c r="EU16" s="12"/>
-      <c r="EV16" s="12"/>
-      <c r="EW16" s="12"/>
-      <c r="EX16" s="12"/>
-      <c r="EY16" s="72">
+      <c r="AM16" s="11"/>
+      <c r="AN16" s="11"/>
+      <c r="AO16" s="11"/>
+      <c r="AP16" s="11"/>
+      <c r="AQ16" s="11"/>
+      <c r="AR16" s="11"/>
+      <c r="AS16" s="11"/>
+      <c r="AT16" s="11"/>
+      <c r="AU16" s="11"/>
+      <c r="AV16" s="11"/>
+      <c r="AW16" s="11"/>
+      <c r="AX16" s="11"/>
+      <c r="AY16" s="11"/>
+      <c r="AZ16" s="11"/>
+      <c r="BA16" s="11"/>
+      <c r="BB16" s="11"/>
+      <c r="BC16" s="11"/>
+      <c r="BD16" s="11"/>
+      <c r="BE16" s="11"/>
+      <c r="BF16" s="11"/>
+      <c r="BG16" s="11"/>
+      <c r="BH16" s="11"/>
+      <c r="BI16" s="11"/>
+      <c r="BJ16" s="11"/>
+      <c r="BK16" s="11"/>
+      <c r="BL16" s="11"/>
+      <c r="BM16" s="11"/>
+      <c r="BN16" s="11"/>
+      <c r="BO16" s="11"/>
+      <c r="BP16" s="11"/>
+      <c r="BQ16" s="11"/>
+      <c r="BR16" s="11"/>
+      <c r="BS16" s="11"/>
+      <c r="BT16" s="11"/>
+      <c r="BU16" s="11"/>
+      <c r="BV16" s="11"/>
+      <c r="BW16" s="11"/>
+      <c r="BX16" s="11"/>
+      <c r="BY16" s="11"/>
+      <c r="BZ16" s="11"/>
+      <c r="CA16" s="11"/>
+      <c r="CB16" s="11"/>
+      <c r="CC16" s="11"/>
+      <c r="CD16" s="11"/>
+      <c r="CE16" s="11"/>
+      <c r="CF16" s="11"/>
+      <c r="CG16" s="11"/>
+      <c r="CH16" s="11"/>
+      <c r="CI16" s="11"/>
+      <c r="CJ16" s="11"/>
+      <c r="CK16" s="11"/>
+      <c r="CL16" s="11"/>
+      <c r="CM16" s="11"/>
+      <c r="CN16" s="11"/>
+      <c r="CO16" s="11"/>
+      <c r="CP16" s="11"/>
+      <c r="CQ16" s="11"/>
+      <c r="CR16" s="11"/>
+      <c r="CS16" s="11"/>
+      <c r="CT16" s="11"/>
+      <c r="CU16" s="11"/>
+      <c r="CV16" s="11"/>
+      <c r="CW16" s="11"/>
+      <c r="CX16" s="11"/>
+      <c r="CY16" s="11"/>
+      <c r="CZ16" s="11"/>
+      <c r="DA16" s="11"/>
+      <c r="DB16" s="11"/>
+      <c r="DC16" s="11"/>
+      <c r="DD16" s="11"/>
+      <c r="DE16" s="11"/>
+      <c r="DF16" s="11"/>
+      <c r="DG16" s="11"/>
+      <c r="DH16" s="11"/>
+      <c r="DI16" s="11"/>
+      <c r="DJ16" s="11"/>
+      <c r="DK16" s="11"/>
+      <c r="DL16" s="11"/>
+      <c r="DM16" s="11"/>
+      <c r="DN16" s="11"/>
+      <c r="DO16" s="11"/>
+      <c r="DP16" s="11"/>
+      <c r="DQ16" s="11"/>
+      <c r="DR16" s="11"/>
+      <c r="DS16" s="11"/>
+      <c r="DT16" s="11"/>
+      <c r="DU16" s="11"/>
+      <c r="DV16" s="11"/>
+      <c r="DW16" s="11"/>
+      <c r="DX16" s="11"/>
+      <c r="DY16" s="11"/>
+      <c r="DZ16" s="11"/>
+      <c r="EA16" s="11"/>
+      <c r="EB16" s="11"/>
+      <c r="EC16" s="11"/>
+      <c r="ED16" s="11"/>
+      <c r="EE16" s="11"/>
+      <c r="EF16" s="11"/>
+      <c r="EG16" s="11"/>
+      <c r="EH16" s="11"/>
+      <c r="EI16" s="11"/>
+      <c r="EJ16" s="11"/>
+      <c r="EK16" s="11"/>
+      <c r="EL16" s="11"/>
+      <c r="EM16" s="11"/>
+      <c r="EN16" s="11"/>
+      <c r="EO16" s="11"/>
+      <c r="EP16" s="11"/>
+      <c r="EQ16" s="11"/>
+      <c r="ER16" s="11"/>
+      <c r="ES16" s="11"/>
+      <c r="ET16" s="11"/>
+      <c r="EU16" s="11"/>
+      <c r="EV16" s="11"/>
+      <c r="EW16" s="11"/>
+      <c r="EX16" s="11"/>
+      <c r="EY16" s="68">
         <f t="shared" si="72"/>
         <v>8.3333333333333356E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:155" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="55"/>
-      <c r="B17" s="58" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="47">
+    <row r="17" spans="1:155" ht="15.6">
+      <c r="A17" s="72"/>
+      <c r="B17" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="46">
         <f>SUM(C15:C16)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="46">
         <f>SUM(D15:D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="46">
         <f>SUM(E15:E16)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="46">
         <f>SUM(F15:F16)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="46">
         <f>SUM(G15:G16)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="47">
+      <c r="H17" s="46">
         <f>SUM(H15:H16)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="47">
+      <c r="I17" s="46">
         <f>SUM(I15:I16)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="47">
+      <c r="J17" s="46">
         <f>SUM(J15:J16)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="47">
+      <c r="K17" s="46">
         <f>SUM(K15:K16)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="47">
+      <c r="L17" s="46">
         <f>SUM(L15:L16)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="47">
+      <c r="M17" s="46">
         <f>SUM(M15:M16)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="47">
+      <c r="N17" s="46">
         <f>SUM(N15:N16)</f>
         <v>0</v>
       </c>
-      <c r="O17" s="47">
+      <c r="O17" s="46">
         <f>SUM(O15:O16)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="47">
+      <c r="P17" s="46">
         <f>SUM(P15:P16)</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="47">
+      <c r="Q17" s="46">
         <f>SUM(Q15:Q16)</f>
         <v>0</v>
       </c>
-      <c r="R17" s="47">
+      <c r="R17" s="46">
         <f>SUM(R15:R16)</f>
         <v>0</v>
       </c>
-      <c r="S17" s="47">
+      <c r="S17" s="46">
         <f>SUM(S15:S16)</f>
         <v>0</v>
       </c>
-      <c r="T17" s="47">
+      <c r="T17" s="46">
         <f>SUM(T15:T16)</f>
         <v>0</v>
       </c>
-      <c r="U17" s="47">
+      <c r="U17" s="46">
         <f>SUM(U15:U16)</f>
         <v>0</v>
       </c>
-      <c r="V17" s="47">
+      <c r="V17" s="46">
         <f>SUM(V15:V16)</f>
         <v>0</v>
       </c>
-      <c r="W17" s="47">
+      <c r="W17" s="46">
         <f>SUM(W15:W16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="X17" s="47">
+      <c r="X17" s="46">
         <f>SUM(X15:X16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="Y17" s="47">
+      <c r="Y17" s="46">
         <f>SUM(Y15:Y16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="Z17" s="47">
+      <c r="Z17" s="46">
         <f>SUM(Z15:Z16)</f>
         <v>0</v>
       </c>
-      <c r="AA17" s="47">
+      <c r="AA17" s="46">
         <f>SUM(AA15:AA16)</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="47">
+      <c r="AB17" s="46">
         <f>SUM(AB15:AB16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AC17" s="47">
+      <c r="AC17" s="46">
         <f>SUM(AC15:AC16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AD17" s="47">
+      <c r="AD17" s="46">
         <f>SUM(AD15:AD16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AE17" s="47">
+      <c r="AE17" s="46">
         <f>SUM(AE15:AE16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AF17" s="47">
+      <c r="AF17" s="46">
         <f>SUM(AF15:AF16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AG17" s="47">
+      <c r="AG17" s="46">
         <f>SUM(AG15:AG16)</f>
         <v>0</v>
       </c>
-      <c r="AH17" s="47">
+      <c r="AH17" s="46">
         <f>SUM(AH15:AH16)</f>
         <v>0</v>
       </c>
-      <c r="AI17" s="47">
+      <c r="AI17" s="46">
         <f>SUM(AI15:AI16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AJ17" s="47">
+      <c r="AJ17" s="46">
         <f>SUM(AJ15:AJ16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AK17" s="47">
+      <c r="AK17" s="46">
         <f>SUM(AK15:AK16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AL17" s="47">
+      <c r="AL17" s="46">
         <f>SUM(AL15:AL16)</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AM17" s="47">
+      <c r="AM17" s="46">
         <f>SUM(AM15:AM16)</f>
         <v>0</v>
       </c>
-      <c r="AN17" s="47">
+      <c r="AN17" s="46">
         <f>SUM(AN15:AN16)</f>
         <v>0</v>
       </c>
-      <c r="AO17" s="47">
+      <c r="AO17" s="46">
         <f>SUM(AO15:AO16)</f>
         <v>0</v>
       </c>
-      <c r="AP17" s="47">
+      <c r="AP17" s="46">
         <f>SUM(AP15:AP16)</f>
         <v>0</v>
       </c>
-      <c r="AQ17" s="47">
+      <c r="AQ17" s="46">
         <f>SUM(AQ15:AQ16)</f>
         <v>0</v>
       </c>
-      <c r="AR17" s="47">
+      <c r="AR17" s="46">
         <f>SUM(AR15:AR16)</f>
         <v>0</v>
       </c>
-      <c r="AS17" s="47">
+      <c r="AS17" s="46">
         <f>SUM(AS15:AS16)</f>
         <v>0</v>
       </c>
-      <c r="AT17" s="47">
+      <c r="AT17" s="46">
         <f>SUM(AT15:AT16)</f>
         <v>0</v>
       </c>
-      <c r="AU17" s="47">
+      <c r="AU17" s="46">
         <f>SUM(AU15:AU16)</f>
         <v>0</v>
       </c>
-      <c r="AV17" s="47">
+      <c r="AV17" s="46">
         <f>SUM(AV15:AV16)</f>
         <v>0</v>
       </c>
-      <c r="AW17" s="47">
+      <c r="AW17" s="46">
         <f>SUM(AW15:AW16)</f>
         <v>0</v>
       </c>
-      <c r="AX17" s="47">
+      <c r="AX17" s="46">
         <f>SUM(AX15:AX16)</f>
         <v>0</v>
       </c>
-      <c r="AY17" s="47">
+      <c r="AY17" s="46">
         <f>SUM(AY15:AY16)</f>
         <v>0</v>
       </c>
-      <c r="AZ17" s="47">
+      <c r="AZ17" s="46">
         <f>SUM(AZ15:AZ16)</f>
         <v>0</v>
       </c>
-      <c r="BA17" s="47">
+      <c r="BA17" s="46">
         <f>SUM(BA15:BA16)</f>
         <v>0</v>
       </c>
-      <c r="BB17" s="47">
+      <c r="BB17" s="46">
         <f>SUM(BB15:BB16)</f>
         <v>0</v>
       </c>
-      <c r="BC17" s="47">
+      <c r="BC17" s="46">
         <f>SUM(BC15:BC16)</f>
         <v>0</v>
       </c>
-      <c r="BD17" s="47">
+      <c r="BD17" s="46">
         <f>SUM(BD15:BD16)</f>
         <v>0</v>
       </c>
-      <c r="BE17" s="47">
+      <c r="BE17" s="46">
         <f>SUM(BE15:BE16)</f>
         <v>0</v>
       </c>
-      <c r="BF17" s="47">
+      <c r="BF17" s="46">
         <f>SUM(BF15:BF16)</f>
         <v>0</v>
       </c>
-      <c r="BG17" s="47">
+      <c r="BG17" s="46">
         <f>SUM(BG15:BG16)</f>
         <v>0</v>
       </c>
-      <c r="BH17" s="47">
+      <c r="BH17" s="46">
         <f>SUM(BH15:BH16)</f>
         <v>0</v>
       </c>
-      <c r="BI17" s="47">
+      <c r="BI17" s="46">
         <f>SUM(BI15:BI16)</f>
         <v>0</v>
       </c>
-      <c r="BJ17" s="47">
+      <c r="BJ17" s="46">
         <f>SUM(BJ15:BJ16)</f>
         <v>0</v>
       </c>
-      <c r="BK17" s="47">
+      <c r="BK17" s="46">
         <f>SUM(BK15:BK16)</f>
         <v>0</v>
       </c>
-      <c r="BL17" s="47">
+      <c r="BL17" s="46">
         <f>SUM(BL15:BL16)</f>
         <v>0</v>
       </c>
-      <c r="BM17" s="47">
+      <c r="BM17" s="46">
         <f>SUM(BM15:BM16)</f>
         <v>0</v>
       </c>
-      <c r="BN17" s="47">
+      <c r="BN17" s="46">
         <f>SUM(BN15:BN16)</f>
         <v>0</v>
       </c>
-      <c r="BO17" s="47">
+      <c r="BO17" s="46">
         <f>SUM(BO15:BO16)</f>
         <v>0</v>
       </c>
-      <c r="BP17" s="47">
+      <c r="BP17" s="46">
         <f>SUM(BP15:BP16)</f>
         <v>0</v>
       </c>
-      <c r="BQ17" s="47">
+      <c r="BQ17" s="46">
         <f>SUM(BQ15:BQ16)</f>
         <v>0</v>
       </c>
-      <c r="BR17" s="47">
+      <c r="BR17" s="46">
         <f>SUM(BR15:BR16)</f>
         <v>0</v>
       </c>
-      <c r="BS17" s="47">
+      <c r="BS17" s="46">
         <f>SUM(BS15:BS16)</f>
         <v>0</v>
       </c>
-      <c r="BT17" s="47">
+      <c r="BT17" s="46">
         <f>SUM(BT15:BT16)</f>
         <v>0</v>
       </c>
-      <c r="BU17" s="47">
+      <c r="BU17" s="46">
         <f>SUM(BU15:BU16)</f>
         <v>0</v>
       </c>
-      <c r="BV17" s="47">
+      <c r="BV17" s="46">
         <f>SUM(BV15:BV16)</f>
         <v>0</v>
       </c>
-      <c r="BW17" s="47">
+      <c r="BW17" s="46">
         <f>SUM(BW15:BW16)</f>
         <v>0</v>
       </c>
-      <c r="BX17" s="47">
+      <c r="BX17" s="46">
         <f>SUM(BX15:BX16)</f>
         <v>0</v>
       </c>
-      <c r="BY17" s="47">
+      <c r="BY17" s="46">
         <f>SUM(BY15:BY16)</f>
         <v>0</v>
       </c>
-      <c r="BZ17" s="47">
+      <c r="BZ17" s="46">
         <f>SUM(BZ15:BZ16)</f>
         <v>0</v>
       </c>
-      <c r="CA17" s="47">
+      <c r="CA17" s="46">
         <f>SUM(CA15:CA16)</f>
         <v>0</v>
       </c>
-      <c r="CB17" s="47">
+      <c r="CB17" s="46">
         <f>SUM(CB15:CB16)</f>
         <v>0</v>
       </c>
-      <c r="CC17" s="47">
+      <c r="CC17" s="46">
         <f>SUM(CC15:CC16)</f>
         <v>0</v>
       </c>
-      <c r="CD17" s="47">
+      <c r="CD17" s="46">
         <f>SUM(CD15:CD16)</f>
         <v>0</v>
       </c>
-      <c r="CE17" s="47">
+      <c r="CE17" s="46">
         <f>SUM(CE15:CE16)</f>
         <v>0</v>
       </c>
-      <c r="CF17" s="47">
+      <c r="CF17" s="46">
         <f>SUM(CF15:CF16)</f>
         <v>0</v>
       </c>
-      <c r="CG17" s="47">
+      <c r="CG17" s="46">
         <f>SUM(CG15:CG16)</f>
         <v>0</v>
       </c>
-      <c r="CH17" s="47">
+      <c r="CH17" s="46">
         <f>SUM(CH15:CH16)</f>
         <v>0</v>
       </c>
-      <c r="CI17" s="47">
+      <c r="CI17" s="46">
         <f>SUM(CI15:CI16)</f>
         <v>0</v>
       </c>
-      <c r="CJ17" s="47">
+      <c r="CJ17" s="46">
         <f>SUM(CJ15:CJ16)</f>
         <v>0</v>
       </c>
-      <c r="CK17" s="47">
+      <c r="CK17" s="46">
         <f>SUM(CK15:CK16)</f>
         <v>0</v>
       </c>
-      <c r="CL17" s="47">
+      <c r="CL17" s="46">
         <f>SUM(CL15:CL16)</f>
         <v>0</v>
       </c>
-      <c r="CM17" s="47">
+      <c r="CM17" s="46">
         <f>SUM(CM15:CM16)</f>
         <v>0</v>
       </c>
-      <c r="CN17" s="47">
+      <c r="CN17" s="46">
         <f>SUM(CN15:CN16)</f>
         <v>0</v>
       </c>
-      <c r="CO17" s="47">
+      <c r="CO17" s="46">
         <f>SUM(CO15:CO16)</f>
         <v>0</v>
       </c>
-      <c r="CP17" s="47">
+      <c r="CP17" s="46">
         <f>SUM(CP15:CP16)</f>
         <v>0</v>
       </c>
-      <c r="CQ17" s="47">
+      <c r="CQ17" s="46">
         <f>SUM(CQ15:CQ16)</f>
         <v>0</v>
       </c>
-      <c r="CR17" s="47">
+      <c r="CR17" s="46">
         <f>SUM(CR15:CR16)</f>
         <v>0</v>
       </c>
-      <c r="CS17" s="47">
+      <c r="CS17" s="46">
         <f>SUM(CS15:CS16)</f>
         <v>0</v>
       </c>
-      <c r="CT17" s="47">
+      <c r="CT17" s="46">
         <f>SUM(CT15:CT16)</f>
         <v>0</v>
       </c>
-      <c r="CU17" s="47">
+      <c r="CU17" s="46">
         <f>SUM(CU15:CU16)</f>
         <v>0</v>
       </c>
-      <c r="CV17" s="47">
+      <c r="CV17" s="46">
         <f>SUM(CV15:CV16)</f>
         <v>0</v>
       </c>
-      <c r="CW17" s="47">
+      <c r="CW17" s="46">
         <f>SUM(CW15:CW16)</f>
         <v>0</v>
       </c>
-      <c r="CX17" s="47">
+      <c r="CX17" s="46">
         <f>SUM(CX15:CX16)</f>
         <v>0</v>
       </c>
-      <c r="CY17" s="47">
+      <c r="CY17" s="46">
         <f>SUM(CY15:CY16)</f>
         <v>0</v>
       </c>
-      <c r="CZ17" s="47">
+      <c r="CZ17" s="46">
         <f>SUM(CZ15:CZ16)</f>
         <v>0</v>
       </c>
-      <c r="DA17" s="47">
+      <c r="DA17" s="46">
         <f>SUM(DA15:DA16)</f>
         <v>0</v>
       </c>
-      <c r="DB17" s="47">
+      <c r="DB17" s="46">
         <f>SUM(DB15:DB16)</f>
         <v>0</v>
       </c>
-      <c r="DC17" s="47">
+      <c r="DC17" s="46">
         <f>SUM(DC15:DC16)</f>
         <v>0</v>
       </c>
-      <c r="DD17" s="47">
+      <c r="DD17" s="46">
         <f>SUM(DD15:DD16)</f>
         <v>0</v>
       </c>
-      <c r="DE17" s="47">
+      <c r="DE17" s="46">
         <f>SUM(DE15:DE16)</f>
         <v>0</v>
       </c>
-      <c r="DF17" s="47">
+      <c r="DF17" s="46">
         <f>SUM(DF15:DF16)</f>
         <v>0</v>
       </c>
-      <c r="DG17" s="47">
+      <c r="DG17" s="46">
         <f>SUM(DG15:DG16)</f>
         <v>0</v>
       </c>
-      <c r="DH17" s="47">
+      <c r="DH17" s="46">
         <f>SUM(DH15:DH16)</f>
         <v>0</v>
       </c>
-      <c r="DI17" s="47">
+      <c r="DI17" s="46">
         <f>SUM(DI15:DI16)</f>
         <v>0</v>
       </c>
-      <c r="DJ17" s="47">
+      <c r="DJ17" s="46">
         <f>SUM(DJ15:DJ16)</f>
         <v>0</v>
       </c>
-      <c r="DK17" s="47">
+      <c r="DK17" s="46">
         <f>SUM(DK15:DK16)</f>
         <v>0</v>
       </c>
-      <c r="DL17" s="47">
+      <c r="DL17" s="46">
         <f>SUM(DL15:DL16)</f>
         <v>0</v>
       </c>
-      <c r="DM17" s="47">
+      <c r="DM17" s="46">
         <f>SUM(DM15:DM16)</f>
         <v>0</v>
       </c>
-      <c r="DN17" s="47">
+      <c r="DN17" s="46">
         <f>SUM(DN15:DN16)</f>
         <v>0</v>
       </c>
-      <c r="DO17" s="47">
+      <c r="DO17" s="46">
         <f>SUM(DO15:DO16)</f>
         <v>0</v>
       </c>
-      <c r="DP17" s="47">
+      <c r="DP17" s="46">
         <f>SUM(DP15:DP16)</f>
         <v>0</v>
       </c>
-      <c r="DQ17" s="47">
+      <c r="DQ17" s="46">
         <f>SUM(DQ15:DQ16)</f>
         <v>0</v>
       </c>
-      <c r="DR17" s="47">
+      <c r="DR17" s="46">
         <f>SUM(DR15:DR16)</f>
         <v>0</v>
       </c>
-      <c r="DS17" s="47">
+      <c r="DS17" s="46">
         <f>SUM(DS15:DS16)</f>
         <v>0</v>
       </c>
-      <c r="DT17" s="47">
+      <c r="DT17" s="46">
         <f>SUM(DT15:DT16)</f>
         <v>0</v>
       </c>
-      <c r="DU17" s="47">
+      <c r="DU17" s="46">
         <f>SUM(DU15:DU16)</f>
         <v>0</v>
       </c>
-      <c r="DV17" s="47">
+      <c r="DV17" s="46">
         <f>SUM(DV15:DV16)</f>
         <v>0</v>
       </c>
-      <c r="DW17" s="47">
+      <c r="DW17" s="46">
         <f>SUM(DW15:DW16)</f>
         <v>0</v>
       </c>
-      <c r="DX17" s="47">
+      <c r="DX17" s="46">
         <f>SUM(DX15:DX16)</f>
         <v>0</v>
       </c>
-      <c r="DY17" s="47">
+      <c r="DY17" s="46">
         <f>SUM(DY15:DY16)</f>
         <v>0</v>
       </c>
-      <c r="DZ17" s="47">
+      <c r="DZ17" s="46">
         <f>SUM(DZ15:DZ16)</f>
         <v>0</v>
       </c>
-      <c r="EA17" s="47">
+      <c r="EA17" s="46">
         <f>SUM(EA15:EA16)</f>
         <v>0</v>
       </c>
-      <c r="EB17" s="47">
+      <c r="EB17" s="46">
         <f>SUM(EB15:EB16)</f>
         <v>0</v>
       </c>
-      <c r="EC17" s="47">
+      <c r="EC17" s="46">
         <f>SUM(EC15:EC16)</f>
         <v>0</v>
       </c>
-      <c r="ED17" s="47">
+      <c r="ED17" s="46">
         <f>SUM(ED15:ED16)</f>
         <v>0</v>
       </c>
-      <c r="EE17" s="47">
+      <c r="EE17" s="46">
         <f>SUM(EE15:EE16)</f>
         <v>0</v>
       </c>
-      <c r="EF17" s="47">
+      <c r="EF17" s="46">
         <f>SUM(EF15:EF16)</f>
         <v>0</v>
       </c>
-      <c r="EG17" s="47">
+      <c r="EG17" s="46">
         <f>SUM(EG15:EG16)</f>
         <v>0</v>
       </c>
-      <c r="EH17" s="47">
+      <c r="EH17" s="46">
         <f>SUM(EH15:EH16)</f>
         <v>0</v>
       </c>
-      <c r="EI17" s="47">
+      <c r="EI17" s="46">
         <f>SUM(EI15:EI16)</f>
         <v>0</v>
       </c>
-      <c r="EJ17" s="47">
+      <c r="EJ17" s="46">
         <f>SUM(EJ15:EJ16)</f>
         <v>0</v>
       </c>
-      <c r="EK17" s="47">
+      <c r="EK17" s="46">
         <f>SUM(EK15:EK16)</f>
         <v>0</v>
       </c>
-      <c r="EL17" s="47">
+      <c r="EL17" s="46">
         <f>SUM(EL15:EL16)</f>
         <v>0</v>
       </c>
-      <c r="EM17" s="47">
+      <c r="EM17" s="46">
         <f>SUM(EM15:EM16)</f>
         <v>0</v>
       </c>
-      <c r="EN17" s="47">
+      <c r="EN17" s="46">
         <f>SUM(EN15:EN16)</f>
         <v>0</v>
       </c>
-      <c r="EO17" s="47">
+      <c r="EO17" s="46">
         <f>SUM(EO15:EO16)</f>
         <v>0</v>
       </c>
-      <c r="EP17" s="47">
+      <c r="EP17" s="46">
         <f>SUM(EP15:EP16)</f>
         <v>0</v>
       </c>
-      <c r="EQ17" s="47">
+      <c r="EQ17" s="46">
         <f>SUM(EQ15:EQ16)</f>
         <v>0</v>
       </c>
-      <c r="ER17" s="47">
+      <c r="ER17" s="46">
         <f>SUM(ER15:ER16)</f>
         <v>0</v>
       </c>
-      <c r="ES17" s="47">
+      <c r="ES17" s="46">
         <f>SUM(ES15:ES16)</f>
         <v>0</v>
       </c>
-      <c r="ET17" s="47">
+      <c r="ET17" s="46">
         <f>SUM(ET15:ET16)</f>
         <v>0</v>
       </c>
-      <c r="EU17" s="47">
+      <c r="EU17" s="46">
         <f>SUM(EU15:EU16)</f>
         <v>0</v>
       </c>
-      <c r="EV17" s="47">
+      <c r="EV17" s="46">
         <f>SUM(EV15:EV16)</f>
         <v>0</v>
       </c>
-      <c r="EW17" s="47">
+      <c r="EW17" s="46">
         <f>SUM(EW15:EW16)</f>
         <v>0</v>
       </c>
-      <c r="EX17" s="47">
+      <c r="EX17" s="46">
         <f>SUM(EX15:EX16)</f>
         <v>0</v>
       </c>
-      <c r="EY17" s="72">
+      <c r="EY17" s="68">
         <f t="shared" si="72"/>
         <v>1.0833333333333333</v>
       </c>
     </row>
-    <row r="18" spans="1:155" ht="34.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="59" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="32"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="32"/>
-      <c r="T18" s="32"/>
-      <c r="U18" s="32"/>
-      <c r="V18" s="32"/>
-      <c r="W18" s="32"/>
-      <c r="X18" s="32"/>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="32"/>
-      <c r="AA18" s="32"/>
-      <c r="AB18" s="32"/>
-      <c r="AC18" s="32"/>
-      <c r="AD18" s="32"/>
-      <c r="AE18" s="32"/>
-      <c r="AF18" s="32"/>
-      <c r="AG18" s="32"/>
-      <c r="AH18" s="32"/>
-      <c r="AI18" s="32"/>
-      <c r="AJ18" s="32"/>
-      <c r="AK18" s="32"/>
-      <c r="AL18" s="32"/>
-      <c r="AM18" s="66">
+    <row r="18" spans="1:155" ht="34.35" customHeight="1">
+      <c r="A18" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="31"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="31"/>
+      <c r="AE18" s="31"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="31"/>
+      <c r="AH18" s="31"/>
+      <c r="AI18" s="31"/>
+      <c r="AJ18" s="31"/>
+      <c r="AK18" s="31"/>
+      <c r="AL18" s="31"/>
+      <c r="AM18" s="62">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AN18" s="63"/>
-      <c r="AO18" s="62"/>
-      <c r="AP18" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="AQ18" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="AR18" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="AS18" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="AT18" s="32"/>
-      <c r="AU18" s="32"/>
-      <c r="AV18" s="32"/>
-      <c r="AW18" s="32"/>
-      <c r="AX18" s="32"/>
-      <c r="AY18" s="32"/>
-      <c r="AZ18" s="32"/>
-      <c r="BA18" s="32"/>
-      <c r="BB18" s="32"/>
-      <c r="BC18" s="32"/>
-      <c r="BD18" s="32"/>
-      <c r="BE18" s="32"/>
-      <c r="BF18" s="32"/>
-      <c r="BG18" s="32"/>
-      <c r="BH18" s="32"/>
-      <c r="BI18" s="32"/>
-      <c r="BJ18" s="32"/>
-      <c r="BK18" s="32"/>
-      <c r="BL18" s="32"/>
-      <c r="BM18" s="32"/>
-      <c r="BN18" s="32"/>
-      <c r="BO18" s="32"/>
-      <c r="BP18" s="32"/>
-      <c r="BQ18" s="32"/>
-      <c r="BR18" s="32"/>
-      <c r="BS18" s="32"/>
-      <c r="BT18" s="32"/>
-      <c r="BU18" s="32"/>
-      <c r="BV18" s="32"/>
-      <c r="BW18" s="32"/>
-      <c r="BX18" s="32"/>
-      <c r="BY18" s="32"/>
-      <c r="BZ18" s="32"/>
-      <c r="CA18" s="32"/>
-      <c r="CB18" s="32"/>
-      <c r="CC18" s="32"/>
-      <c r="CD18" s="32"/>
-      <c r="CE18" s="32"/>
-      <c r="CF18" s="32"/>
-      <c r="CG18" s="32"/>
-      <c r="CH18" s="32"/>
-      <c r="CI18" s="32"/>
-      <c r="CJ18" s="32"/>
-      <c r="CK18" s="32"/>
-      <c r="CL18" s="32"/>
-      <c r="CM18" s="32"/>
-      <c r="CN18" s="32"/>
-      <c r="CO18" s="32"/>
-      <c r="CP18" s="32"/>
-      <c r="CQ18" s="32"/>
-      <c r="CR18" s="32"/>
-      <c r="CS18" s="32"/>
-      <c r="CT18" s="32"/>
-      <c r="CU18" s="32"/>
-      <c r="CV18" s="32"/>
-      <c r="CW18" s="32"/>
-      <c r="CX18" s="32"/>
-      <c r="CY18" s="32"/>
-      <c r="CZ18" s="32"/>
-      <c r="DA18" s="32"/>
-      <c r="DB18" s="32"/>
-      <c r="DC18" s="32"/>
-      <c r="DD18" s="32"/>
-      <c r="DE18" s="32"/>
-      <c r="DF18" s="32"/>
-      <c r="DG18" s="32"/>
-      <c r="DH18" s="32"/>
-      <c r="DI18" s="32"/>
-      <c r="DJ18" s="32"/>
-      <c r="DK18" s="32"/>
-      <c r="DL18" s="32"/>
-      <c r="DM18" s="32"/>
-      <c r="DN18" s="32"/>
-      <c r="DO18" s="32"/>
-      <c r="DP18" s="32"/>
-      <c r="DQ18" s="32"/>
-      <c r="DR18" s="32"/>
-      <c r="DS18" s="32"/>
-      <c r="DT18" s="32"/>
-      <c r="DU18" s="32"/>
-      <c r="DV18" s="32"/>
-      <c r="DW18" s="32"/>
-      <c r="DX18" s="32"/>
-      <c r="DY18" s="32"/>
-      <c r="DZ18" s="32"/>
-      <c r="EA18" s="32"/>
-      <c r="EB18" s="32"/>
-      <c r="EC18" s="32"/>
-      <c r="ED18" s="32"/>
-      <c r="EE18" s="32"/>
-      <c r="EF18" s="32"/>
-      <c r="EG18" s="32"/>
-      <c r="EH18" s="32"/>
-      <c r="EI18" s="32"/>
-      <c r="EJ18" s="32"/>
-      <c r="EK18" s="32"/>
-      <c r="EL18" s="32"/>
-      <c r="EM18" s="32"/>
-      <c r="EN18" s="32"/>
-      <c r="EO18" s="32"/>
-      <c r="EP18" s="32"/>
-      <c r="EQ18" s="32"/>
-      <c r="ER18" s="32"/>
-      <c r="ES18" s="32"/>
-      <c r="ET18" s="32"/>
-      <c r="EU18" s="32"/>
-      <c r="EV18" s="32"/>
-      <c r="EW18" s="32"/>
-      <c r="EX18" s="32"/>
-      <c r="EY18" s="72">
+      <c r="AN18" s="59"/>
+      <c r="AO18" s="58"/>
+      <c r="AP18" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AQ18" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AR18" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AS18" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AT18" s="31"/>
+      <c r="AU18" s="31"/>
+      <c r="AV18" s="31"/>
+      <c r="AW18" s="31"/>
+      <c r="AX18" s="31"/>
+      <c r="AY18" s="31"/>
+      <c r="AZ18" s="31"/>
+      <c r="BA18" s="31"/>
+      <c r="BB18" s="31"/>
+      <c r="BC18" s="31"/>
+      <c r="BD18" s="31"/>
+      <c r="BE18" s="31"/>
+      <c r="BF18" s="31"/>
+      <c r="BG18" s="31"/>
+      <c r="BH18" s="31"/>
+      <c r="BI18" s="31"/>
+      <c r="BJ18" s="31"/>
+      <c r="BK18" s="31"/>
+      <c r="BL18" s="31"/>
+      <c r="BM18" s="31"/>
+      <c r="BN18" s="31"/>
+      <c r="BO18" s="31"/>
+      <c r="BP18" s="31"/>
+      <c r="BQ18" s="31"/>
+      <c r="BR18" s="31"/>
+      <c r="BS18" s="31"/>
+      <c r="BT18" s="31"/>
+      <c r="BU18" s="31"/>
+      <c r="BV18" s="31"/>
+      <c r="BW18" s="31"/>
+      <c r="BX18" s="31"/>
+      <c r="BY18" s="31"/>
+      <c r="BZ18" s="31"/>
+      <c r="CA18" s="31"/>
+      <c r="CB18" s="31"/>
+      <c r="CC18" s="31"/>
+      <c r="CD18" s="31"/>
+      <c r="CE18" s="31"/>
+      <c r="CF18" s="31"/>
+      <c r="CG18" s="31"/>
+      <c r="CH18" s="31"/>
+      <c r="CI18" s="31"/>
+      <c r="CJ18" s="31"/>
+      <c r="CK18" s="31"/>
+      <c r="CL18" s="31"/>
+      <c r="CM18" s="31"/>
+      <c r="CN18" s="31"/>
+      <c r="CO18" s="31"/>
+      <c r="CP18" s="31"/>
+      <c r="CQ18" s="31"/>
+      <c r="CR18" s="31"/>
+      <c r="CS18" s="31"/>
+      <c r="CT18" s="31"/>
+      <c r="CU18" s="31"/>
+      <c r="CV18" s="31"/>
+      <c r="CW18" s="31"/>
+      <c r="CX18" s="31"/>
+      <c r="CY18" s="31"/>
+      <c r="CZ18" s="31"/>
+      <c r="DA18" s="31"/>
+      <c r="DB18" s="31"/>
+      <c r="DC18" s="31"/>
+      <c r="DD18" s="31"/>
+      <c r="DE18" s="31"/>
+      <c r="DF18" s="31"/>
+      <c r="DG18" s="31"/>
+      <c r="DH18" s="31"/>
+      <c r="DI18" s="31"/>
+      <c r="DJ18" s="31"/>
+      <c r="DK18" s="31"/>
+      <c r="DL18" s="31"/>
+      <c r="DM18" s="31"/>
+      <c r="DN18" s="31"/>
+      <c r="DO18" s="31"/>
+      <c r="DP18" s="31"/>
+      <c r="DQ18" s="31"/>
+      <c r="DR18" s="31"/>
+      <c r="DS18" s="31"/>
+      <c r="DT18" s="31"/>
+      <c r="DU18" s="31"/>
+      <c r="DV18" s="31"/>
+      <c r="DW18" s="31"/>
+      <c r="DX18" s="31"/>
+      <c r="DY18" s="31"/>
+      <c r="DZ18" s="31"/>
+      <c r="EA18" s="31"/>
+      <c r="EB18" s="31"/>
+      <c r="EC18" s="31"/>
+      <c r="ED18" s="31"/>
+      <c r="EE18" s="31"/>
+      <c r="EF18" s="31"/>
+      <c r="EG18" s="31"/>
+      <c r="EH18" s="31"/>
+      <c r="EI18" s="31"/>
+      <c r="EJ18" s="31"/>
+      <c r="EK18" s="31"/>
+      <c r="EL18" s="31"/>
+      <c r="EM18" s="31"/>
+      <c r="EN18" s="31"/>
+      <c r="EO18" s="31"/>
+      <c r="EP18" s="31"/>
+      <c r="EQ18" s="31"/>
+      <c r="ER18" s="31"/>
+      <c r="ES18" s="31"/>
+      <c r="ET18" s="31"/>
+      <c r="EU18" s="31"/>
+      <c r="EV18" s="31"/>
+      <c r="EW18" s="31"/>
+      <c r="EX18" s="31"/>
+      <c r="EY18" s="68">
         <f>SUM(C18:EX18)</f>
         <v>0.91666666666666674</v>
       </c>
     </row>
-    <row r="19" spans="1:155" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="54"/>
-      <c r="B19" s="59" t="s">
+    <row r="19" spans="1:155" ht="31.15">
+      <c r="A19" s="71"/>
+      <c r="B19" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="32"/>
-      <c r="R19" s="32"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="32"/>
-      <c r="U19" s="32"/>
-      <c r="V19" s="32"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="32"/>
-      <c r="Z19" s="32"/>
-      <c r="AA19" s="32"/>
-      <c r="AB19" s="32"/>
-      <c r="AC19" s="32"/>
-      <c r="AD19" s="32"/>
-      <c r="AE19" s="32"/>
-      <c r="AF19" s="32"/>
-      <c r="AG19" s="32"/>
-      <c r="AH19" s="32"/>
-      <c r="AI19" s="32"/>
-      <c r="AJ19" s="32"/>
-      <c r="AK19" s="32"/>
-      <c r="AL19" s="32"/>
-      <c r="AM19" s="32"/>
-      <c r="AN19" s="32"/>
-      <c r="AO19" s="32"/>
-      <c r="AP19" s="32"/>
-      <c r="AQ19" s="32"/>
-      <c r="AR19" s="32"/>
-      <c r="AS19" s="32"/>
-      <c r="AT19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="AU19" s="63"/>
-      <c r="AV19" s="62"/>
-      <c r="AW19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="AX19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="AY19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="AZ19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BA19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BB19" s="63"/>
-      <c r="BC19" s="62"/>
-      <c r="BD19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BE19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BF19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BG19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BH19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BI19" s="63"/>
-      <c r="BJ19" s="62"/>
-      <c r="BK19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BL19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BM19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BN19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BO19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BP19" s="63"/>
-      <c r="BQ19" s="62"/>
-      <c r="BR19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BS19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BT19" s="69">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BU19" s="69">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BV19" s="69">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BW19" s="63"/>
-      <c r="BX19" s="62"/>
-      <c r="BY19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="BZ19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CA19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CB19" s="69">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CC19" s="69">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CD19" s="63"/>
-      <c r="CE19" s="62"/>
-      <c r="CF19" s="69">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CG19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CH19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CI19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CJ19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CK19" s="63"/>
-      <c r="CL19" s="62"/>
-      <c r="CM19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CN19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CO19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CP19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CQ19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CR19" s="63"/>
-      <c r="CS19" s="62"/>
-      <c r="CT19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CU19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CV19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CW19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CX19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="CY19" s="63"/>
-      <c r="CZ19" s="62"/>
-      <c r="DA19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DB19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DC19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DD19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DE19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DF19" s="63"/>
-      <c r="DG19" s="62"/>
-      <c r="DH19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DI19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DJ19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DK19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DL19" s="68">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DM19" s="63"/>
-      <c r="DN19" s="62"/>
-      <c r="DO19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DP19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DQ19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DR19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DS19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DT19" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="DU19" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="DV19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DW19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DX19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DY19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="DZ19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="EA19" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EB19" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EC19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="ED19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="EE19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="EF19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="EG19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="EH19" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EI19" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EJ19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="EK19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="EL19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="EM19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="EN19" s="66">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="EO19" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EP19" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EQ19" s="70"/>
-      <c r="ER19" s="70"/>
-      <c r="ES19" s="70"/>
-      <c r="ET19" s="70"/>
-      <c r="EU19" s="70"/>
-      <c r="EV19" s="70"/>
-      <c r="EW19" s="70"/>
-      <c r="EX19" s="32"/>
-      <c r="EY19" s="72">
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="31"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="31"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="31"/>
+      <c r="AB19" s="31"/>
+      <c r="AC19" s="31"/>
+      <c r="AD19" s="31"/>
+      <c r="AE19" s="31"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="31"/>
+      <c r="AH19" s="31"/>
+      <c r="AI19" s="31"/>
+      <c r="AJ19" s="31"/>
+      <c r="AK19" s="31"/>
+      <c r="AL19" s="31"/>
+      <c r="AM19" s="31"/>
+      <c r="AN19" s="31"/>
+      <c r="AO19" s="31"/>
+      <c r="AP19" s="31"/>
+      <c r="AQ19" s="31"/>
+      <c r="AR19" s="31"/>
+      <c r="AS19" s="31"/>
+      <c r="AT19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AU19" s="59"/>
+      <c r="AV19" s="58"/>
+      <c r="AW19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AX19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AY19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AZ19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BA19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BB19" s="59"/>
+      <c r="BC19" s="58"/>
+      <c r="BD19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BE19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BF19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BG19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BH19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BI19" s="59"/>
+      <c r="BJ19" s="58"/>
+      <c r="BK19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BL19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BM19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BN19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BO19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BP19" s="59"/>
+      <c r="BQ19" s="58"/>
+      <c r="BR19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BS19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BT19" s="65">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BU19" s="65">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BV19" s="65">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BW19" s="59"/>
+      <c r="BX19" s="58"/>
+      <c r="BY19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="BZ19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CA19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CB19" s="65">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CC19" s="65">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CD19" s="59"/>
+      <c r="CE19" s="58"/>
+      <c r="CF19" s="65">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CG19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CH19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CI19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CJ19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CK19" s="59"/>
+      <c r="CL19" s="58"/>
+      <c r="CM19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CN19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CO19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CP19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CQ19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CR19" s="59"/>
+      <c r="CS19" s="58"/>
+      <c r="CT19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CU19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CV19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CW19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CX19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="CY19" s="59"/>
+      <c r="CZ19" s="58"/>
+      <c r="DA19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DB19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DC19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DD19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DE19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DF19" s="59"/>
+      <c r="DG19" s="58"/>
+      <c r="DH19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DI19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DJ19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DK19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DL19" s="64">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DM19" s="59"/>
+      <c r="DN19" s="58"/>
+      <c r="DO19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DP19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DQ19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DR19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DS19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DT19" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="DU19" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="DV19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DW19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DX19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DY19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="DZ19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="EA19" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EB19" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EC19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="ED19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="EE19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="EF19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="EG19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="EH19" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EI19" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EJ19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="EK19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="EL19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="EM19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="EN19" s="62">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="EO19" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EP19" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EQ19" s="66"/>
+      <c r="ER19" s="66"/>
+      <c r="ES19" s="66"/>
+      <c r="ET19" s="66"/>
+      <c r="EU19" s="66"/>
+      <c r="EV19" s="66"/>
+      <c r="EW19" s="66"/>
+      <c r="EX19" s="31"/>
+      <c r="EY19" s="68">
         <f t="shared" ref="EY19" si="73">SUM(C19:EX19)</f>
         <v>15.791666666666682</v>
       </c>
     </row>
-    <row r="20" spans="1:155" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="54"/>
-      <c r="B20" s="59" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="32"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="32"/>
-      <c r="U20" s="32"/>
-      <c r="V20" s="32"/>
-      <c r="W20" s="32"/>
-      <c r="X20" s="32"/>
-      <c r="Y20" s="32"/>
-      <c r="Z20" s="32"/>
-      <c r="AA20" s="32"/>
-      <c r="AB20" s="32"/>
-      <c r="AC20" s="32"/>
-      <c r="AD20" s="32"/>
-      <c r="AE20" s="32"/>
-      <c r="AF20" s="32"/>
-      <c r="AG20" s="32"/>
-      <c r="AH20" s="32"/>
-      <c r="AI20" s="32"/>
-      <c r="AJ20" s="32"/>
-      <c r="AK20" s="32"/>
-      <c r="AL20" s="32"/>
-      <c r="AM20" s="32"/>
-      <c r="AN20" s="32"/>
-      <c r="AO20" s="32"/>
-      <c r="AP20" s="32"/>
-      <c r="AQ20" s="32"/>
-      <c r="AR20" s="32"/>
-      <c r="AS20" s="32"/>
-      <c r="AT20" s="32"/>
-      <c r="AU20" s="32"/>
-      <c r="AV20" s="32"/>
-      <c r="AW20" s="32"/>
-      <c r="AX20" s="32"/>
-      <c r="AY20" s="32"/>
-      <c r="AZ20" s="32"/>
-      <c r="BA20" s="66">
+    <row r="20" spans="1:155" ht="31.15">
+      <c r="A20" s="71"/>
+      <c r="B20" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="31"/>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="31"/>
+      <c r="AE20" s="31"/>
+      <c r="AF20" s="31"/>
+      <c r="AG20" s="31"/>
+      <c r="AH20" s="31"/>
+      <c r="AI20" s="31"/>
+      <c r="AJ20" s="31"/>
+      <c r="AK20" s="31"/>
+      <c r="AL20" s="31"/>
+      <c r="AM20" s="31"/>
+      <c r="AN20" s="31"/>
+      <c r="AO20" s="31"/>
+      <c r="AP20" s="31"/>
+      <c r="AQ20" s="31"/>
+      <c r="AR20" s="31"/>
+      <c r="AS20" s="31"/>
+      <c r="AT20" s="31"/>
+      <c r="AU20" s="31"/>
+      <c r="AV20" s="31"/>
+      <c r="AW20" s="31"/>
+      <c r="AX20" s="31"/>
+      <c r="AY20" s="31"/>
+      <c r="AZ20" s="31"/>
+      <c r="BA20" s="62">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="BB20" s="32"/>
-      <c r="BC20" s="32"/>
-      <c r="BD20" s="32"/>
-      <c r="BE20" s="32"/>
-      <c r="BF20" s="32"/>
-      <c r="BG20" s="32"/>
-      <c r="BH20" s="66">
+      <c r="BB20" s="31"/>
+      <c r="BC20" s="31"/>
+      <c r="BD20" s="31"/>
+      <c r="BE20" s="31"/>
+      <c r="BF20" s="31"/>
+      <c r="BG20" s="31"/>
+      <c r="BH20" s="62">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="BI20" s="32"/>
-      <c r="BJ20" s="32"/>
-      <c r="BK20" s="32"/>
-      <c r="BL20" s="32"/>
-      <c r="BM20" s="32"/>
-      <c r="BN20" s="32"/>
-      <c r="BO20" s="66">
+      <c r="BI20" s="31"/>
+      <c r="BJ20" s="31"/>
+      <c r="BK20" s="31"/>
+      <c r="BL20" s="31"/>
+      <c r="BM20" s="31"/>
+      <c r="BN20" s="31"/>
+      <c r="BO20" s="62">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="BP20" s="32"/>
-      <c r="BQ20" s="32"/>
-      <c r="BR20" s="32"/>
-      <c r="BS20" s="32"/>
-      <c r="BT20" s="32"/>
-      <c r="BU20" s="32"/>
-      <c r="BV20" s="66">
+      <c r="BP20" s="31"/>
+      <c r="BQ20" s="31"/>
+      <c r="BR20" s="31"/>
+      <c r="BS20" s="31"/>
+      <c r="BT20" s="31"/>
+      <c r="BU20" s="31"/>
+      <c r="BV20" s="62">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="BW20" s="32"/>
-      <c r="BX20" s="32"/>
-      <c r="BY20" s="32"/>
-      <c r="BZ20" s="32"/>
-      <c r="CA20" s="32"/>
-      <c r="CB20" s="32"/>
-      <c r="CC20" s="32"/>
-      <c r="CD20" s="32"/>
-      <c r="CE20" s="32"/>
-      <c r="CF20" s="32"/>
-      <c r="CG20" s="32"/>
-      <c r="CH20" s="32"/>
-      <c r="CI20" s="32"/>
-      <c r="CJ20" s="68">
+      <c r="BW20" s="31"/>
+      <c r="BX20" s="31"/>
+      <c r="BY20" s="31"/>
+      <c r="BZ20" s="31"/>
+      <c r="CA20" s="31"/>
+      <c r="CB20" s="31"/>
+      <c r="CC20" s="31"/>
+      <c r="CD20" s="31"/>
+      <c r="CE20" s="31"/>
+      <c r="CF20" s="31"/>
+      <c r="CG20" s="31"/>
+      <c r="CH20" s="31"/>
+      <c r="CI20" s="31"/>
+      <c r="CJ20" s="64">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="CK20" s="32"/>
-      <c r="CL20" s="32"/>
-      <c r="CM20" s="32"/>
-      <c r="CN20" s="32"/>
-      <c r="CO20" s="32"/>
-      <c r="CP20" s="32"/>
-      <c r="CQ20" s="32"/>
-      <c r="CR20" s="32"/>
-      <c r="CS20" s="32"/>
-      <c r="CT20" s="32"/>
-      <c r="CU20" s="32"/>
-      <c r="CV20" s="32"/>
-      <c r="CW20" s="32"/>
-      <c r="CX20" s="32"/>
-      <c r="CY20" s="32"/>
-      <c r="CZ20" s="32"/>
-      <c r="DA20" s="32"/>
-      <c r="DB20" s="32"/>
-      <c r="DC20" s="32"/>
-      <c r="DD20" s="32"/>
-      <c r="DE20" s="68">
+      <c r="CK20" s="31"/>
+      <c r="CL20" s="31"/>
+      <c r="CM20" s="31"/>
+      <c r="CN20" s="31"/>
+      <c r="CO20" s="31"/>
+      <c r="CP20" s="31"/>
+      <c r="CQ20" s="31"/>
+      <c r="CR20" s="31"/>
+      <c r="CS20" s="31"/>
+      <c r="CT20" s="31"/>
+      <c r="CU20" s="31"/>
+      <c r="CV20" s="31"/>
+      <c r="CW20" s="31"/>
+      <c r="CX20" s="31"/>
+      <c r="CY20" s="31"/>
+      <c r="CZ20" s="31"/>
+      <c r="DA20" s="31"/>
+      <c r="DB20" s="31"/>
+      <c r="DC20" s="31"/>
+      <c r="DD20" s="31"/>
+      <c r="DE20" s="64">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="DF20" s="32"/>
-      <c r="DG20" s="32"/>
-      <c r="DH20" s="32"/>
-      <c r="DI20" s="32"/>
-      <c r="DJ20" s="32"/>
-      <c r="DK20" s="32"/>
-      <c r="DL20" s="68">
+      <c r="DF20" s="31"/>
+      <c r="DG20" s="31"/>
+      <c r="DH20" s="31"/>
+      <c r="DI20" s="31"/>
+      <c r="DJ20" s="31"/>
+      <c r="DK20" s="31"/>
+      <c r="DL20" s="64">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="DM20" s="32"/>
-      <c r="DN20" s="32"/>
-      <c r="DO20" s="32"/>
-      <c r="DP20" s="32"/>
-      <c r="DQ20" s="32"/>
-      <c r="DR20" s="32"/>
-      <c r="DS20" s="32"/>
-      <c r="DT20" s="66">
+      <c r="DM20" s="31"/>
+      <c r="DN20" s="31"/>
+      <c r="DO20" s="31"/>
+      <c r="DP20" s="31"/>
+      <c r="DQ20" s="31"/>
+      <c r="DR20" s="31"/>
+      <c r="DS20" s="31"/>
+      <c r="DT20" s="62">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="DU20" s="32"/>
-      <c r="DV20" s="32"/>
-      <c r="DW20" s="32"/>
-      <c r="DX20" s="32"/>
-      <c r="DY20" s="32"/>
-      <c r="DZ20" s="32"/>
-      <c r="EA20" s="32"/>
-      <c r="EB20" s="32"/>
-      <c r="EC20" s="66">
+      <c r="DU20" s="31"/>
+      <c r="DV20" s="31"/>
+      <c r="DW20" s="31"/>
+      <c r="DX20" s="31"/>
+      <c r="DY20" s="31"/>
+      <c r="DZ20" s="31"/>
+      <c r="EA20" s="31"/>
+      <c r="EB20" s="31"/>
+      <c r="EC20" s="62">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="ED20" s="32"/>
-      <c r="EE20" s="32"/>
-      <c r="EF20" s="32"/>
-      <c r="EG20" s="32"/>
-      <c r="EH20" s="32"/>
-      <c r="EI20" s="32"/>
-      <c r="EJ20" s="66">
+      <c r="ED20" s="31"/>
+      <c r="EE20" s="31"/>
+      <c r="EF20" s="31"/>
+      <c r="EG20" s="31"/>
+      <c r="EH20" s="31"/>
+      <c r="EI20" s="31"/>
+      <c r="EJ20" s="62">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="EK20" s="32"/>
-      <c r="EL20" s="32"/>
-      <c r="EM20" s="32"/>
-      <c r="EN20" s="32"/>
-      <c r="EO20" s="32"/>
-      <c r="EP20" s="32"/>
-      <c r="EQ20" s="32"/>
-      <c r="ER20" s="32"/>
-      <c r="ES20" s="32"/>
-      <c r="ET20" s="32"/>
-      <c r="EU20" s="32"/>
-      <c r="EV20" s="32"/>
-      <c r="EW20" s="32"/>
-      <c r="EX20" s="32"/>
-      <c r="EY20" s="72">
+      <c r="EK20" s="31"/>
+      <c r="EL20" s="31"/>
+      <c r="EM20" s="31"/>
+      <c r="EN20" s="31"/>
+      <c r="EO20" s="31"/>
+      <c r="EP20" s="31"/>
+      <c r="EQ20" s="31"/>
+      <c r="ER20" s="31"/>
+      <c r="ES20" s="31"/>
+      <c r="ET20" s="31"/>
+      <c r="EU20" s="31"/>
+      <c r="EV20" s="31"/>
+      <c r="EW20" s="31"/>
+      <c r="EX20" s="31"/>
+      <c r="EY20" s="68">
         <f>SUM(C20:EX20)</f>
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:155" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="54"/>
-      <c r="B21" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="32"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="32"/>
-      <c r="T21" s="32"/>
-      <c r="U21" s="32"/>
-      <c r="V21" s="32"/>
-      <c r="W21" s="32"/>
-      <c r="X21" s="32"/>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="32"/>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="32"/>
-      <c r="AC21" s="32"/>
-      <c r="AD21" s="32"/>
-      <c r="AE21" s="32"/>
-      <c r="AF21" s="32"/>
-      <c r="AG21" s="32"/>
-      <c r="AH21" s="32"/>
-      <c r="AI21" s="32"/>
-      <c r="AJ21" s="32"/>
-      <c r="AK21" s="32"/>
-      <c r="AL21" s="32"/>
-      <c r="AM21" s="32"/>
-      <c r="AN21" s="32"/>
-      <c r="AO21" s="32"/>
-      <c r="AP21" s="32"/>
-      <c r="AQ21" s="32"/>
-      <c r="AR21" s="32"/>
-      <c r="AS21" s="32"/>
-      <c r="AT21" s="32"/>
-      <c r="AU21" s="32"/>
-      <c r="AV21" s="32"/>
-      <c r="AW21" s="32"/>
-      <c r="AX21" s="32"/>
-      <c r="AY21" s="32"/>
-      <c r="AZ21" s="32"/>
-      <c r="BA21" s="32"/>
-      <c r="BB21" s="32"/>
-      <c r="BC21" s="32"/>
-      <c r="BD21" s="32"/>
-      <c r="BE21" s="32"/>
-      <c r="BF21" s="32"/>
-      <c r="BG21" s="32"/>
-      <c r="BH21" s="32"/>
-      <c r="BI21" s="32"/>
-      <c r="BJ21" s="32"/>
-      <c r="BK21" s="32"/>
-      <c r="BL21" s="32"/>
-      <c r="BM21" s="32"/>
-      <c r="BN21" s="32"/>
-      <c r="BO21" s="32"/>
-      <c r="BP21" s="32"/>
-      <c r="BQ21" s="32"/>
-      <c r="BR21" s="32"/>
-      <c r="BS21" s="32"/>
-      <c r="BT21" s="32"/>
-      <c r="BU21" s="32"/>
-      <c r="BV21" s="32"/>
-      <c r="BW21" s="32"/>
-      <c r="BX21" s="32"/>
-      <c r="BY21" s="32"/>
-      <c r="BZ21" s="32"/>
-      <c r="CA21" s="32"/>
-      <c r="CB21" s="32"/>
-      <c r="CC21" s="32"/>
-      <c r="CD21" s="32"/>
-      <c r="CE21" s="32"/>
-      <c r="CF21" s="32"/>
-      <c r="CG21" s="32"/>
-      <c r="CH21" s="32"/>
-      <c r="CI21" s="32"/>
-      <c r="CJ21" s="32"/>
-      <c r="CK21" s="32"/>
-      <c r="CL21" s="32"/>
-      <c r="CM21" s="32"/>
-      <c r="CN21" s="32"/>
-      <c r="CO21" s="32"/>
-      <c r="CP21" s="32"/>
-      <c r="CQ21" s="32"/>
-      <c r="CR21" s="32"/>
-      <c r="CS21" s="32"/>
-      <c r="CT21" s="32"/>
-      <c r="CU21" s="32"/>
-      <c r="CV21" s="32"/>
-      <c r="CW21" s="32"/>
-      <c r="CX21" s="32"/>
-      <c r="CY21" s="32"/>
-      <c r="CZ21" s="32"/>
-      <c r="DA21" s="32"/>
-      <c r="DB21" s="32"/>
-      <c r="DC21" s="32"/>
-      <c r="DD21" s="32"/>
-      <c r="DE21" s="32"/>
-      <c r="DF21" s="32"/>
-      <c r="DG21" s="32"/>
-      <c r="DH21" s="32"/>
-      <c r="DI21" s="32"/>
-      <c r="DJ21" s="32"/>
-      <c r="DK21" s="32"/>
-      <c r="DL21" s="32"/>
-      <c r="DM21" s="32"/>
-      <c r="DN21" s="32"/>
-      <c r="DO21" s="32"/>
-      <c r="DP21" s="32"/>
-      <c r="DQ21" s="32"/>
-      <c r="DR21" s="32"/>
-      <c r="DS21" s="32"/>
-      <c r="DT21" s="32"/>
-      <c r="DU21" s="32"/>
-      <c r="DV21" s="32"/>
-      <c r="DW21" s="32"/>
-      <c r="DX21" s="32"/>
-      <c r="DY21" s="32"/>
-      <c r="DZ21" s="32"/>
-      <c r="EA21" s="32"/>
-      <c r="EB21" s="32"/>
-      <c r="EC21" s="32"/>
-      <c r="ED21" s="32"/>
-      <c r="EE21" s="32"/>
-      <c r="EF21" s="32"/>
-      <c r="EG21" s="32"/>
-      <c r="EH21" s="32"/>
-      <c r="EI21" s="32"/>
-      <c r="EJ21" s="32"/>
-      <c r="EK21" s="32"/>
-      <c r="EL21" s="32"/>
-      <c r="EM21" s="32"/>
-      <c r="EN21" s="32"/>
-      <c r="EO21" s="32"/>
-      <c r="EP21" s="32"/>
-      <c r="EQ21" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="ER21" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="ES21" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="ET21" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EU21" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EV21" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EW21" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EX21" s="66">
-        <v>0.125</v>
-      </c>
-      <c r="EY21" s="72">
+    <row r="21" spans="1:155" ht="31.15">
+      <c r="A21" s="71"/>
+      <c r="B21" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="31"/>
+      <c r="V21" s="31"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="31"/>
+      <c r="Y21" s="31"/>
+      <c r="Z21" s="31"/>
+      <c r="AA21" s="31"/>
+      <c r="AB21" s="31"/>
+      <c r="AC21" s="31"/>
+      <c r="AD21" s="31"/>
+      <c r="AE21" s="31"/>
+      <c r="AF21" s="31"/>
+      <c r="AG21" s="31"/>
+      <c r="AH21" s="31"/>
+      <c r="AI21" s="31"/>
+      <c r="AJ21" s="31"/>
+      <c r="AK21" s="31"/>
+      <c r="AL21" s="31"/>
+      <c r="AM21" s="31"/>
+      <c r="AN21" s="31"/>
+      <c r="AO21" s="31"/>
+      <c r="AP21" s="31"/>
+      <c r="AQ21" s="31"/>
+      <c r="AR21" s="31"/>
+      <c r="AS21" s="31"/>
+      <c r="AT21" s="31"/>
+      <c r="AU21" s="31"/>
+      <c r="AV21" s="31"/>
+      <c r="AW21" s="31"/>
+      <c r="AX21" s="31"/>
+      <c r="AY21" s="31"/>
+      <c r="AZ21" s="31"/>
+      <c r="BA21" s="31"/>
+      <c r="BB21" s="31"/>
+      <c r="BC21" s="31"/>
+      <c r="BD21" s="31"/>
+      <c r="BE21" s="31"/>
+      <c r="BF21" s="31"/>
+      <c r="BG21" s="31"/>
+      <c r="BH21" s="31"/>
+      <c r="BI21" s="31"/>
+      <c r="BJ21" s="31"/>
+      <c r="BK21" s="31"/>
+      <c r="BL21" s="31"/>
+      <c r="BM21" s="31"/>
+      <c r="BN21" s="31"/>
+      <c r="BO21" s="31"/>
+      <c r="BP21" s="31"/>
+      <c r="BQ21" s="31"/>
+      <c r="BR21" s="31"/>
+      <c r="BS21" s="31"/>
+      <c r="BT21" s="31"/>
+      <c r="BU21" s="31"/>
+      <c r="BV21" s="31"/>
+      <c r="BW21" s="31"/>
+      <c r="BX21" s="31"/>
+      <c r="BY21" s="31"/>
+      <c r="BZ21" s="31"/>
+      <c r="CA21" s="31"/>
+      <c r="CB21" s="31"/>
+      <c r="CC21" s="31"/>
+      <c r="CD21" s="31"/>
+      <c r="CE21" s="31"/>
+      <c r="CF21" s="31"/>
+      <c r="CG21" s="31"/>
+      <c r="CH21" s="31"/>
+      <c r="CI21" s="31"/>
+      <c r="CJ21" s="31"/>
+      <c r="CK21" s="31"/>
+      <c r="CL21" s="31"/>
+      <c r="CM21" s="31"/>
+      <c r="CN21" s="31"/>
+      <c r="CO21" s="31"/>
+      <c r="CP21" s="31"/>
+      <c r="CQ21" s="31"/>
+      <c r="CR21" s="31"/>
+      <c r="CS21" s="31"/>
+      <c r="CT21" s="31"/>
+      <c r="CU21" s="31"/>
+      <c r="CV21" s="31"/>
+      <c r="CW21" s="31"/>
+      <c r="CX21" s="31"/>
+      <c r="CY21" s="31"/>
+      <c r="CZ21" s="31"/>
+      <c r="DA21" s="31"/>
+      <c r="DB21" s="31"/>
+      <c r="DC21" s="31"/>
+      <c r="DD21" s="31"/>
+      <c r="DE21" s="31"/>
+      <c r="DF21" s="31"/>
+      <c r="DG21" s="31"/>
+      <c r="DH21" s="31"/>
+      <c r="DI21" s="31"/>
+      <c r="DJ21" s="31"/>
+      <c r="DK21" s="31"/>
+      <c r="DL21" s="31"/>
+      <c r="DM21" s="31"/>
+      <c r="DN21" s="31"/>
+      <c r="DO21" s="31"/>
+      <c r="DP21" s="31"/>
+      <c r="DQ21" s="31"/>
+      <c r="DR21" s="31"/>
+      <c r="DS21" s="31"/>
+      <c r="DT21" s="31"/>
+      <c r="DU21" s="31"/>
+      <c r="DV21" s="31"/>
+      <c r="DW21" s="31"/>
+      <c r="DX21" s="31"/>
+      <c r="DY21" s="31"/>
+      <c r="DZ21" s="31"/>
+      <c r="EA21" s="31"/>
+      <c r="EB21" s="31"/>
+      <c r="EC21" s="31"/>
+      <c r="ED21" s="31"/>
+      <c r="EE21" s="31"/>
+      <c r="EF21" s="31"/>
+      <c r="EG21" s="31"/>
+      <c r="EH21" s="31"/>
+      <c r="EI21" s="31"/>
+      <c r="EJ21" s="31"/>
+      <c r="EK21" s="31"/>
+      <c r="EL21" s="31"/>
+      <c r="EM21" s="31"/>
+      <c r="EN21" s="31"/>
+      <c r="EO21" s="31"/>
+      <c r="EP21" s="31"/>
+      <c r="EQ21" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="ER21" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="ES21" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="ET21" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EU21" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EV21" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EW21" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EX21" s="62">
+        <v>0.125</v>
+      </c>
+      <c r="EY21" s="68">
         <f>SUM(C21:EX21)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:155" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="54"/>
-      <c r="B22" s="58" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="47">
+    <row r="22" spans="1:155" ht="15.6">
+      <c r="A22" s="71"/>
+      <c r="B22" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="46">
         <f>SUM(C18:C21)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="46">
         <f>SUM(D18:D21)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="46">
         <f>SUM(E18:E21)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="47">
+      <c r="F22" s="46">
         <f>SUM(F18:F21)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="47">
+      <c r="G22" s="46">
         <f>SUM(G18:G21)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="47">
+      <c r="H22" s="46">
         <f>SUM(H18:H21)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="47">
+      <c r="I22" s="46">
         <f>SUM(I18:I21)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="47">
+      <c r="J22" s="46">
         <f>SUM(J18:J21)</f>
         <v>0</v>
       </c>
-      <c r="K22" s="47">
+      <c r="K22" s="46">
         <f>SUM(K18:K21)</f>
         <v>0</v>
       </c>
-      <c r="L22" s="47">
+      <c r="L22" s="46">
         <f>SUM(L18:L21)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="47">
+      <c r="M22" s="46">
         <f>SUM(M18:M21)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="47">
+      <c r="N22" s="46">
         <f>SUM(N18:N21)</f>
         <v>0</v>
       </c>
-      <c r="O22" s="47">
+      <c r="O22" s="46">
         <f>SUM(O18:O21)</f>
         <v>0</v>
       </c>
-      <c r="P22" s="47">
+      <c r="P22" s="46">
         <f>SUM(P18:P21)</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="47">
+      <c r="Q22" s="46">
         <f>SUM(Q18:Q21)</f>
         <v>0</v>
       </c>
-      <c r="R22" s="47">
+      <c r="R22" s="46">
         <f>SUM(R18:R21)</f>
         <v>0</v>
       </c>
-      <c r="S22" s="47">
+      <c r="S22" s="46">
         <f>SUM(S18:S21)</f>
         <v>0</v>
       </c>
-      <c r="T22" s="47">
+      <c r="T22" s="46">
         <f>SUM(T18:T21)</f>
         <v>0</v>
       </c>
-      <c r="U22" s="47">
+      <c r="U22" s="46">
         <f>SUM(U18:U21)</f>
         <v>0</v>
       </c>
-      <c r="V22" s="47">
+      <c r="V22" s="46">
         <f>SUM(V18:V21)</f>
         <v>0</v>
       </c>
-      <c r="W22" s="47">
+      <c r="W22" s="46">
         <f>SUM(W18:W21)</f>
         <v>0</v>
       </c>
-      <c r="X22" s="47">
+      <c r="X22" s="46">
         <f>SUM(X18:X21)</f>
         <v>0</v>
       </c>
-      <c r="Y22" s="47">
+      <c r="Y22" s="46">
         <f>SUM(Y18:Y21)</f>
         <v>0</v>
       </c>
-      <c r="Z22" s="47">
+      <c r="Z22" s="46">
         <f>SUM(Z18:Z21)</f>
         <v>0</v>
       </c>
-      <c r="AA22" s="47">
+      <c r="AA22" s="46">
         <f>SUM(AA18:AA21)</f>
         <v>0</v>
       </c>
-      <c r="AB22" s="47">
+      <c r="AB22" s="46">
         <f>SUM(AB18:AB21)</f>
         <v>0</v>
       </c>
-      <c r="AC22" s="47">
+      <c r="AC22" s="46">
         <f>SUM(AC18:AC21)</f>
         <v>0</v>
       </c>
-      <c r="AD22" s="47">
+      <c r="AD22" s="46">
         <f>SUM(AD18:AD21)</f>
         <v>0</v>
       </c>
-      <c r="AE22" s="47">
+      <c r="AE22" s="46">
         <f>SUM(AE18:AE21)</f>
         <v>0</v>
       </c>
-      <c r="AF22" s="47">
+      <c r="AF22" s="46">
         <f>SUM(AF18:AF21)</f>
         <v>0</v>
       </c>
-      <c r="AG22" s="47">
+      <c r="AG22" s="46">
         <f>SUM(AG18:AG21)</f>
         <v>0</v>
       </c>
-      <c r="AH22" s="47">
+      <c r="AH22" s="46">
         <f>SUM(AH18:AH21)</f>
         <v>0</v>
       </c>
-      <c r="AI22" s="47">
+      <c r="AI22" s="46">
         <f>SUM(AI18:AI21)</f>
         <v>0</v>
       </c>
-      <c r="AJ22" s="47">
+      <c r="AJ22" s="46">
         <f>SUM(AJ18:AJ21)</f>
         <v>0</v>
       </c>
-      <c r="AK22" s="47">
+      <c r="AK22" s="46">
         <f>SUM(AK18:AK21)</f>
         <v>0</v>
       </c>
-      <c r="AL22" s="47">
+      <c r="AL22" s="46">
         <f>SUM(AL18:AL21)</f>
         <v>0</v>
       </c>
-      <c r="AM22" s="47">
+      <c r="AM22" s="46">
         <f>SUM(AM18:AM21)</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AN22" s="47">
+      <c r="AN22" s="46">
         <f>SUM(AN18:AN21)</f>
         <v>0</v>
       </c>
-      <c r="AO22" s="47">
+      <c r="AO22" s="46">
         <f>SUM(AO18:AO21)</f>
         <v>0</v>
       </c>
-      <c r="AP22" s="47">
+      <c r="AP22" s="46">
         <f>SUM(AP18:AP21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AQ22" s="47">
+      <c r="AQ22" s="46">
         <f>SUM(AQ18:AQ21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AR22" s="47">
+      <c r="AR22" s="46">
         <f>SUM(AR18:AR21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AS22" s="47">
+      <c r="AS22" s="46">
         <f>SUM(AS18:AS21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AT22" s="47">
+      <c r="AT22" s="46">
         <f>SUM(AT18:AT21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AU22" s="47">
+      <c r="AU22" s="46">
         <f>SUM(AU18:AU21)</f>
         <v>0</v>
       </c>
-      <c r="AV22" s="47">
+      <c r="AV22" s="46">
         <f>SUM(AV18:AV21)</f>
         <v>0</v>
       </c>
-      <c r="AW22" s="47">
+      <c r="AW22" s="46">
         <f>SUM(AW18:AW21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AX22" s="47">
+      <c r="AX22" s="46">
         <f>SUM(AX18:AX21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AY22" s="47">
+      <c r="AY22" s="46">
         <f>SUM(AY18:AY21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AZ22" s="47">
+      <c r="AZ22" s="46">
         <f>SUM(AZ18:AZ21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BA22" s="47">
+      <c r="BA22" s="46">
         <f>SUM(BA18:BA21)</f>
         <v>0.25</v>
       </c>
-      <c r="BB22" s="47">
+      <c r="BB22" s="46">
         <f>SUM(BB18:BB21)</f>
         <v>0</v>
       </c>
-      <c r="BC22" s="47">
+      <c r="BC22" s="46">
         <f>SUM(BC18:BC21)</f>
         <v>0</v>
       </c>
-      <c r="BD22" s="47">
+      <c r="BD22" s="46">
         <f>SUM(BD18:BD21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BE22" s="47">
+      <c r="BE22" s="46">
         <f>SUM(BE18:BE21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BF22" s="47">
+      <c r="BF22" s="46">
         <f>SUM(BF18:BF21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BG22" s="47">
+      <c r="BG22" s="46">
         <f>SUM(BG18:BG21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BH22" s="47">
+      <c r="BH22" s="46">
         <f>SUM(BH18:BH21)</f>
         <v>0.25</v>
       </c>
-      <c r="BI22" s="47">
+      <c r="BI22" s="46">
         <f>SUM(BI18:BI21)</f>
         <v>0</v>
       </c>
-      <c r="BJ22" s="47">
+      <c r="BJ22" s="46">
         <f>SUM(BJ18:BJ21)</f>
         <v>0</v>
       </c>
-      <c r="BK22" s="47">
+      <c r="BK22" s="46">
         <f>SUM(BK18:BK21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BL22" s="47">
+      <c r="BL22" s="46">
         <f>SUM(BL18:BL21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BM22" s="47">
+      <c r="BM22" s="46">
         <f>SUM(BM18:BM21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BN22" s="47">
+      <c r="BN22" s="46">
         <f>SUM(BN18:BN21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BO22" s="47">
+      <c r="BO22" s="46">
         <f>SUM(BO18:BO21)</f>
         <v>0.25</v>
       </c>
-      <c r="BP22" s="47">
+      <c r="BP22" s="46">
         <f>SUM(BP18:BP21)</f>
         <v>0</v>
       </c>
-      <c r="BQ22" s="47">
+      <c r="BQ22" s="46">
         <f>SUM(BQ18:BQ21)</f>
         <v>0</v>
       </c>
-      <c r="BR22" s="47">
+      <c r="BR22" s="46">
         <f>SUM(BR18:BR21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BS22" s="47">
+      <c r="BS22" s="46">
         <f>SUM(BS18:BS21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BT22" s="47">
+      <c r="BT22" s="46">
         <f>SUM(BT18:BT21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BU22" s="47">
+      <c r="BU22" s="46">
         <f>SUM(BU18:BU21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BV22" s="47">
+      <c r="BV22" s="46">
         <f>SUM(BV18:BV21)</f>
         <v>0.25</v>
       </c>
-      <c r="BW22" s="47">
+      <c r="BW22" s="46">
         <f>SUM(BW18:BW21)</f>
         <v>0</v>
       </c>
-      <c r="BX22" s="47">
+      <c r="BX22" s="46">
         <f>SUM(BX18:BX21)</f>
         <v>0</v>
       </c>
-      <c r="BY22" s="47">
+      <c r="BY22" s="46">
         <f>SUM(BY18:BY21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BZ22" s="47">
+      <c r="BZ22" s="46">
         <f>SUM(BZ18:BZ21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CA22" s="47">
+      <c r="CA22" s="46">
         <f>SUM(CA18:CA21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CB22" s="47">
+      <c r="CB22" s="46">
         <f>SUM(CB18:CB21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CC22" s="47">
+      <c r="CC22" s="46">
         <f>SUM(CC18:CC21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CD22" s="47">
+      <c r="CD22" s="46">
         <f>SUM(CD18:CD21)</f>
         <v>0</v>
       </c>
-      <c r="CE22" s="47">
+      <c r="CE22" s="46">
         <f>SUM(CE18:CE21)</f>
         <v>0</v>
       </c>
-      <c r="CF22" s="47">
+      <c r="CF22" s="46">
         <f>SUM(CF18:CF21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CG22" s="47">
+      <c r="CG22" s="46">
         <f>SUM(CG18:CG21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CH22" s="47">
+      <c r="CH22" s="46">
         <f>SUM(CH18:CH21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CI22" s="47">
+      <c r="CI22" s="46">
         <f>SUM(CI18:CI21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CJ22" s="47">
+      <c r="CJ22" s="46">
         <f>SUM(CJ18:CJ21)</f>
         <v>0.25</v>
       </c>
-      <c r="CK22" s="47">
+      <c r="CK22" s="46">
         <f>SUM(CK18:CK21)</f>
         <v>0</v>
       </c>
-      <c r="CL22" s="47">
+      <c r="CL22" s="46">
         <f>SUM(CL18:CL21)</f>
         <v>0</v>
       </c>
-      <c r="CM22" s="47">
+      <c r="CM22" s="46">
         <f>SUM(CM18:CM21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CN22" s="47">
+      <c r="CN22" s="46">
         <f>SUM(CN18:CN21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CO22" s="47">
+      <c r="CO22" s="46">
         <f>SUM(CO18:CO21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CP22" s="47">
+      <c r="CP22" s="46">
         <f>SUM(CP18:CP21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CQ22" s="47">
+      <c r="CQ22" s="46">
         <f>SUM(CQ18:CQ21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CR22" s="47">
+      <c r="CR22" s="46">
         <f>SUM(CR18:CR21)</f>
         <v>0</v>
       </c>
-      <c r="CS22" s="47">
+      <c r="CS22" s="46">
         <f>SUM(CS18:CS21)</f>
         <v>0</v>
       </c>
-      <c r="CT22" s="47">
+      <c r="CT22" s="46">
         <f>SUM(CT18:CT21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CU22" s="47">
+      <c r="CU22" s="46">
         <f>SUM(CU18:CU21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CV22" s="47">
+      <c r="CV22" s="46">
         <f>SUM(CV18:CV21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CW22" s="47">
+      <c r="CW22" s="46">
         <f>SUM(CW18:CW21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CX22" s="47">
+      <c r="CX22" s="46">
         <f>SUM(CX18:CX21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CY22" s="47">
+      <c r="CY22" s="46">
         <f>SUM(CY18:CY21)</f>
         <v>0</v>
       </c>
-      <c r="CZ22" s="47">
+      <c r="CZ22" s="46">
         <f>SUM(CZ18:CZ21)</f>
         <v>0</v>
       </c>
-      <c r="DA22" s="47">
+      <c r="DA22" s="46">
         <f>SUM(DA18:DA21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DB22" s="47">
+      <c r="DB22" s="46">
         <f>SUM(DB18:DB21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DC22" s="47">
+      <c r="DC22" s="46">
         <f>SUM(DC18:DC21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DD22" s="47">
+      <c r="DD22" s="46">
         <f>SUM(DD18:DD21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DE22" s="47">
+      <c r="DE22" s="46">
         <f>SUM(DE18:DE21)</f>
         <v>0.25</v>
       </c>
-      <c r="DF22" s="47">
+      <c r="DF22" s="46">
         <f>SUM(DF18:DF21)</f>
         <v>0</v>
       </c>
-      <c r="DG22" s="47">
+      <c r="DG22" s="46">
         <f>SUM(DG18:DG21)</f>
         <v>0</v>
       </c>
-      <c r="DH22" s="47">
+      <c r="DH22" s="46">
         <f>SUM(DH18:DH21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DI22" s="47">
+      <c r="DI22" s="46">
         <f>SUM(DI18:DI21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DJ22" s="47">
+      <c r="DJ22" s="46">
         <f>SUM(DJ18:DJ21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DK22" s="47">
+      <c r="DK22" s="46">
         <f>SUM(DK18:DK21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DL22" s="47">
+      <c r="DL22" s="46">
         <f>SUM(DL18:DL21)</f>
         <v>0.25</v>
       </c>
-      <c r="DM22" s="47">
+      <c r="DM22" s="46">
         <f>SUM(DM18:DM21)</f>
         <v>0</v>
       </c>
-      <c r="DN22" s="47">
+      <c r="DN22" s="46">
         <f>SUM(DN18:DN21)</f>
         <v>0</v>
       </c>
-      <c r="DO22" s="47">
+      <c r="DO22" s="46">
         <f>SUM(DO18:DO21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DP22" s="47">
+      <c r="DP22" s="46">
         <f>SUM(DP18:DP21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DQ22" s="47">
+      <c r="DQ22" s="46">
         <f>SUM(DQ18:DQ21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DR22" s="47">
+      <c r="DR22" s="46">
         <f>SUM(DR18:DR21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DS22" s="47">
+      <c r="DS22" s="46">
         <f>SUM(DS18:DS21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DT22" s="47">
+      <c r="DT22" s="46">
         <f>SUM(DT18:DT21)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="DU22" s="47">
+      <c r="DU22" s="46">
         <f>SUM(DU18:DU21)</f>
         <v>0.125</v>
       </c>
-      <c r="DV22" s="47">
+      <c r="DV22" s="46">
         <f>SUM(DV18:DV21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DW22" s="47">
+      <c r="DW22" s="46">
         <f>SUM(DW18:DW21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DX22" s="47">
+      <c r="DX22" s="46">
         <f>SUM(DX18:DX21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DY22" s="47">
+      <c r="DY22" s="46">
         <f>SUM(DY18:DY21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DZ22" s="47">
+      <c r="DZ22" s="46">
         <f>SUM(DZ18:DZ21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EA22" s="47">
+      <c r="EA22" s="46">
         <f>SUM(EA18:EA21)</f>
         <v>0.125</v>
       </c>
-      <c r="EB22" s="47">
+      <c r="EB22" s="46">
         <f>SUM(EB18:EB21)</f>
         <v>0.125</v>
       </c>
-      <c r="EC22" s="47">
+      <c r="EC22" s="46">
         <f>SUM(EC18:EC21)</f>
         <v>0.25</v>
       </c>
-      <c r="ED22" s="47">
+      <c r="ED22" s="46">
         <f>SUM(ED18:ED21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EE22" s="47">
+      <c r="EE22" s="46">
         <f>SUM(EE18:EE21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EF22" s="47">
+      <c r="EF22" s="46">
         <f>SUM(EF18:EF21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EG22" s="47">
+      <c r="EG22" s="46">
         <f>SUM(EG18:EG21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EH22" s="47">
+      <c r="EH22" s="46">
         <f>SUM(EH18:EH21)</f>
         <v>0.125</v>
       </c>
-      <c r="EI22" s="47">
+      <c r="EI22" s="46">
         <f>SUM(EI18:EI21)</f>
         <v>0.125</v>
       </c>
-      <c r="EJ22" s="47">
+      <c r="EJ22" s="46">
         <f>SUM(EJ18:EJ21)</f>
         <v>0.25</v>
       </c>
-      <c r="EK22" s="47">
+      <c r="EK22" s="46">
         <f>SUM(EK18:EK21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EL22" s="47">
+      <c r="EL22" s="46">
         <f>SUM(EL18:EL21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EM22" s="47">
+      <c r="EM22" s="46">
         <f>SUM(EM18:EM21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EN22" s="47">
+      <c r="EN22" s="46">
         <f>SUM(EN18:EN21)</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EO22" s="47">
+      <c r="EO22" s="46">
         <f>SUM(EO18:EO21)</f>
         <v>0.125</v>
       </c>
-      <c r="EP22" s="47">
+      <c r="EP22" s="46">
         <f>SUM(EP18:EP21)</f>
         <v>0.125</v>
       </c>
-      <c r="EQ22" s="47">
+      <c r="EQ22" s="46">
         <f>SUM(EQ18:EQ21)</f>
         <v>0.125</v>
       </c>
-      <c r="ER22" s="47">
+      <c r="ER22" s="46">
         <f>SUM(ER18:ER21)</f>
         <v>0.125</v>
       </c>
-      <c r="ES22" s="47">
+      <c r="ES22" s="46">
         <f>SUM(ES18:ES21)</f>
         <v>0.125</v>
       </c>
-      <c r="ET22" s="47">
+      <c r="ET22" s="46">
         <f>SUM(ET18:ET21)</f>
         <v>0.125</v>
       </c>
-      <c r="EU22" s="47">
+      <c r="EU22" s="46">
         <f>SUM(EU18:EU21)</f>
         <v>0.125</v>
       </c>
-      <c r="EV22" s="47">
+      <c r="EV22" s="46">
         <f>SUM(EV18:EV21)</f>
         <v>0.125</v>
       </c>
-      <c r="EW22" s="47">
+      <c r="EW22" s="46">
         <f>SUM(EW18:EW21)</f>
         <v>0.125</v>
       </c>
-      <c r="EX22" s="47">
+      <c r="EX22" s="46">
         <f>SUM(EX18:EX21)</f>
         <v>0.125</v>
       </c>
-      <c r="EY22" s="72">
+      <c r="EY22" s="68">
         <f t="shared" si="72"/>
         <v>18.125000000000007</v>
       </c>
     </row>
-    <row r="23" spans="1:155" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:155" ht="15.6">
       <c r="A23" s="73" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B23" s="74"/>
-      <c r="C23" s="47">
+      <c r="C23" s="46">
         <f>C14+C17+C22</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D23" s="47">
+      <c r="D23" s="46">
         <f>D14+D17+D22</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E23" s="47">
+      <c r="E23" s="46">
         <f>E14+E17+E22</f>
         <v>0</v>
       </c>
-      <c r="F23" s="47">
+      <c r="F23" s="46">
         <f>F14+F17+F22</f>
         <v>0</v>
       </c>
-      <c r="G23" s="47">
+      <c r="G23" s="46">
         <f>G14+G17+G22</f>
         <v>0.125</v>
       </c>
-      <c r="H23" s="47">
+      <c r="H23" s="46">
         <f>H14+H17+H22</f>
         <v>0.125</v>
       </c>
-      <c r="I23" s="47">
+      <c r="I23" s="46">
         <f>I14+I17+I22</f>
         <v>0.125</v>
       </c>
-      <c r="J23" s="47">
+      <c r="J23" s="46">
         <f>J14+J17+J22</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="K23" s="47">
+      <c r="K23" s="46">
         <f>K14+K17+K22</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="L23" s="47">
+      <c r="L23" s="46">
         <f>L14+L17+L22</f>
         <v>0</v>
       </c>
-      <c r="M23" s="47">
+      <c r="M23" s="46">
         <f>M14+M17+M22</f>
         <v>0</v>
       </c>
-      <c r="N23" s="47">
+      <c r="N23" s="46">
         <f>N14+N17+N22</f>
         <v>0.125</v>
       </c>
-      <c r="O23" s="47">
+      <c r="O23" s="46">
         <f>O14+O17+O22</f>
         <v>0.125</v>
       </c>
-      <c r="P23" s="47">
+      <c r="P23" s="46">
         <f>P14+P17+P22</f>
         <v>0.125</v>
       </c>
-      <c r="Q23" s="47">
+      <c r="Q23" s="46">
         <f>Q14+Q17+Q22</f>
         <v>0.125</v>
       </c>
-      <c r="R23" s="47">
+      <c r="R23" s="46">
         <f>R14+R17+R22</f>
         <v>0.125</v>
       </c>
-      <c r="S23" s="47">
+      <c r="S23" s="46">
         <f>S14+S17+S22</f>
         <v>0</v>
       </c>
-      <c r="T23" s="47">
+      <c r="T23" s="46">
         <f>T14+T17+T22</f>
         <v>0</v>
       </c>
-      <c r="U23" s="47">
+      <c r="U23" s="46">
         <f t="shared" ref="U23:AL23" si="74">U14+U17+U22</f>
         <v>0.125</v>
       </c>
-      <c r="V23" s="47">
+      <c r="V23" s="46">
         <f t="shared" si="74"/>
         <v>0.125</v>
       </c>
-      <c r="W23" s="47">
+      <c r="W23" s="46">
         <f t="shared" si="74"/>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="X23" s="47">
+      <c r="X23" s="46">
         <f t="shared" si="74"/>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="Y23" s="47">
+      <c r="Y23" s="46">
         <f>Y14+Y17+Y22</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="Z23" s="47">
+      <c r="Z23" s="46">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AA23" s="47">
+      <c r="AA23" s="46">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AB23" s="47">
+      <c r="AB23" s="46">
         <f t="shared" si="74"/>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AC23" s="47">
+      <c r="AC23" s="46">
         <f t="shared" si="74"/>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AD23" s="47">
+      <c r="AD23" s="46">
         <f>AD14+AD17+AD22</f>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AE23" s="47">
+      <c r="AE23" s="46">
         <f t="shared" si="74"/>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AF23" s="47">
+      <c r="AF23" s="46">
         <f t="shared" si="74"/>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AG23" s="47">
+      <c r="AG23" s="46">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="47">
+      <c r="AH23" s="46">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AI23" s="47">
+      <c r="AI23" s="46">
         <f t="shared" si="74"/>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AJ23" s="47">
+      <c r="AJ23" s="46">
         <f t="shared" si="74"/>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AK23" s="47">
+      <c r="AK23" s="46">
         <f t="shared" si="74"/>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AL23" s="47">
+      <c r="AL23" s="46">
         <f t="shared" si="74"/>
         <v>9.0277777777777776E-2</v>
       </c>
-      <c r="AM23" s="47">
+      <c r="AM23" s="46">
         <f>AM14+AM17+AM22</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="AN23" s="47">
+      <c r="AN23" s="46">
         <f>AN14+AN17+AN22</f>
         <v>0</v>
       </c>
-      <c r="AO23" s="47">
+      <c r="AO23" s="46">
         <f>AO14+AO17+AO22</f>
         <v>0</v>
       </c>
-      <c r="AP23" s="47">
+      <c r="AP23" s="46">
         <f>AP14+AP17+AP22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AQ23" s="47">
+      <c r="AQ23" s="46">
         <f>AQ14+AQ17+AQ22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AR23" s="47">
+      <c r="AR23" s="46">
         <f>AR14+AR17+AR22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AS23" s="47">
+      <c r="AS23" s="46">
         <f>AS14+AS17+AS22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AT23" s="47">
+      <c r="AT23" s="46">
         <f>AT14+AT17+AT22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AU23" s="47">
+      <c r="AU23" s="46">
         <f>AU14+AU17+AU22</f>
         <v>0</v>
       </c>
-      <c r="AV23" s="47">
+      <c r="AV23" s="46">
         <f>AV14+AV17+AV22</f>
         <v>0</v>
       </c>
-      <c r="AW23" s="47">
+      <c r="AW23" s="46">
         <f>AW14+AW17+AW22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AX23" s="47">
+      <c r="AX23" s="46">
         <f>AX14+AX17+AX22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AY23" s="47">
+      <c r="AY23" s="46">
         <f>AY14+AY17+AY22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="AZ23" s="47">
+      <c r="AZ23" s="46">
         <f>AZ14+AZ17+AZ22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BA23" s="47">
+      <c r="BA23" s="46">
         <f>BA14+BA17+BA22</f>
         <v>0.25</v>
       </c>
-      <c r="BB23" s="47">
+      <c r="BB23" s="46">
         <f>BB14+BB17+BB22</f>
         <v>0</v>
       </c>
-      <c r="BC23" s="47">
+      <c r="BC23" s="46">
         <f>BC14+BC17+BC22</f>
         <v>0</v>
       </c>
-      <c r="BD23" s="47">
+      <c r="BD23" s="46">
         <f>BD14+BD17+BD22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BE23" s="47">
+      <c r="BE23" s="46">
         <f>BE14+BE17+BE22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BF23" s="47">
+      <c r="BF23" s="46">
         <f>BF14+BF17+BF22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BG23" s="47">
+      <c r="BG23" s="46">
         <f>BG14+BG17+BG22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BH23" s="47">
+      <c r="BH23" s="46">
         <f>BH14+BH17+BH22</f>
         <v>0.25</v>
       </c>
-      <c r="BI23" s="47">
+      <c r="BI23" s="46">
         <f>BI14+BI17+BI22</f>
         <v>0</v>
       </c>
-      <c r="BJ23" s="47">
+      <c r="BJ23" s="46">
         <f>BJ14+BJ17+BJ22</f>
         <v>0</v>
       </c>
-      <c r="BK23" s="47">
+      <c r="BK23" s="46">
         <f>BK14+BK17+BK22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BL23" s="47">
+      <c r="BL23" s="46">
         <f>BL14+BL17+BL22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BM23" s="47">
+      <c r="BM23" s="46">
         <f>BM14+BM17+BM22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BN23" s="47">
+      <c r="BN23" s="46">
         <f>BN14+BN17+BN22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BO23" s="47">
+      <c r="BO23" s="46">
         <f>BO14+BO17+BO22</f>
         <v>0.25</v>
       </c>
-      <c r="BP23" s="47">
+      <c r="BP23" s="46">
         <f>BP14+BP17+BP22</f>
         <v>0</v>
       </c>
-      <c r="BQ23" s="47">
+      <c r="BQ23" s="46">
         <f>BQ14+BQ17+BQ22</f>
         <v>0</v>
       </c>
-      <c r="BR23" s="47">
+      <c r="BR23" s="46">
         <f>BR14+BR17+BR22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BS23" s="47">
+      <c r="BS23" s="46">
         <f>BS14+BS17+BS22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BT23" s="47">
+      <c r="BT23" s="46">
         <f>BT14+BT17+BT22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BU23" s="47">
+      <c r="BU23" s="46">
         <f>BU14+BU17+BU22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BV23" s="47">
+      <c r="BV23" s="46">
         <f>BV14+BV17+BV22</f>
         <v>0.25</v>
       </c>
-      <c r="BW23" s="47">
+      <c r="BW23" s="46">
         <f>BW14+BW17+BW22</f>
         <v>0</v>
       </c>
-      <c r="BX23" s="47">
+      <c r="BX23" s="46">
         <f>BX14+BX17+BX22</f>
         <v>0</v>
       </c>
-      <c r="BY23" s="47">
+      <c r="BY23" s="46">
         <f>BY14+BY17+BY22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="BZ23" s="47">
+      <c r="BZ23" s="46">
         <f>BZ14+BZ17+BZ22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CA23" s="47">
+      <c r="CA23" s="46">
         <f>CA14+CA17+CA22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CB23" s="47">
+      <c r="CB23" s="46">
         <f>CB14+CB17+CB22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CC23" s="47">
+      <c r="CC23" s="46">
         <f>CC14+CC17+CC22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CD23" s="47">
+      <c r="CD23" s="46">
         <f>CD14+CD17+CD22</f>
         <v>0</v>
       </c>
-      <c r="CE23" s="47">
+      <c r="CE23" s="46">
         <f>CE14+CE17+CE22</f>
         <v>0</v>
       </c>
-      <c r="CF23" s="47">
+      <c r="CF23" s="46">
         <f>CF14+CF17+CF22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CG23" s="47">
+      <c r="CG23" s="46">
         <f>CG14+CG17+CG22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CH23" s="47">
+      <c r="CH23" s="46">
         <f>CH14+CH17+CH22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CI23" s="47">
+      <c r="CI23" s="46">
         <f>CI14+CI17+CI22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CJ23" s="47">
+      <c r="CJ23" s="46">
         <f>CJ14+CJ17+CJ22</f>
         <v>0.25</v>
       </c>
-      <c r="CK23" s="47">
+      <c r="CK23" s="46">
         <f>CK14+CK17+CK22</f>
         <v>0</v>
       </c>
-      <c r="CL23" s="47">
+      <c r="CL23" s="46">
         <f>CL14+CL17+CL22</f>
         <v>0</v>
       </c>
-      <c r="CM23" s="47">
+      <c r="CM23" s="46">
         <f>CM14+CM17+CM22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CN23" s="47">
+      <c r="CN23" s="46">
         <f>CN14+CN17+CN22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CO23" s="47">
+      <c r="CO23" s="46">
         <f>CO14+CO17+CO22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CP23" s="47">
+      <c r="CP23" s="46">
         <f>CP14+CP17+CP22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CQ23" s="47">
+      <c r="CQ23" s="46">
         <f>CQ14+CQ17+CQ22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CR23" s="47">
+      <c r="CR23" s="46">
         <f>CR14+CR17+CR22</f>
         <v>0</v>
       </c>
-      <c r="CS23" s="47">
+      <c r="CS23" s="46">
         <f>CS14+CS17+CS22</f>
         <v>0</v>
       </c>
-      <c r="CT23" s="47">
+      <c r="CT23" s="46">
         <f>CT14+CT17+CT22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CU23" s="47">
+      <c r="CU23" s="46">
         <f>CU14+CU17+CU22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CV23" s="47">
+      <c r="CV23" s="46">
         <f>CV14+CV17+CV22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CW23" s="47">
+      <c r="CW23" s="46">
         <f>CW14+CW17+CW22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CX23" s="47">
+      <c r="CX23" s="46">
         <f>CX14+CX17+CX22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="CY23" s="47">
+      <c r="CY23" s="46">
         <f>CY14+CY17+CY22</f>
         <v>0</v>
       </c>
-      <c r="CZ23" s="47">
+      <c r="CZ23" s="46">
         <f>CZ14+CZ17+CZ22</f>
         <v>0</v>
       </c>
-      <c r="DA23" s="47">
+      <c r="DA23" s="46">
         <f>DA14+DA17+DA22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DB23" s="47">
+      <c r="DB23" s="46">
         <f>DB14+DB17+DB22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DC23" s="47">
+      <c r="DC23" s="46">
         <f>DC14+DC17+DC22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DD23" s="47">
+      <c r="DD23" s="46">
         <f>DD14+DD17+DD22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DE23" s="47">
+      <c r="DE23" s="46">
         <f>DE14+DE17+DE22</f>
         <v>0.25</v>
       </c>
-      <c r="DF23" s="47">
+      <c r="DF23" s="46">
         <f>DF14+DF17+DF22</f>
         <v>0</v>
       </c>
-      <c r="DG23" s="47">
+      <c r="DG23" s="46">
         <f>DG14+DG17+DG22</f>
         <v>0</v>
       </c>
-      <c r="DH23" s="47">
+      <c r="DH23" s="46">
         <f>DH14+DH17+DH22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DI23" s="47">
+      <c r="DI23" s="46">
         <f>DI14+DI17+DI22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DJ23" s="47">
+      <c r="DJ23" s="46">
         <f>DJ14+DJ17+DJ22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DK23" s="47">
+      <c r="DK23" s="46">
         <f>DK14+DK17+DK22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DL23" s="47">
+      <c r="DL23" s="46">
         <f>DL14+DL17+DL22</f>
         <v>0.25</v>
       </c>
-      <c r="DM23" s="47">
+      <c r="DM23" s="46">
         <f>DM14+DM17+DM22</f>
         <v>0</v>
       </c>
-      <c r="DN23" s="47">
+      <c r="DN23" s="46">
         <f>DN14+DN17+DN22</f>
         <v>0</v>
       </c>
-      <c r="DO23" s="47">
+      <c r="DO23" s="46">
         <f>DO14+DO17+DO22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DP23" s="47">
+      <c r="DP23" s="46">
         <f>DP14+DP17+DP22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DQ23" s="47">
+      <c r="DQ23" s="46">
         <f>DQ14+DQ17+DQ22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DR23" s="47">
+      <c r="DR23" s="46">
         <f>DR14+DR17+DR22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DS23" s="47">
+      <c r="DS23" s="46">
         <f>DS14+DS17+DS22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DT23" s="47">
+      <c r="DT23" s="46">
         <f>DT14+DT17+DT22</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="DU23" s="47">
+      <c r="DU23" s="46">
         <f>DU14+DU17+DU22</f>
         <v>0.125</v>
       </c>
-      <c r="DV23" s="47">
+      <c r="DV23" s="46">
         <f>DV14+DV17+DV22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DW23" s="47">
+      <c r="DW23" s="46">
         <f>DW14+DW17+DW22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DX23" s="47">
+      <c r="DX23" s="46">
         <f>DX14+DX17+DX22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DY23" s="47">
+      <c r="DY23" s="46">
         <f>DY14+DY17+DY22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="DZ23" s="47">
+      <c r="DZ23" s="46">
         <f>DZ14+DZ17+DZ22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EA23" s="47">
+      <c r="EA23" s="46">
         <f>EA14+EA17+EA22</f>
         <v>0.125</v>
       </c>
-      <c r="EB23" s="47">
+      <c r="EB23" s="46">
         <f>EB14+EB17+EB22</f>
         <v>0.125</v>
       </c>
-      <c r="EC23" s="47">
+      <c r="EC23" s="46">
         <f>EC14+EC17+EC22</f>
         <v>0.25</v>
       </c>
-      <c r="ED23" s="47">
+      <c r="ED23" s="46">
         <f>ED14+ED17+ED22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EE23" s="47">
+      <c r="EE23" s="46">
         <f>EE14+EE17+EE22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EF23" s="47">
+      <c r="EF23" s="46">
         <f>EF14+EF17+EF22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EG23" s="47">
+      <c r="EG23" s="46">
         <f>EG14+EG17+EG22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EH23" s="47">
+      <c r="EH23" s="46">
         <f>EH14+EH17+EH22</f>
         <v>0.125</v>
       </c>
-      <c r="EI23" s="47">
+      <c r="EI23" s="46">
         <f>EI14+EI17+EI22</f>
         <v>0.125</v>
       </c>
-      <c r="EJ23" s="47">
+      <c r="EJ23" s="46">
         <f>EJ14+EJ17+EJ22</f>
         <v>0.25</v>
       </c>
-      <c r="EK23" s="47">
+      <c r="EK23" s="46">
         <f>EK14+EK17+EK22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EL23" s="47">
+      <c r="EL23" s="46">
         <f>EL14+EL17+EL22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EM23" s="47">
+      <c r="EM23" s="46">
         <f>EM14+EM17+EM22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EN23" s="47">
+      <c r="EN23" s="46">
         <f>EN14+EN17+EN22</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="EO23" s="47">
+      <c r="EO23" s="46">
         <f>EO14+EO17+EO22</f>
         <v>0.125</v>
       </c>
-      <c r="EP23" s="47">
+      <c r="EP23" s="46">
         <f>EP14+EP17+EP22</f>
         <v>0.125</v>
       </c>
-      <c r="EQ23" s="47">
+      <c r="EQ23" s="46">
         <f>EQ14+EQ17+EQ22</f>
         <v>0.125</v>
       </c>
-      <c r="ER23" s="47">
+      <c r="ER23" s="46">
         <f>ER14+ER17+ER22</f>
         <v>0.125</v>
       </c>
-      <c r="ES23" s="47">
+      <c r="ES23" s="46">
         <f>ES14+ES17+ES22</f>
         <v>0.125</v>
       </c>
-      <c r="ET23" s="47">
+      <c r="ET23" s="46">
         <f>ET14+ET17+ET22</f>
         <v>0.125</v>
       </c>
-      <c r="EU23" s="47">
+      <c r="EU23" s="46">
         <f>EU14+EU17+EU22</f>
         <v>0.125</v>
       </c>
-      <c r="EV23" s="47">
+      <c r="EV23" s="46">
         <f>EV14+EV17+EV22</f>
         <v>0.125</v>
       </c>
-      <c r="EW23" s="47">
+      <c r="EW23" s="46">
         <f>EW14+EW17+EW22</f>
         <v>0.125</v>
       </c>
-      <c r="EX23" s="47">
+      <c r="EX23" s="46">
         <f>EX14+EX17+EX22</f>
         <v>0.125</v>
       </c>
-      <c r="EY23" s="72">
+      <c r="EY23" s="68">
         <f t="shared" si="72"/>
         <v>20.791666666666668</v>
       </c>
@@ -7096,9 +7095,5 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BCAE355-489D-4D00-9C8B-00B8220779E5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BCAE355-489D-4D00-9C8B-00B8220779E5}"/>
 </file>